--- a/数据库.xlsx
+++ b/数据库.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$171</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,456 +30,1256 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="150">
-  <si>
-    <t>日期,联赛,主队,客队,盘口,预测方向,实际比分,盈亏,归因</t>
-  </si>
-  <si>
-    <t>2026-06-15,世界杯,荷兰,瑞典,主让1.5,荷兰胜,5-1,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-06-15,世界杯,德国,科特迪瓦,主让1.25,德国胜,2-1,+25元,赢半</t>
-  </si>
-  <si>
-    <t>2026-06-15,世界杯,厄瓜多尔,库拉索,主让1.75,厄瓜多尔胜,0-0,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-06-16,世界杯,突尼斯,日本,客让0.75,日本胜,0-4,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-06-20,世界杯,葡萄牙,乌兹别克斯坦,主让1.75,葡萄牙胜,5-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-06-20,世界杯,英格兰,加纳,主让2,英格兰胜,0-0,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-06-20,世界杯,巴拿马,克罗地亚,客让1,克罗地亚胜,0-1,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-06-20,世界杯,哥伦比亚,刚果(金),主让0.75,哥伦比亚胜,3-1,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-06-24,世界杯,西班牙,沙特,主让2,西班牙胜,2-0,0元,走水</t>
-  </si>
-  <si>
-    <t>2026-06-24,世界杯,比利时,伊朗,主让1,比利时胜,1-0,0元,走水</t>
-  </si>
-  <si>
-    <t>2026-06-24,世界杯,乌拉圭,佛得角,主让1,乌拉圭胜,1-0,0元,走水</t>
-  </si>
-  <si>
-    <t>2026-06-24,世界杯,挪威,塞内加尔,主让0.5,挪威胜,2-1,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-06-27,世界杯,英格兰,刚果(金),主让1.5,英格兰胜,2-1,-50元,赢球输盘</t>
-  </si>
-  <si>
-    <t>2026-06-27,世界杯,比利时,塞内加尔,客让0.5,比利时胜,2-2,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-06-27,世界杯,美国,波黑,主让1,美国胜,2-0,0元,走水</t>
-  </si>
-  <si>
-    <t>2026-06-30,世界杯,巴西,日本,主让0.75,巴西胜,2-1,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-06-30,世界杯,德国,巴拉圭,主让1.25,德国胜,1-1,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-06-30,世界杯,荷兰,摩洛哥,主让0.5,平局,1-1,+50元,平局命中</t>
-  </si>
-  <si>
-    <t>2026-07-01,世界杯,科特迪瓦,挪威,客让0.5,挪威胜,1-2,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-01,世界杯,法国,瑞典,主让1.5,法国胜,3-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-01,世界杯,墨西哥,厄瓜多尔,主让0.5,墨西哥胜,1-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-02,世界杯,英格兰,刚果(金),主让1.5,英格兰胜,2-1,-50元,赢球输盘</t>
-  </si>
-  <si>
-    <t>2026-07-02,世界杯,比利时,塞内加尔,客让0.5,平局,2-2,+50元,平局命中</t>
-  </si>
-  <si>
-    <t>2026-07-02,世界杯,美国,波黑,主让1,美国胜,2-0,0元,走水</t>
-  </si>
-  <si>
-    <t>2026-07-03,世界杯,西班牙,奥地利,主让1.5,西班牙胜,3-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-03,世界杯,葡萄牙,克罗地亚,主让0.5,葡萄牙胜,2-1,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-03,世界杯,瑞士,阿尔及利亚,主让0.5,阿尔及利亚不败,0-0,+50元,下盘命中</t>
-  </si>
-  <si>
-    <t>2026-07-04,世界杯,澳大利亚,埃及,客让0.25,平局,1-1,+50元,平局命中</t>
-  </si>
-  <si>
-    <t>2026-07-04,世界杯,阿根廷,佛得角,主让2,阿根廷胜,1-1,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-04,世界杯,哥伦比亚,加纳,主让1.25,哥伦比亚胜,1-0,-25元,赢球输半</t>
-  </si>
-  <si>
-    <t>2026-07-05,世界杯,加拿大,摩洛哥,客让0.75,摩洛哥胜,0-3,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-05,世界杯,巴拉圭,法国,客让2,法国胜,0-1,-50元,赢球输盘</t>
-  </si>
-  <si>
-    <t>2026-07-06,世界杯,巴西,挪威,主让0.75,巴西胜,1-2,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-06,世界杯,墨西哥,英格兰,客让0.25,英格兰胜,2-3,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-07,世界杯,葡萄牙,西班牙,客让0.5,西班牙不败,0-1,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-07,世界杯,美国,比利时,平手,比利时胜,1-4,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-08,世界杯,阿根廷,埃及,主让1.5,阿根廷胜,3-2,-50元,赢球输盘</t>
-  </si>
-  <si>
-    <t>2026-07-08,世界杯,瑞士,哥伦比亚,客让0.25,平局,0-0,+50元,平局命中</t>
-  </si>
-  <si>
-    <t>2026-07-10,世界杯,法国,摩洛哥,主让1,法国胜,2-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-11,世界杯,西班牙,比利时,主让0.75,西班牙胜,2-1,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-12,世界杯,挪威,英格兰,客让0.5,英格兰胜,1-1,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-12,世界杯,阿根廷,瑞士,主让0.75,阿根廷胜,1-1,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-13,世界杯,法国,西班牙,主让0.25,法国胜,0-2,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-13,世界杯,英格兰,阿根廷,平手,英格兰不败,1-2,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-19,世界杯,法国,英格兰,主让0.5,法国胜,4-6,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-01,韩K联,FC首尔,仁川联,主让0.5,FC首尔胜,1-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-01,韩K联,金泉尚武,济州SK,主让0.25,平局,1-1,+50元,平局命中</t>
-  </si>
-  <si>
-    <t>2026-07-01,韩K联,光州FC,蔚山HD,客让0.5,蔚山HD胜,1-1,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-11,韩K联,仁川联,FC安养,主让0.25,FC安养不败,0-1,+50元,受让命中</t>
-  </si>
-  <si>
-    <t>2026-07-11,韩K联,济州SK,大田市民,平手,大田市民不败,0-0,0元,走水</t>
-  </si>
-  <si>
-    <t>2026-07-11,韩K联,FC首尔,江原FC,主让0.25,小球,0-0,+50元,小球命中</t>
-  </si>
-  <si>
-    <t>2026-07-18,韩K联,大田市民,蔚山HD,平手,蔚山HD不败,2-2,0元,走水</t>
-  </si>
-  <si>
-    <t>2026-07-18,韩K联,江原FC,金泉尚武,主让0.75,江原FC胜,2-0,+50元,穿盘命中</t>
-  </si>
-  <si>
-    <t>2026-07-18,韩K联,济州SK,浦项制铁,客让0.25,济州SK不败,2-1,+50元,受让命中</t>
-  </si>
-  <si>
-    <t>2026-07-18,韩K联,仁川联,全北现代,客让0.25,小球,1-0,+50元,小球命中</t>
-  </si>
-  <si>
-    <t>2026-07-19,韩K联,富川FC,FC首尔,客让0.75,FC首尔胜,1-3,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-19,韩K联,FC安养,光州FC,主让0.75,FC安养胜,1-1,-25元,赢球输半</t>
-  </si>
-  <si>
-    <t>2026-07-21,韩K联,济州SK,江原FC,客让0.25,江原FC不败,1-1,0元,走水</t>
-  </si>
-  <si>
-    <t>2026-07-21,韩K联,全北现代,大田市民,主让0.5,全北现代胜,0-0,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-21,韩K联,蔚山HD,仁川联,主让0.25,蔚山HD不败,1-2,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-22,韩K联,FC首尔,浦项制铁,主让0.5,FC首尔胜,3-1,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-22,韩K联,光州FC,金泉尚武,客让0.25,金泉尚武不败,1-1,0元,走水</t>
-  </si>
-  <si>
-    <t>2026-07-25,韩K联,金泉尚武,大田市民,主让0.25,金泉尚武+0.25,3-2,+30元,受让低水命中</t>
-  </si>
-  <si>
-    <t>2026-07-25,韩K联,浦项制铁,全北现代,客让0.25,浦项制铁+0.25,0-2,-20元,受让方向失误</t>
-  </si>
-  <si>
-    <t>2026-07-26,韩K联,FC安养,江原FC,客让0.25,江原FC不败,2-1,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-26,韩K联,光州FC,济州SK,客让0.5,济州SK胜,1-2,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-26,韩K联,仁川联,富川FC,主让0.75,仁川联胜,1-1,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-26,韩K联,FC首尔,蔚山HD,主让0.5,FC首尔胜,1-3,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-08-01,韩K联,蔚山HD,FC安养,主让0.5,FC安养+0.5,3-1,-40元,豪门主场反弹被低估</t>
-  </si>
-  <si>
-    <t>2026-08-01,韩K联,济州SK,仁川联,客让0.25,放弃,3-3,0元,放弃正确</t>
-  </si>
-  <si>
-    <t>2026-08-01,韩K联,大田市民,光州FC,主让1,光州FC+1,2-0,-20元,深盘诱导误判</t>
-  </si>
-  <si>
-    <t>2026-08-02,韩K联,蔚山HD,FC安养,主让0.5,FC安养+0.5,3-1,-40元,豪门主场反弹</t>
-  </si>
-  <si>
-    <t>2026-08-02,韩K联,大田市民,光州FC,主让1,光州FC+1,2-0,-20元,深盘诱导误判</t>
-  </si>
-  <si>
-    <t>2026-07-29,韩国杯,仁川联,金浦市民,主让1,放弃,0-1,0元,深盘放弃正确</t>
-  </si>
-  <si>
-    <t>2026-07-29,韩国杯,蔚山HD,蔚山市民,主让2,放弃,0-1,0元,深盘放弃正确</t>
-  </si>
-  <si>
-    <t>2026-07-29,韩国杯,釜山偶像,FC首尔,客让0.75,釜山偶像+0.75,2-0,+40元,主队方向+20%</t>
-  </si>
-  <si>
-    <t>2026-07-29,韩国杯,光州FC,天安城,主让0.5,光州FC胜,1-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-29,韩国杯,忠南牙山,始兴市民,受让0.5,放弃,2-1,0元,放弃正确</t>
-  </si>
-  <si>
-    <t>2026-07-22,欧冠,奥莫尼亚,凯拉特,主让0.75,奥莫尼亚胜,1-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-22,欧冠,索菲亚列夫斯基,克拉约瓦大学,主让0.5,索菲亚列夫斯基胜,1-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-23,欧冠,埃格纳蒂亚,采列,主让0.5,放弃,3-3,0元,放弃正确</t>
-  </si>
-  <si>
-    <t>2026-07-23,欧冠,图恩,萨格勒布迪纳摩,客让0.5,萨格勒布迪纳摩胜,1-1,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-28,欧冠,古比斯,萨巴赫,平手,萨巴赫不败,0-2,+50元,超低水命中</t>
-  </si>
-  <si>
-    <t>2026-07-28,欧冠,林肯红魔,米亚尔比,客让1.25,林肯红魔+1.25,0-0,+50元,受让命中</t>
-  </si>
-  <si>
-    <t>2026-07-28,欧冠,萨格勒布迪纳摩,图恩,主让1.25,萨格勒布迪纳摩胜,2-2,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-29,欧冠,波兹南,奥胡斯,主让1.25,波兹南胜,0-3,-50元,次回合崩盘</t>
-  </si>
-  <si>
-    <t>2026-07-29,欧冠,费内巴切,扎布热矿工,客让1,费内巴切-1,1-1,-40元,首回合领先战意存疑</t>
-  </si>
-  <si>
-    <t>2026-07-30,欧罗巴,费伦茨瓦罗斯,特温特,主让0.25,费伦茨-0.25,2-2,-60元,首回合领先战意存疑</t>
-  </si>
-  <si>
-    <t>2026-07-30,欧罗巴,安德莱赫特,哈马比,主让0.25,哈马比+0.25,3-1,-40元,欧战底蕴被低估</t>
-  </si>
-  <si>
-    <t>2026-07-30,欧罗巴,杜堡尔,帕纳瓦兹,主让1.5,杜堡尔-1.5,1-1,-30元,欧协联低适配性</t>
-  </si>
-  <si>
-    <t>2026-07-30,欧罗巴,艾斯卡迪斯,瓦杜兹,客让1,瓦杜兹-1,2-0,+30元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-30,欧罗巴,诺亚FC,野牛,主让1.5,诺亚FC胜,2-1,+15元,主场优势</t>
-  </si>
-  <si>
-    <t>2026-07-12,瑞典超,马尔默,哥德堡,主让0.5,马尔默胜,4-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-12,瑞典超,哈马比,卡尔马,主让1.5,哈马比胜,2-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-12,瑞典超,瓦斯特拉斯,代格福什,主让0.25,瓦斯特拉斯不败,2-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-13,瑞典超,佐加顿斯,哈尔姆斯塔德,主让2,佐加顿斯胜,3-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-17,瑞典超,哥德堡,布洛马波卡纳,主让0.25,哥德堡不败,1-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-17,瑞典超,米亚尔比,韦斯特罗斯,主让0.75,韦斯特罗斯+0.75,1-2,+50元,受让命中</t>
-  </si>
-  <si>
-    <t>2026-07-18,瑞典超,索尔纳,哥德堡盖斯,客让0.25,索尔纳不败,2-0,+50元,受让命中</t>
-  </si>
-  <si>
-    <t>2026-07-18,瑞典超,利勒斯特罗姆,KFUM奥斯陆,主让1,利勒斯特罗姆-1,2-1,0元,走水</t>
-  </si>
-  <si>
-    <t>2026-07-25,瑞典超,代格福什,尤尔加登,客让0.75,尤尔加登-0.75,0-1,+25元,赢半</t>
-  </si>
-  <si>
-    <t>2026-07-25,瑞典超,哥德堡盖斯,哈尔姆斯塔德,主让1.25,放弃,1-1,0元,放弃正确</t>
-  </si>
-  <si>
-    <t>2026-07-25,瑞典超,马尔默,埃尔夫斯堡,主让0.5,马尔默-0.5,1-2,-30元,爆冷</t>
-  </si>
-  <si>
-    <t>2026-07-26,瑞典超,哥德堡盖斯,哈尔姆斯塔德,主让1.25,放弃,1-1,0元,放弃正确</t>
-  </si>
-  <si>
-    <t>2026-07-26,瑞典超,马尔默,埃尔夫斯堡,主让0.5,马尔默-0.5,1-2,-30元,爆冷</t>
-  </si>
-  <si>
-    <t>2026-08-01,瑞典超,赫根,卡尔马,主让0.75,赫根-0.75,1-1,-60元,客场连败反弹</t>
-  </si>
-  <si>
-    <t>2026-08-02,瑞典超,布洛马波卡纳,马尔默,客让0.25,马尔默不败,1-2,+20元,历史交锋碾压</t>
-  </si>
-  <si>
-    <t>2026-08-02,瑞典超,哥德堡,代格福什,主让0.75,小球,2-0,-5元,小球命中</t>
-  </si>
-  <si>
-    <t>2026-08-02,瑞典超,索尔纳,奥尔格里特,主让1.25,索尔纳胜,0-3,-70元,10人伤停崩塌</t>
-  </si>
-  <si>
-    <t>2026-07-12,挪超,KFUM奥斯陆,博德闪耀,客让1,博德闪耀胜,0-2,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-12,挪超,布兰,斯达,主让1.5,布兰胜,2-1,-50元,赢球输盘</t>
-  </si>
-  <si>
-    <t>2026-07-12,挪超,罗森博格,克里斯蒂安松,主让1,克里斯蒂安松+1,3-0,-50元,深盘诱导误判</t>
-  </si>
-  <si>
-    <t>2026-07-12,挪超,桑纳菲尤尔,汉坎,主让0.5,汉坎不败,2-2,+50元,受让命中</t>
-  </si>
-  <si>
-    <t>2026-07-12,挪超,萨普斯堡08,维京,客让0.75,维京胜,1-0,-50元,冷门</t>
-  </si>
-  <si>
-    <t>2026-07-17,挪超,博德闪耀,腓特烈斯塔,主让2.5,放弃,2-0,0元,放弃正确</t>
-  </si>
-  <si>
-    <t>2026-07-18,挪超,罗森博格,腓特烈斯塔,主让0.75,罗森博格胜,4-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-26,挪超,莫尔德,KFUM奥斯陆,客让0.5,莫尔德胜,2-4,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-26,挪超,萨普斯堡,汉坎,主让0.75,萨普斯堡胜,1-0,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-08-02,挪超,莫尔德,萨普斯堡,主让1,萨普斯堡+1,3-3,0元,受让走水</t>
-  </si>
-  <si>
-    <t>2026-08-02,挪超,布兰,罗森博格,主让0.5,罗森博格不败,待确认,待确认,待确认</t>
-  </si>
-  <si>
-    <t>2026-07-11,芬超,拉赫蒂,赫尔辛基,客让0.25,拉赫蒂不败,2-0,+50元,受让命中</t>
-  </si>
-  <si>
-    <t>2026-07-11,芬超,TPS图尔库,AC奥卢,平手,平局,3-0,-50元,方向失误</t>
-  </si>
-  <si>
-    <t>2026-07-11,芬超,格尼斯坦,玛丽港,主让1.5,格尼斯坦胜,4-2,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-12,芬超,赫尔辛基,VPS瓦萨,主让0.5,赫尔辛基胜,2-1,+50元,实力碾压</t>
-  </si>
-  <si>
-    <t>2026-07-18,芬超,玛丽港,奥卢,客让1.25,放弃,1-1,0元,放弃正确</t>
-  </si>
-  <si>
-    <t>2026-07-18,芬超,古比斯,VPS瓦萨,主让0.5,VPS瓦萨+0.5,3-1,-30元,双线作战影响被高估</t>
-  </si>
-  <si>
-    <t>2026-07-18,芬超,克里斯蒂安松,斯达,主让0.25,克里斯蒂安松-0.25,1-2,-30元,榜尾保级战意被低估</t>
-  </si>
-  <si>
-    <t>2026-07-19,芬超,奥卢,格尼斯坦,主让0.25,格尼斯坦+0.25,0-2,+50元,超低水命中</t>
-  </si>
-  <si>
-    <t>2026-07-19,芬超,塞伊奈约基,古比斯,平手,塞伊奈约基平手,0-2,-60元,平手盘误判</t>
-  </si>
-  <si>
-    <t>2026-08-01,芬超,拉赫蒂,雅罗,主让1,拉赫蒂胜,2-0,+30元,主场龙</t>
-  </si>
-  <si>
-    <t>2026-08-01,芬超,VPS瓦萨,图尔库国际,平手,瓦萨不败,0-1,-30元,主场不败被高估</t>
-  </si>
-  <si>
-    <t>2026-08-01,芬超,奥卢,埃尔维斯,主让0.25,奥卢不败,1-0,+15元,主场防守稳固</t>
-  </si>
-  <si>
-    <t>2026-08-03,瑞典超,索尔纳,奥尔格里特,主让1.25,索尔纳胜,0-3,-70元,10人伤停导致防线崩塌</t>
-  </si>
-  <si>
-    <t>2026-08-03,瑞典超,布洛马波卡纳,马尔默,客让0.25,马尔默不败,1-2,+20元,历史交锋碾压+水位下降</t>
-  </si>
-  <si>
-    <t>2026-08-03,瑞典超,哥德堡,代格福什,主让0.75,小球&lt;2.5/3,2-0,-5.4元,小球命中但水位低</t>
-  </si>
-  <si>
-    <t>2026-08-03,芬超,VPS瓦萨,图尔库国际,平手,瓦萨不败,0-1,-30元,主场不败金身被高估</t>
-  </si>
-  <si>
-    <t>2026-08-03,芬超,奥卢,埃尔维斯,主让0.25,奥卢不败,1-0,+15元,主场防守稳固+对手双线疲惫</t>
-  </si>
-  <si>
-    <t>2026-08-03,挪超,莫尔德,萨普斯堡,主让1,萨普斯堡+1,3-3,0元,受让方走水</t>
-  </si>
-  <si>
-    <t>2026-08-02,韩K联,蔚山HD,FC安养,主让0.5,FC安养+0.5,3-1,-40元,豪门主场反弹战意被低估</t>
-  </si>
-  <si>
-    <t>2026-08-02,韩K联,大田市民,光州FC,主让1,光州FC+1,2-0,-20元,误判深盘诱导</t>
-  </si>
-  <si>
-    <t>2026-08-02,韩K联,济州SK,仁川联,客让0.25,放弃,3-3,0元,放弃正确</t>
-  </si>
-  <si>
-    <t>2026-08-02,韩K联,VPS瓦萨,图尔库国际,平手,瓦萨不败,0-1,0元,待确认</t>
-  </si>
-  <si>
-    <t>2026-08-01,韩K联,金泉尚武,大田市民,主让0.25,金泉尚武+0.25,3-2,+30元,受让低水命中</t>
-  </si>
-  <si>
-    <t>2026-08-01,韩K联,浦项制铁,全北现代,客让0.25,浦项制铁+0.25,0-2,-20元,受让方向判断失误</t>
-  </si>
-  <si>
-    <t>2026-07-31,欧罗巴,费伦茨瓦罗斯,特温特,主让0.25,费伦茨-0.25,2-2,-60元,首回合领先次回合战意存疑</t>
-  </si>
-  <si>
-    <t>2026-07-31,欧罗巴,安德莱赫特,哈马比,主让0.25,哈马比+0.25,3-1,-40元,欧战底蕴权重被低估</t>
-  </si>
-  <si>
-    <t>2026-07-30,欧冠,波兹南,奥胡斯,主让1.25,波兹南胜,0-3,-50元,首回合4-1后次回合崩盘</t>
-  </si>
-  <si>
-    <t>2026-07-30,欧冠,费内巴切,扎布热矿工,客让1,费内巴切-1,1-1,-40元,首回合领先战意存疑</t>
-  </si>
-  <si>
-    <t>2026-07-29,韩国杯,釜山偶像,FC首尔,客让0.75,釜山偶像+0.75,2-0,+40元,主队方向+20%权重</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="396">
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>联赛</t>
+  </si>
+  <si>
+    <t>主队</t>
+  </si>
+  <si>
+    <t>客队</t>
+  </si>
+  <si>
+    <t>盘口</t>
+  </si>
+  <si>
+    <t>预测方向</t>
+  </si>
+  <si>
+    <t>实际比分</t>
+  </si>
+  <si>
+    <t>盈亏</t>
+  </si>
+  <si>
+    <t>归因</t>
+  </si>
+  <si>
+    <t>世界杯</t>
+  </si>
+  <si>
+    <t>荷兰</t>
+  </si>
+  <si>
+    <t>瑞典</t>
+  </si>
+  <si>
+    <t>主让1.5</t>
+  </si>
+  <si>
+    <t>荷兰胜</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>+50元</t>
+  </si>
+  <si>
+    <t>实力碾压</t>
+  </si>
+  <si>
+    <t>德国</t>
+  </si>
+  <si>
+    <t>科特迪瓦</t>
+  </si>
+  <si>
+    <t>主让1.25</t>
+  </si>
+  <si>
+    <t>德国胜</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>+25元</t>
+  </si>
+  <si>
+    <t>赢半</t>
+  </si>
+  <si>
+    <t>厄瓜多尔</t>
+  </si>
+  <si>
+    <t>库拉索</t>
+  </si>
+  <si>
+    <t>主让1.75</t>
+  </si>
+  <si>
+    <t>厄瓜多尔胜</t>
+  </si>
+  <si>
+    <t>0-0</t>
+  </si>
+  <si>
+    <t>-50元</t>
+  </si>
+  <si>
+    <t>冷门</t>
+  </si>
+  <si>
+    <t>突尼斯</t>
+  </si>
+  <si>
+    <t>日本</t>
+  </si>
+  <si>
+    <t>客让0.75</t>
+  </si>
+  <si>
+    <t>日本胜</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>葡萄牙</t>
+  </si>
+  <si>
+    <t>乌兹别克斯坦</t>
+  </si>
+  <si>
+    <t>葡萄牙胜</t>
+  </si>
+  <si>
+    <t>5-0</t>
+  </si>
+  <si>
+    <t>英格兰</t>
+  </si>
+  <si>
+    <t>加纳</t>
+  </si>
+  <si>
+    <t>主让2</t>
+  </si>
+  <si>
+    <t>英格兰胜</t>
+  </si>
+  <si>
+    <t>巴拿马</t>
+  </si>
+  <si>
+    <t>克罗地亚</t>
+  </si>
+  <si>
+    <t>客让1</t>
+  </si>
+  <si>
+    <t>克罗地亚胜</t>
+  </si>
+  <si>
+    <t>0-1</t>
+  </si>
+  <si>
+    <t>哥伦比亚</t>
+  </si>
+  <si>
+    <t>刚果(金)</t>
+  </si>
+  <si>
+    <t>主让0.75</t>
+  </si>
+  <si>
+    <t>哥伦比亚胜</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>西班牙</t>
+  </si>
+  <si>
+    <t>沙特</t>
+  </si>
+  <si>
+    <t>西班牙胜</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>0元</t>
+  </si>
+  <si>
+    <t>走水</t>
+  </si>
+  <si>
+    <t>比利时</t>
+  </si>
+  <si>
+    <t>伊朗</t>
+  </si>
+  <si>
+    <t>主让1</t>
+  </si>
+  <si>
+    <t>比利时胜</t>
+  </si>
+  <si>
+    <t>1-0</t>
+  </si>
+  <si>
+    <t>乌拉圭</t>
+  </si>
+  <si>
+    <t>佛得角</t>
+  </si>
+  <si>
+    <t>乌拉圭胜</t>
+  </si>
+  <si>
+    <t>挪威</t>
+  </si>
+  <si>
+    <t>塞内加尔</t>
+  </si>
+  <si>
+    <t>主让0.5</t>
+  </si>
+  <si>
+    <t>挪威胜</t>
+  </si>
+  <si>
+    <t>赢球输盘</t>
+  </si>
+  <si>
+    <t>客让0.5</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>美国</t>
+  </si>
+  <si>
+    <t>波黑</t>
+  </si>
+  <si>
+    <t>美国胜</t>
+  </si>
+  <si>
+    <t>巴西</t>
+  </si>
+  <si>
+    <t>巴西胜</t>
+  </si>
+  <si>
+    <t>巴拉圭</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>摩洛哥</t>
+  </si>
+  <si>
+    <t>平局</t>
+  </si>
+  <si>
+    <t>平局命中</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>法国</t>
+  </si>
+  <si>
+    <t>法国胜</t>
+  </si>
+  <si>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>墨西哥</t>
+  </si>
+  <si>
+    <t>墨西哥胜</t>
+  </si>
+  <si>
+    <t>韩K联</t>
+  </si>
+  <si>
+    <t>FC首尔</t>
+  </si>
+  <si>
+    <t>仁川联</t>
+  </si>
+  <si>
+    <t>FC首尔胜</t>
+  </si>
+  <si>
+    <t>金泉尚武</t>
+  </si>
+  <si>
+    <t>济州SK</t>
+  </si>
+  <si>
+    <t>主让0.25</t>
+  </si>
+  <si>
+    <t>光州FC</t>
+  </si>
+  <si>
+    <t>蔚山HD</t>
+  </si>
+  <si>
+    <t>蔚山HD胜</t>
+  </si>
+  <si>
+    <t>奥地利</t>
+  </si>
+  <si>
+    <t>瑞士</t>
+  </si>
+  <si>
+    <t>阿尔及利亚</t>
+  </si>
+  <si>
+    <t>阿尔及利亚不败</t>
+  </si>
+  <si>
+    <t>下盘命中</t>
+  </si>
+  <si>
+    <t>澳大利亚</t>
+  </si>
+  <si>
+    <t>埃及</t>
+  </si>
+  <si>
+    <t>客让0.25</t>
+  </si>
+  <si>
+    <t>阿根廷</t>
+  </si>
+  <si>
+    <t>阿根廷胜</t>
+  </si>
+  <si>
+    <t>-25元</t>
+  </si>
+  <si>
+    <t>赢球输半</t>
+  </si>
+  <si>
+    <t>加拿大</t>
+  </si>
+  <si>
+    <t>摩洛哥胜</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>客让2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>西班牙不败</t>
+  </si>
+  <si>
+    <t>平手</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>FC安养</t>
+  </si>
+  <si>
+    <t>FC安养不败</t>
+  </si>
+  <si>
+    <t>受让命中</t>
+  </si>
+  <si>
+    <t>大田市民</t>
+  </si>
+  <si>
+    <t>大田市民不败</t>
+  </si>
+  <si>
+    <t>江原FC</t>
+  </si>
+  <si>
+    <t>小球</t>
+  </si>
+  <si>
+    <t>小球命中</t>
+  </si>
+  <si>
+    <t>芬超</t>
+  </si>
+  <si>
+    <t>拉赫蒂</t>
+  </si>
+  <si>
+    <t>赫尔辛基</t>
+  </si>
+  <si>
+    <t>拉赫蒂不败</t>
+  </si>
+  <si>
+    <t>TPS图尔库</t>
+  </si>
+  <si>
+    <t>AC奥卢</t>
+  </si>
+  <si>
+    <t>方向失误</t>
+  </si>
+  <si>
+    <t>格尼斯坦</t>
+  </si>
+  <si>
+    <t>玛丽港</t>
+  </si>
+  <si>
+    <t>格尼斯坦胜</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>瑞典超</t>
+  </si>
+  <si>
+    <t>马尔默</t>
+  </si>
+  <si>
+    <t>哥德堡</t>
+  </si>
+  <si>
+    <t>马尔默胜</t>
+  </si>
+  <si>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>哈马比</t>
+  </si>
+  <si>
+    <t>卡尔马</t>
+  </si>
+  <si>
+    <t>哈马比胜</t>
+  </si>
+  <si>
+    <t>瓦斯特拉斯</t>
+  </si>
+  <si>
+    <t>代格福什</t>
+  </si>
+  <si>
+    <t>瓦斯特拉斯不败</t>
+  </si>
+  <si>
+    <t>挪超</t>
+  </si>
+  <si>
+    <t>KFUM奥斯陆</t>
+  </si>
+  <si>
+    <t>博德闪耀</t>
+  </si>
+  <si>
+    <t>博德闪耀胜</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>布兰</t>
+  </si>
+  <si>
+    <t>斯达</t>
+  </si>
+  <si>
+    <t>布兰胜</t>
+  </si>
+  <si>
+    <t>罗森博格</t>
+  </si>
+  <si>
+    <t>克里斯蒂安松</t>
+  </si>
+  <si>
+    <t>克里斯蒂安松+1</t>
+  </si>
+  <si>
+    <t>深盘诱导误判</t>
+  </si>
+  <si>
+    <t>桑纳菲尤尔</t>
+  </si>
+  <si>
+    <t>汉坎</t>
+  </si>
+  <si>
+    <t>汉坎不败</t>
+  </si>
+  <si>
+    <t>萨普斯堡08</t>
+  </si>
+  <si>
+    <t>维京</t>
+  </si>
+  <si>
+    <t>维京胜</t>
+  </si>
+  <si>
+    <t>VPS瓦萨</t>
+  </si>
+  <si>
+    <t>赫尔辛基胜</t>
+  </si>
+  <si>
+    <t>英格兰不败</t>
+  </si>
+  <si>
+    <t>佐加顿斯</t>
+  </si>
+  <si>
+    <t>哈尔姆斯塔德</t>
+  </si>
+  <si>
+    <t>佐加顿斯胜</t>
+  </si>
+  <si>
+    <t>布洛马波卡纳</t>
+  </si>
+  <si>
+    <t>哥德堡不败</t>
+  </si>
+  <si>
+    <t>米亚尔比</t>
+  </si>
+  <si>
+    <t>韦斯特罗斯</t>
+  </si>
+  <si>
+    <t>韦斯特罗斯+0.75</t>
+  </si>
+  <si>
+    <t>腓特烈斯塔</t>
+  </si>
+  <si>
+    <t>主让2.5</t>
+  </si>
+  <si>
+    <t>放弃</t>
+  </si>
+  <si>
+    <t>放弃正确</t>
+  </si>
+  <si>
+    <t>蔚山HD不败</t>
+  </si>
+  <si>
+    <t>江原FC胜</t>
+  </si>
+  <si>
+    <t>穿盘命中</t>
+  </si>
+  <si>
+    <t>浦项制铁</t>
+  </si>
+  <si>
+    <t>济州SK不败</t>
+  </si>
+  <si>
+    <t>全北现代</t>
+  </si>
+  <si>
+    <t>索尔纳</t>
+  </si>
+  <si>
+    <t>哥德堡盖斯</t>
+  </si>
+  <si>
+    <t>索尔纳不败</t>
+  </si>
+  <si>
+    <t>利勒斯特罗姆</t>
+  </si>
+  <si>
+    <t>利勒斯特罗姆-1</t>
+  </si>
+  <si>
+    <t>罗森博格胜</t>
+  </si>
+  <si>
+    <t>奥卢</t>
+  </si>
+  <si>
+    <t>客让1.25</t>
+  </si>
+  <si>
+    <t>古比斯</t>
+  </si>
+  <si>
+    <t>VPS瓦萨+0.5</t>
+  </si>
+  <si>
+    <t>-30元</t>
+  </si>
+  <si>
+    <t>双线作战影响被高估</t>
+  </si>
+  <si>
+    <t>克里斯蒂安松-0.25</t>
+  </si>
+  <si>
+    <t>榜尾保级战意被低估</t>
+  </si>
+  <si>
+    <t>4-6</t>
+  </si>
+  <si>
+    <t>富川FC</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>FC安养胜</t>
+  </si>
+  <si>
+    <t>格尼斯坦+0.25</t>
+  </si>
+  <si>
+    <t>超低水命中</t>
+  </si>
+  <si>
+    <t>塞伊奈约基</t>
+  </si>
+  <si>
+    <t>塞伊奈约基平手</t>
+  </si>
+  <si>
+    <t>-60元</t>
+  </si>
+  <si>
+    <t>平手盘误判</t>
+  </si>
+  <si>
+    <t>江原FC不败</t>
+  </si>
+  <si>
+    <t>全北现代胜</t>
+  </si>
+  <si>
+    <t>金泉尚武不败</t>
+  </si>
+  <si>
+    <t>欧冠</t>
+  </si>
+  <si>
+    <t>奥莫尼亚</t>
+  </si>
+  <si>
+    <t>凯拉特</t>
+  </si>
+  <si>
+    <t>奥莫尼亚胜</t>
+  </si>
+  <si>
+    <t>索菲亚列夫斯基</t>
+  </si>
+  <si>
+    <t>克拉约瓦大学</t>
+  </si>
+  <si>
+    <t>索菲亚列夫斯基胜</t>
+  </si>
+  <si>
+    <t>埃格纳蒂亚</t>
+  </si>
+  <si>
+    <t>采列</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>图恩</t>
+  </si>
+  <si>
+    <t>萨格勒布迪纳摩</t>
+  </si>
+  <si>
+    <t>萨格勒布迪纳摩胜</t>
+  </si>
+  <si>
+    <t>金泉尚武+0.25</t>
+  </si>
+  <si>
+    <t>+30元</t>
+  </si>
+  <si>
+    <t>受让低水命中</t>
+  </si>
+  <si>
+    <t>浦项制铁+0.25</t>
+  </si>
+  <si>
+    <t>-20元</t>
+  </si>
+  <si>
+    <t>受让方向失误</t>
+  </si>
+  <si>
+    <t>尤尔加登</t>
+  </si>
+  <si>
+    <t>尤尔加登-0.75</t>
+  </si>
+  <si>
+    <t>埃尔夫斯堡</t>
+  </si>
+  <si>
+    <t>马尔默-0.5</t>
+  </si>
+  <si>
+    <t>爆冷</t>
+  </si>
+  <si>
+    <t>济州SK胜</t>
+  </si>
+  <si>
+    <t>仁川联胜</t>
+  </si>
+  <si>
+    <t>莫尔德</t>
+  </si>
+  <si>
+    <t>莫尔德胜</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>萨普斯堡</t>
+  </si>
+  <si>
+    <t>萨普斯堡胜</t>
+  </si>
+  <si>
+    <t>萨巴赫</t>
+  </si>
+  <si>
+    <t>萨巴赫不败</t>
+  </si>
+  <si>
+    <t>林肯红魔</t>
+  </si>
+  <si>
+    <t>林肯红魔+1.25</t>
+  </si>
+  <si>
+    <t>韩国杯</t>
+  </si>
+  <si>
+    <t>金浦市民</t>
+  </si>
+  <si>
+    <t>深盘放弃正确</t>
+  </si>
+  <si>
+    <t>蔚山市民</t>
+  </si>
+  <si>
+    <t>釜山偶像</t>
+  </si>
+  <si>
+    <t>釜山偶像+0.75</t>
+  </si>
+  <si>
+    <t>+40元</t>
+  </si>
+  <si>
+    <t>主队方向+20%</t>
+  </si>
+  <si>
+    <t>天安城</t>
+  </si>
+  <si>
+    <t>光州FC胜</t>
+  </si>
+  <si>
+    <t>忠南牙山</t>
+  </si>
+  <si>
+    <t>始兴市民</t>
+  </si>
+  <si>
+    <t>受让0.5</t>
+  </si>
+  <si>
+    <t>波兹南</t>
+  </si>
+  <si>
+    <t>奥胡斯</t>
+  </si>
+  <si>
+    <t>波兹南胜</t>
+  </si>
+  <si>
+    <t>次回合崩盘</t>
+  </si>
+  <si>
+    <t>费内巴切</t>
+  </si>
+  <si>
+    <t>扎布热矿工</t>
+  </si>
+  <si>
+    <t>费内巴切-1</t>
+  </si>
+  <si>
+    <t>-40元</t>
+  </si>
+  <si>
+    <t>首回合领先战意存疑</t>
+  </si>
+  <si>
+    <t>主队方向+20%权重</t>
+  </si>
+  <si>
+    <t>欧罗巴</t>
+  </si>
+  <si>
+    <t>费伦茨瓦罗斯</t>
+  </si>
+  <si>
+    <t>特温特</t>
+  </si>
+  <si>
+    <t>费伦茨-0.25</t>
+  </si>
+  <si>
+    <t>安德莱赫特</t>
+  </si>
+  <si>
+    <t>哈马比+0.25</t>
+  </si>
+  <si>
+    <t>欧战底蕴被低估</t>
+  </si>
+  <si>
+    <t>杜堡尔</t>
+  </si>
+  <si>
+    <t>帕纳瓦兹</t>
+  </si>
+  <si>
+    <t>杜堡尔-1.5</t>
+  </si>
+  <si>
+    <t>欧协联低适配性</t>
+  </si>
+  <si>
+    <t>艾斯卡迪斯</t>
+  </si>
+  <si>
+    <t>瓦杜兹</t>
+  </si>
+  <si>
+    <t>瓦杜兹-1</t>
+  </si>
+  <si>
+    <t>诺亚FC</t>
+  </si>
+  <si>
+    <t>野牛</t>
+  </si>
+  <si>
+    <t>诺亚FC胜</t>
+  </si>
+  <si>
+    <t>+15元</t>
+  </si>
+  <si>
+    <t>主场优势</t>
+  </si>
+  <si>
+    <t>首回合4-1后次回合崩盘</t>
+  </si>
+  <si>
+    <t>首回合领先次回合战意存疑</t>
+  </si>
+  <si>
+    <t>欧战底蕴权重被低估</t>
+  </si>
+  <si>
+    <t>FC安养+0.5</t>
+  </si>
+  <si>
+    <t>豪门主场反弹被低估</t>
+  </si>
+  <si>
+    <t>光州FC+1</t>
+  </si>
+  <si>
+    <t>赫根</t>
+  </si>
+  <si>
+    <t>赫根-0.75</t>
+  </si>
+  <si>
+    <t>客场连败反弹</t>
+  </si>
+  <si>
+    <t>雅罗</t>
+  </si>
+  <si>
+    <t>拉赫蒂胜</t>
+  </si>
+  <si>
+    <t>主场龙</t>
+  </si>
+  <si>
+    <t>图尔库国际</t>
+  </si>
+  <si>
+    <t>瓦萨不败</t>
+  </si>
+  <si>
+    <t>主场不败被高估</t>
+  </si>
+  <si>
+    <t>埃尔维斯</t>
+  </si>
+  <si>
+    <t>奥卢不败</t>
+  </si>
+  <si>
+    <t>主场防守稳固</t>
+  </si>
+  <si>
+    <t>受让方向判断失误</t>
+  </si>
+  <si>
+    <t>豪门主场反弹</t>
+  </si>
+  <si>
+    <t>马尔默不败</t>
+  </si>
+  <si>
+    <t>+20元</t>
+  </si>
+  <si>
+    <t>历史交锋碾压</t>
+  </si>
+  <si>
+    <t>-5元</t>
+  </si>
+  <si>
+    <t>奥尔格里特</t>
+  </si>
+  <si>
+    <t>索尔纳胜</t>
+  </si>
+  <si>
+    <t>-70元</t>
+  </si>
+  <si>
+    <t>10人伤停崩塌</t>
+  </si>
+  <si>
+    <t>萨普斯堡+1</t>
+  </si>
+  <si>
+    <t>受让走水</t>
+  </si>
+  <si>
+    <t>罗森博格不败</t>
+  </si>
+  <si>
+    <t>待确认</t>
+  </si>
+  <si>
+    <t>豪门主场反弹战意被低估</t>
+  </si>
+  <si>
+    <t>误判深盘诱导</t>
+  </si>
+  <si>
+    <t>10人伤停导致防线崩塌</t>
+  </si>
+  <si>
+    <t>历史交锋碾压+水位下降</t>
+  </si>
+  <si>
+    <t>小球&lt;2.5/3</t>
+  </si>
+  <si>
+    <t>-5.4元</t>
+  </si>
+  <si>
+    <t>小球命中但水位低</t>
+  </si>
+  <si>
+    <t>主场不败金身被高估</t>
+  </si>
+  <si>
+    <t>主场防守稳固+对手双线疲惫</t>
+  </si>
+  <si>
+    <t>受让方走水</t>
+  </si>
+  <si>
+    <t>受让平半</t>
+  </si>
+  <si>
+    <t>天狼星</t>
+  </si>
+  <si>
+    <t>受让半球</t>
+  </si>
+  <si>
+    <t>赢小球</t>
+  </si>
+  <si>
+    <t>让球半</t>
+  </si>
+  <si>
+    <t>6-0</t>
+  </si>
+  <si>
+    <t>方向错误</t>
+  </si>
+  <si>
+    <t>欧冠杯</t>
+  </si>
+  <si>
+    <t>布拉迪斯拉发</t>
+  </si>
+  <si>
+    <t>客队不败+小球</t>
+  </si>
+  <si>
+    <t>平局命中，模型正确预判了跨联赛盲盒局的平局可能性</t>
+  </si>
+  <si>
+    <t>圣吉罗斯(中)</t>
+  </si>
+  <si>
+    <t>主让0/0.5</t>
+  </si>
+  <si>
+    <t>客队不败+大球</t>
+  </si>
+  <si>
+    <t>布拉格斯巴达</t>
+  </si>
+  <si>
+    <t>里昂</t>
+  </si>
+  <si>
+    <t>客让0/0.5</t>
+  </si>
+  <si>
+    <t>客胜+小球</t>
+  </si>
+  <si>
+    <t>判断错误</t>
+  </si>
+  <si>
+    <t>沙姆洛克流浪</t>
+  </si>
+  <si>
+    <t>主让0.5/1</t>
+  </si>
+  <si>
+    <t>主胜+大球</t>
+  </si>
+  <si>
+    <t>巴西杯</t>
+  </si>
+  <si>
+    <t>巴拉纳竞技</t>
+  </si>
+  <si>
+    <t>维多利亚</t>
+  </si>
+  <si>
+    <t>主胜</t>
+  </si>
+  <si>
+    <t>阿甲</t>
+  </si>
+  <si>
+    <t>飓风队</t>
+  </si>
+  <si>
+    <t>图库曼竞技</t>
+  </si>
+  <si>
+    <t>未分析</t>
+  </si>
+  <si>
+    <t>未参与</t>
+  </si>
+  <si>
+    <t>东南锦</t>
+  </si>
+  <si>
+    <t>缅甸</t>
+  </si>
+  <si>
+    <t>老挝</t>
+  </si>
+  <si>
+    <t>7-2</t>
+  </si>
+  <si>
+    <t>菲律宾</t>
+  </si>
+  <si>
+    <t>泰国</t>
+  </si>
+  <si>
+    <t>客让1/1.5</t>
+  </si>
+  <si>
+    <t>冷门，强队让1.5球未能赢球，属于概率性爆冷，暂不触发L3权重修正</t>
+  </si>
+  <si>
+    <t>阿拉特亚美尼</t>
+  </si>
+  <si>
+    <t>列克</t>
+  </si>
+  <si>
+    <t>欧协联</t>
+  </si>
+  <si>
+    <t>奥达里加</t>
+  </si>
+  <si>
+    <t>地拉拿迪纳摩</t>
+  </si>
+  <si>
+    <t>贝尔谢巴夏普尔</t>
+  </si>
+  <si>
+    <t>贝格莱德红星</t>
+  </si>
+  <si>
+    <t>索非亚列夫斯基</t>
+  </si>
+  <si>
+    <t>阿拉木图凯拉特</t>
+  </si>
+  <si>
+    <t>奥林匹亚科斯</t>
+  </si>
+  <si>
+    <t>奈梅亨</t>
+  </si>
+  <si>
+    <t>主让1/1.5</t>
+  </si>
+  <si>
+    <t>主胜（不穿盘）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冷门，深盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高水陷阱，已进入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>L2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>专项观察（第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次错误）</t>
+    </r>
+  </si>
+  <si>
+    <t>考诺萨基列斯</t>
+  </si>
+  <si>
+    <t>放弃正确，深盘规则虽放弃了这场，但实际打出穿盘，已在初筛日报中标记为L1“误判”</t>
+  </si>
+  <si>
+    <t>拉恩</t>
+  </si>
+  <si>
+    <t>伊比利亚1999</t>
+  </si>
+  <si>
+    <t>尤文图德</t>
+  </si>
+  <si>
+    <t>米内罗竞技</t>
   </si>
 </sst>
 </file>
@@ -489,13 +1292,25 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -641,13 +1456,25 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -962,139 +1789,160 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1621,775 +2469,4982 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A153"/>
+  <dimension ref="A1:I171"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="14.875" style="1"/>
+    <col min="2" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="10.375" style="1"/>
+    <col min="8" max="8" width="9" style="2"/>
+    <col min="9" max="9" width="47.75" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+    <row r="2" spans="1:9">
+      <c r="A2" s="3">
+        <v>46188</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
+      <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
+    <row r="3" spans="1:9">
+      <c r="A3" s="3">
+        <v>46188</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
+      <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
+      <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
+      <c r="G3" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+      <c r="H3" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
+      <c r="I3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
+    <row r="4" spans="1:9">
+      <c r="A4" s="3">
+        <v>46188</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
+      <c r="E4" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
+      <c r="F4" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
+      <c r="G4" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
+      <c r="H4" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
+      <c r="I4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
+    <row r="5" spans="1:9">
+      <c r="A5" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
+      <c r="D5" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
+      <c r="E5" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
+      <c r="F5" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
+      <c r="G5" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
+      <c r="H5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3">
+        <v>46193</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
+      <c r="D6" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
+      <c r="G6" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="3">
+        <v>46193</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
+      <c r="D7" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
+      <c r="E7" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
+      <c r="F7" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="3">
+        <v>46193</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
+      <c r="D8" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
+      <c r="E8" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
+      <c r="F8" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
+      <c r="G8" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3">
+        <v>46193</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
+      <c r="D9" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
+      <c r="E9" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
+      <c r="F9" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
+      <c r="G9" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
+      <c r="D10" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
+      <c r="E10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
+      <c r="G10" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
+      <c r="H10" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
+      <c r="I10" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
+    <row r="11" spans="1:9">
+      <c r="A11" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
+      <c r="D11" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
+      <c r="E11" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
+      <c r="F11" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
+      <c r="G11" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
+      <c r="H11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
+      <c r="D12" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
+      <c r="E12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
+      <c r="G12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
+      <c r="D13" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
+      <c r="E13" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
+      <c r="F13" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
+      <c r="G13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="3">
+        <v>46200</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
+    <row r="15" spans="1:9">
+      <c r="A15" s="3">
+        <v>46200</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
+      <c r="F15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
+      <c r="H15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="3">
+        <v>46200</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
+      <c r="D16" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
+      <c r="E16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
+      <c r="G16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
+      <c r="D17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
+      <c r="G17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
+      <c r="E18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
+      <c r="H18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
+      <c r="E19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
+      <c r="G19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
+    <row r="20" spans="1:9">
+      <c r="A20" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
+      <c r="D21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
+      <c r="G21" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
+      <c r="H21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
+      <c r="D22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
+      <c r="G22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
+      <c r="C23" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
+      <c r="D23" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
+      <c r="E23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
+      <c r="G23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
+      <c r="D24" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
+      <c r="E24" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
+      <c r="F24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
+      <c r="D25" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
+      <c r="E25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
+      <c r="G25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="3">
+        <v>46205</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="3">
+        <v>46205</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="3">
+        <v>46205</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" t="s">
+      <c r="E29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
+      <c r="D31" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
+      <c r="E31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
+      <c r="G31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
+    <row r="32" spans="1:9">
+      <c r="A32" s="3">
+        <v>46207</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" t="s">
+      <c r="D32" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
+      <c r="E32" s="1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" t="s">
+      <c r="F32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="3">
+        <v>46207</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" t="s">
+      <c r="D33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
+      <c r="G33" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="3">
+        <v>46207</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" t="s">
+      <c r="I34" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
+    <row r="35" spans="1:9">
+      <c r="A35" s="3">
+        <v>46208</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" t="s">
+      <c r="D35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" t="s">
+      <c r="G35" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" t="s">
+      <c r="H35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="3">
+        <v>46208</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
+      <c r="F36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="3">
+        <v>46209</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="3">
+        <v>46209</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" t="s">
+      <c r="H38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="3">
+        <v>46210</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" t="s">
+      <c r="G39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="3">
+        <v>46210</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
+      <c r="F40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" t="s">
+      <c r="H40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="3">
+        <v>46211</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" t="s">
+      <c r="H41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="3">
+        <v>46211</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="3">
+        <v>46214</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="3">
+        <v>46214</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
+      <c r="E45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" t="s">
+      <c r="G45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
-      <c r="A126" t="s">
+    <row r="46" spans="1:9">
+      <c r="A46" s="3">
+        <v>46214</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" t="s">
+      <c r="E46" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
+      <c r="G46" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="3">
+        <v>46214</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" t="s">
+      <c r="E47" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" t="s">
+      <c r="G47" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
-      <c r="A131" t="s">
+    <row r="48" spans="1:9">
+      <c r="A48" s="3">
+        <v>46214</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
+      <c r="C48" s="1" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
+      <c r="D48" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" t="s">
+      <c r="E48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" t="s">
+      <c r="G48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="3">
+        <v>46214</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" t="s">
+      <c r="D49" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" t="s">
+      <c r="E49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
-      <c r="A139" t="s">
+    <row r="50" spans="1:9">
+      <c r="A50" s="3">
+        <v>46214</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" t="s">
+      <c r="D50" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" t="s">
+      <c r="E50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" t="s">
+      <c r="G50" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" t="s">
+      <c r="H50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
+      <c r="C53" s="1" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" t="s">
+      <c r="D53" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" t="s">
+      <c r="E53" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" t="s">
+      <c r="G53" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" t="s">
+      <c r="H53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" t="s">
+      <c r="D54" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" t="s">
+      <c r="E54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" t="s">
+      <c r="G54" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" t="s">
-        <v>149</v>
+      <c r="H59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="3">
+        <v>46216</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="3">
+        <v>46216</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="3">
+        <v>46216</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="3">
+        <v>46221</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="3">
+        <v>46221</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="3">
+        <v>46221</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="3">
+        <v>46221</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="3">
+        <v>46221</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="3">
+        <v>46221</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="3">
+        <v>46221</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="3">
+        <v>46221</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="3">
+        <v>46221</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="3">
+        <v>46221</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="3">
+        <v>46222</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="3">
+        <v>46222</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="3">
+        <v>46222</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="3">
+        <v>46222</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="3">
+        <v>46222</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="3">
+        <v>46228</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="3">
+        <v>46228</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="3">
+        <v>46228</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="3">
+        <v>46228</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="3">
+        <v>46228</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="3">
+        <v>46229</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="3">
+        <v>46229</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="3">
+        <v>46229</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="3">
+        <v>46229</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="3">
+        <v>46229</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="3">
+        <v>46229</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="3">
+        <v>46229</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="3">
+        <v>46229</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="156" ht="30" spans="1:9">
+      <c r="A156" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I156" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="157" ht="30" spans="1:9">
+      <c r="A157" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H157" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I157" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="158" ht="30" spans="1:9">
+      <c r="A158" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I158" s="7" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="159" ht="30" spans="1:9">
+      <c r="A159" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H159" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I159" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="160" ht="27" spans="1:9">
+      <c r="A160" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I160" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="161" ht="27" spans="1:9">
+      <c r="A161" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H161" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I161" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="162" ht="16.5" spans="1:9">
+      <c r="A162" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I162" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="163" ht="30" spans="1:9">
+      <c r="A163" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H163" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I163" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="164" ht="27" spans="1:9">
+      <c r="A164" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H164" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I164" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="165" ht="27" spans="1:9">
+      <c r="A165" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H165" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I165" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="166" ht="27" spans="1:9">
+      <c r="A166" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H166" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I166" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="167" ht="27" spans="1:9">
+      <c r="A167" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H167" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I167" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="168" ht="30" spans="1:9">
+      <c r="A168" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H168" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I168" s="7" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="169" ht="27" spans="1:9">
+      <c r="A169" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H169" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I169" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="170" ht="30" spans="1:9">
+      <c r="A170" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H170" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I170" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="171" ht="27" spans="1:9">
+      <c r="A171" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H171" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I171" s="5" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I171" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:I171">
+      <sortCondition ref="A1"/>
+    </sortState>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/数据库.xlsx
+++ b/数据库.xlsx
@@ -7,10 +7,11 @@
     <workbookView windowWidth="19635" windowHeight="7695"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="智胜库" sheetId="1" r:id="rId1"/>
+    <sheet name="精选场次" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">智胜库!$A$1:$I$214</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="481">
   <si>
     <t>日期</t>
   </si>
@@ -1280,6 +1281,261 @@
   </si>
   <si>
     <t>米内罗竞技</t>
+  </si>
+  <si>
+    <t>阿波罗利马索尔</t>
+  </si>
+  <si>
+    <t>帕纳辛纳科斯</t>
+  </si>
+  <si>
+    <t>索非亚1948</t>
+  </si>
+  <si>
+    <t>主让1.5/2</t>
+  </si>
+  <si>
+    <t>比亚韦斯托克</t>
+  </si>
+  <si>
+    <t>格拉斯哥流浪者</t>
+  </si>
+  <si>
+    <t>客队不败</t>
+  </si>
+  <si>
+    <t>特拉维夫马卡比</t>
+  </si>
+  <si>
+    <t>索非亚中央陆军</t>
+  </si>
+  <si>
+    <t>冷门（崩盘）</t>
+  </si>
+  <si>
+    <t>亚布洛内茨</t>
+  </si>
+  <si>
+    <t>里加足球学院</t>
+  </si>
+  <si>
+    <t>锡永</t>
+  </si>
+  <si>
+    <t>马瑟韦尔</t>
+  </si>
+  <si>
+    <t>主不败</t>
+  </si>
+  <si>
+    <t>派德</t>
+  </si>
+  <si>
+    <t>维也纳快速</t>
+  </si>
+  <si>
+    <t>客让1.5/2</t>
+  </si>
+  <si>
+    <t>克卢日</t>
+  </si>
+  <si>
+    <t>特罗姆瑟</t>
+  </si>
+  <si>
+    <t>客不败</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>主队崩盘</t>
+  </si>
+  <si>
+    <t>波兹南莱赫</t>
+  </si>
+  <si>
+    <t>克拉克斯维克</t>
+  </si>
+  <si>
+    <t>大小球</t>
+  </si>
+  <si>
+    <t>赫拉德茨克拉洛韦</t>
+  </si>
+  <si>
+    <t>贝西克塔斯</t>
+  </si>
+  <si>
+    <t>客胜</t>
+  </si>
+  <si>
+    <t>萨尔茨堡</t>
+  </si>
+  <si>
+    <t>帕福斯</t>
+  </si>
+  <si>
+    <t>放弃（走水）</t>
+  </si>
+  <si>
+    <t>德布勒森尼</t>
+  </si>
+  <si>
+    <t>哥本哈根</t>
+  </si>
+  <si>
+    <t>客让0.5/1</t>
+  </si>
+  <si>
+    <t>里加FC</t>
+  </si>
+  <si>
+    <t>吉奥里</t>
+  </si>
+  <si>
+    <t>扎尔吉里斯</t>
+  </si>
+  <si>
+    <t>斯普利特海杜克</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>琴斯托霍瓦</t>
+  </si>
+  <si>
+    <t>谢里夫</t>
+  </si>
+  <si>
+    <t>圣加仑</t>
+  </si>
+  <si>
+    <t>冷门命中</t>
+  </si>
+  <si>
+    <t>基辅迪纳摩</t>
+  </si>
+  <si>
+    <t>卡拉巴克</t>
+  </si>
+  <si>
+    <t>根特</t>
+  </si>
+  <si>
+    <t>伊斯卡尔德斯</t>
+  </si>
+  <si>
+    <t>塔林弗洛拉</t>
+  </si>
+  <si>
+    <t>比达耶路撒冷</t>
+  </si>
+  <si>
+    <t>奥地利维也纳</t>
+  </si>
+  <si>
+    <t>塞萨洛尼基</t>
+  </si>
+  <si>
+    <t>主场高估</t>
+  </si>
+  <si>
+    <t>维京古尔</t>
+  </si>
+  <si>
+    <t>阿贾克斯</t>
+  </si>
+  <si>
+    <t>谢尔伯恩</t>
+  </si>
+  <si>
+    <t>特拉维夫夏普尔</t>
+  </si>
+  <si>
+    <t>GKS卡托威斯</t>
+  </si>
+  <si>
+    <t>斯特里达</t>
+  </si>
+  <si>
+    <t>瓦路尔</t>
+  </si>
+  <si>
+    <t>北西兰</t>
+  </si>
+  <si>
+    <t>巴尼亚卢卡战士</t>
+  </si>
+  <si>
+    <t>迪尼普罗加切</t>
+  </si>
+  <si>
+    <t>卢加诺</t>
+  </si>
+  <si>
+    <t>NSI鲁纳维克</t>
+  </si>
+  <si>
+    <t>里耶卡</t>
+  </si>
+  <si>
+    <t>波希米亚人</t>
+  </si>
+  <si>
+    <t>中日德兰</t>
+  </si>
+  <si>
+    <t>英联杯</t>
+  </si>
+  <si>
+    <t>布里斯托城</t>
+  </si>
+  <si>
+    <t>沃尔索尔</t>
+  </si>
+  <si>
+    <t>希伯尼安</t>
+  </si>
+  <si>
+    <t>斯肯迪亚</t>
+  </si>
+  <si>
+    <t>特费奥里</t>
+  </si>
+  <si>
+    <t>德利塔</t>
+  </si>
+  <si>
+    <t>客让1.5</t>
+  </si>
+  <si>
+    <t>贝尔格莱德游击</t>
+  </si>
+  <si>
+    <t>本菲卡</t>
+  </si>
+  <si>
+    <t>哈茨</t>
+  </si>
+  <si>
+    <t>大球</t>
+  </si>
+  <si>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>圣塔菲联</t>
+  </si>
+  <si>
+    <t>拉努斯</t>
+  </si>
+  <si>
+    <t>科林蒂安</t>
+  </si>
+  <si>
+    <t>巴西国际</t>
   </si>
 </sst>
 </file>
@@ -1919,8 +2175,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1930,9 +2192,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2469,4978 +2728,6225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I171"/>
+  <dimension ref="A1:I214"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.875" style="1"/>
-    <col min="2" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="10.375" style="1"/>
-    <col min="8" max="8" width="9" style="2"/>
-    <col min="9" max="9" width="47.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.875" style="3"/>
+    <col min="2" max="6" width="9" style="3"/>
+    <col min="7" max="7" width="10.375" style="4"/>
+    <col min="8" max="8" width="9" style="4"/>
+    <col min="9" max="9" width="47.75" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="3">
+      <c r="A2" s="5">
         <v>46188</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="3">
+      <c r="A3" s="5">
         <v>46188</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="3">
+      <c r="A4" s="5">
         <v>46188</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="3">
+      <c r="A5" s="5">
         <v>46189</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="3">
+      <c r="A6" s="5">
         <v>46193</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="3">
+      <c r="A7" s="5">
         <v>46193</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="3">
+      <c r="A8" s="5">
         <v>46193</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="3">
+      <c r="A9" s="5">
         <v>46193</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="3">
+      <c r="A10" s="5">
         <v>46197</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="3">
+      <c r="A11" s="5">
         <v>46197</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="3">
+      <c r="A12" s="5">
         <v>46197</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="3">
+      <c r="A13" s="5">
         <v>46197</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="3">
+      <c r="A14" s="5">
         <v>46200</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="3">
+      <c r="A15" s="5">
         <v>46200</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="3">
+      <c r="A16" s="5">
         <v>46200</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="3">
+      <c r="A17" s="5">
         <v>46203</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="3">
+      <c r="A18" s="5">
         <v>46203</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="3">
+      <c r="A19" s="5">
         <v>46203</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="3">
+      <c r="A20" s="5">
         <v>46204</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="3">
+      <c r="A21" s="5">
         <v>46204</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="3">
+      <c r="A22" s="5">
         <v>46204</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="3">
+      <c r="A23" s="5">
         <v>46204</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="3">
+      <c r="A24" s="5">
         <v>46204</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="3">
+      <c r="A25" s="5">
         <v>46204</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="3">
+      <c r="A26" s="5">
         <v>46205</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="3">
+      <c r="A27" s="5">
         <v>46205</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="3">
+      <c r="A28" s="5">
         <v>46205</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="3">
+      <c r="A29" s="5">
         <v>46206</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="3">
+      <c r="A30" s="5">
         <v>46206</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="3">
+      <c r="A31" s="5">
         <v>46206</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="3">
+      <c r="A32" s="5">
         <v>46207</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="3">
+      <c r="A33" s="5">
         <v>46207</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="3">
+      <c r="A34" s="5">
         <v>46207</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" s="3" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="3">
+      <c r="A35" s="5">
         <v>46208</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="3">
+      <c r="A36" s="5">
         <v>46208</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="3">
+      <c r="A37" s="5">
         <v>46209</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="3">
+      <c r="A38" s="5">
         <v>46209</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="3">
+      <c r="A39" s="5">
         <v>46210</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="3">
+      <c r="A40" s="5">
         <v>46210</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H40" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="3">
+      <c r="A41" s="5">
         <v>46211</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="H41" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="3">
+      <c r="A42" s="5">
         <v>46211</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="3">
+      <c r="A43" s="5">
         <v>46213</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="3">
+      <c r="A44" s="5">
         <v>46214</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H44" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I44" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="3">
+      <c r="A45" s="5">
         <v>46214</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H45" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="3">
+      <c r="A46" s="5">
         <v>46214</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="H46" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="3">
+      <c r="A47" s="5">
         <v>46214</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="H47" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="3">
+      <c r="A48" s="5">
         <v>46214</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="H48" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="3">
+      <c r="A49" s="5">
         <v>46214</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H49" s="2" t="s">
+      <c r="H49" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" s="3" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="3">
+      <c r="A50" s="5">
         <v>46214</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H50" s="2" t="s">
+      <c r="H50" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="3">
+      <c r="A51" s="5">
         <v>46215</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="H51" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="I51" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="3">
+      <c r="A52" s="5">
         <v>46215</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="I52" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="3">
+      <c r="A53" s="5">
         <v>46215</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="H53" s="2" t="s">
+      <c r="H53" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="3">
+      <c r="A54" s="5">
         <v>46215</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="H54" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="3">
+      <c r="A55" s="5">
         <v>46215</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="3">
+      <c r="A56" s="5">
         <v>46215</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H56" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="3">
+      <c r="A57" s="5">
         <v>46215</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H57" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="I57" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="3">
+      <c r="A58" s="5">
         <v>46215</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H58" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I58" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="3">
+      <c r="A59" s="5">
         <v>46215</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="H59" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I59" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="3">
+      <c r="A60" s="5">
         <v>46215</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="G60" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="H60" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="I60" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="3">
+      <c r="A61" s="5">
         <v>46215</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="H61" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="I61" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="3">
+      <c r="A62" s="5">
         <v>46216</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="G62" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="H62" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="I62" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="3">
+      <c r="A63" s="5">
         <v>46216</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="H63" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="I63" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="3">
+      <c r="A64" s="5">
         <v>46216</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="G64" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H64" s="2" t="s">
+      <c r="H64" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="I64" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="3">
+      <c r="A65" s="5">
         <v>46220</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G65" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H65" s="2" t="s">
+      <c r="H65" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I65" s="1" t="s">
+      <c r="I65" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="3">
+      <c r="A66" s="5">
         <v>46220</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G66" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H66" s="2" t="s">
+      <c r="H66" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I66" s="1" t="s">
+      <c r="I66" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="3">
+      <c r="A67" s="5">
         <v>46220</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="G67" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H67" s="2" t="s">
+      <c r="H67" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I67" s="1" t="s">
+      <c r="I67" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="3">
+      <c r="A68" s="5">
         <v>46221</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="G68" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H68" s="2" t="s">
+      <c r="H68" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="I68" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="3">
+      <c r="A69" s="5">
         <v>46221</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="G69" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="H69" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="I69" s="3" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="3">
+      <c r="A70" s="5">
         <v>46221</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G70" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H70" s="2" t="s">
+      <c r="H70" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="I70" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" s="3">
+      <c r="A71" s="5">
         <v>46221</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="G71" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H71" s="2" t="s">
+      <c r="H71" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I71" s="1" t="s">
+      <c r="I71" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="3">
+      <c r="A72" s="5">
         <v>46221</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E72" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="G72" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H72" s="2" t="s">
+      <c r="H72" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I72" s="1" t="s">
+      <c r="I72" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="3">
+      <c r="A73" s="5">
         <v>46221</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G73" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H73" s="2" t="s">
+      <c r="H73" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="I73" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="3">
+      <c r="A74" s="5">
         <v>46221</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E74" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="G74" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="H74" s="2" t="s">
+      <c r="H74" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="I74" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="3">
+      <c r="A75" s="5">
         <v>46221</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G75" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H75" s="2" t="s">
+      <c r="H75" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I75" s="1" t="s">
+      <c r="I75" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="76" spans="1:9">
-      <c r="A76" s="3">
+      <c r="A76" s="5">
         <v>46221</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H76" s="2" t="s">
+      <c r="H76" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="I76" s="1" t="s">
+      <c r="I76" s="3" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:9">
-      <c r="A77" s="3">
+      <c r="A77" s="5">
         <v>46221</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G77" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H77" s="2" t="s">
+      <c r="H77" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="I77" s="3" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="A78" s="3">
+      <c r="A78" s="5">
         <v>46222</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E78" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="H78" s="2" t="s">
+      <c r="H78" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I78" s="1" t="s">
+      <c r="I78" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="3">
+      <c r="A79" s="5">
         <v>46222</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D79" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E79" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F79" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="G79" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="H79" s="2" t="s">
+      <c r="H79" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="I79" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:9">
-      <c r="A80" s="3">
+      <c r="A80" s="5">
         <v>46222</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E80" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H80" s="2" t="s">
+      <c r="H80" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="I80" s="1" t="s">
+      <c r="I80" s="3" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="81" spans="1:9">
-      <c r="A81" s="3">
+      <c r="A81" s="5">
         <v>46222</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="G81" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H81" s="2" t="s">
+      <c r="H81" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I81" s="1" t="s">
+      <c r="I81" s="3" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" s="3">
+      <c r="A82" s="5">
         <v>46222</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E82" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F82" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="G82" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H82" s="2" t="s">
+      <c r="H82" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="I82" s="1" t="s">
+      <c r="I82" s="3" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="83" spans="1:9">
-      <c r="A83" s="3">
+      <c r="A83" s="5">
         <v>46224</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F83" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G83" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H83" s="2" t="s">
+      <c r="H83" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I83" s="1" t="s">
+      <c r="I83" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:9">
-      <c r="A84" s="3">
+      <c r="A84" s="5">
         <v>46224</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D84" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E84" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F84" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G84" s="1" t="s">
+      <c r="G84" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="H84" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I84" s="1" t="s">
+      <c r="I84" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="85" spans="1:9">
-      <c r="A85" s="3">
+      <c r="A85" s="5">
         <v>46224</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E85" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F85" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G85" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H85" s="2" t="s">
+      <c r="H85" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I85" s="1" t="s">
+      <c r="I85" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:9">
-      <c r="A86" s="3">
+      <c r="A86" s="5">
         <v>46225</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E86" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F86" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G86" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H86" s="2" t="s">
+      <c r="H86" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I86" s="1" t="s">
+      <c r="I86" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="87" spans="1:9">
-      <c r="A87" s="3">
+      <c r="A87" s="5">
         <v>46225</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D87" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E87" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F87" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G87" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="H87" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I87" s="1" t="s">
+      <c r="I87" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="88" spans="1:9">
-      <c r="A88" s="3">
+      <c r="A88" s="5">
         <v>46225</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E88" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F88" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="G88" s="1" t="s">
+      <c r="G88" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H88" s="2" t="s">
+      <c r="H88" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I88" s="1" t="s">
+      <c r="I88" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:9">
-      <c r="A89" s="3">
+      <c r="A89" s="5">
         <v>46225</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E89" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F89" s="1" t="s">
+      <c r="F89" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="G89" s="1" t="s">
+      <c r="G89" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H89" s="2" t="s">
+      <c r="H89" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I89" s="1" t="s">
+      <c r="I89" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:9">
-      <c r="A90" s="3">
+      <c r="A90" s="5">
         <v>46226</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E90" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="F90" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G90" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H90" s="2" t="s">
+      <c r="H90" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I90" s="1" t="s">
+      <c r="I90" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:9">
-      <c r="A91" s="3">
+      <c r="A91" s="5">
         <v>46226</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E91" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F91" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H91" s="2" t="s">
+      <c r="H91" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I91" s="1" t="s">
+      <c r="I91" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:9">
-      <c r="A92" s="3">
+      <c r="A92" s="5">
         <v>46228</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E92" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="F92" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G92" s="2" t="s">
+      <c r="G92" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H92" s="2" t="s">
+      <c r="H92" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="I92" s="1" t="s">
+      <c r="I92" s="3" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="3">
+      <c r="A93" s="5">
         <v>46228</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D93" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E93" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="F93" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="G93" s="1" t="s">
+      <c r="G93" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H93" s="2" t="s">
+      <c r="H93" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="I93" s="1" t="s">
+      <c r="I93" s="3" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" s="3">
+      <c r="A94" s="5">
         <v>46228</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D94" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E94" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F94" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="G94" s="1" t="s">
+      <c r="G94" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H94" s="2" t="s">
+      <c r="H94" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I94" s="1" t="s">
+      <c r="I94" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:9">
-      <c r="A95" s="3">
+      <c r="A95" s="5">
         <v>46228</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E95" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="F95" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G95" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H95" s="2" t="s">
+      <c r="H95" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I95" s="1" t="s">
+      <c r="I95" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="96" spans="1:9">
-      <c r="A96" s="3">
+      <c r="A96" s="5">
         <v>46228</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D96" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E96" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F96" s="1" t="s">
+      <c r="F96" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="G96" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H96" s="2" t="s">
+      <c r="H96" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="I96" s="1" t="s">
+      <c r="I96" s="3" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="97" spans="1:9">
-      <c r="A97" s="3">
+      <c r="A97" s="5">
         <v>46229</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D97" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E97" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="F97" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G97" s="2" t="s">
+      <c r="G97" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H97" s="2" t="s">
+      <c r="H97" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I97" s="1" t="s">
+      <c r="I97" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:9">
-      <c r="A98" s="3">
+      <c r="A98" s="5">
         <v>46229</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D98" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E98" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F98" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="G98" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H98" s="2" t="s">
+      <c r="H98" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I98" s="1" t="s">
+      <c r="I98" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:9">
-      <c r="A99" s="3">
+      <c r="A99" s="5">
         <v>46229</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D99" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E99" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F99" s="1" t="s">
+      <c r="F99" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="G99" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H99" s="2" t="s">
+      <c r="H99" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I99" s="1" t="s">
+      <c r="I99" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:9">
-      <c r="A100" s="3">
+      <c r="A100" s="5">
         <v>46229</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E100" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F100" s="1" t="s">
+      <c r="F100" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G100" s="2" t="s">
+      <c r="G100" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="H100" s="2" t="s">
+      <c r="H100" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="I100" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:9">
-      <c r="A101" s="3">
+      <c r="A101" s="5">
         <v>46229</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D101" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E101" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="F101" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="G101" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H101" s="2" t="s">
+      <c r="H101" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="I101" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" s="3">
+      <c r="A102" s="5">
         <v>46229</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D102" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E102" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="F102" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G102" s="2" t="s">
+      <c r="G102" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H102" s="2" t="s">
+      <c r="H102" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="I102" s="1" t="s">
+      <c r="I102" s="3" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="103" spans="1:9">
-      <c r="A103" s="3">
+      <c r="A103" s="5">
         <v>46229</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="D103" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E103" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="F103" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G103" s="2" t="s">
+      <c r="G103" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="H103" s="2" t="s">
+      <c r="H103" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I103" s="1" t="s">
+      <c r="I103" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:9">
-      <c r="A104" s="3">
+      <c r="A104" s="5">
         <v>46229</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="D104" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E104" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F104" s="1" t="s">
+      <c r="F104" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="G104" s="1" t="s">
+      <c r="G104" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H104" s="2" t="s">
+      <c r="H104" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I104" s="1" t="s">
+      <c r="I104" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:9">
-      <c r="A105" s="3">
+      <c r="A105" s="5">
         <v>46231</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E105" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="F105" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="G105" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H105" s="2" t="s">
+      <c r="H105" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I105" s="1" t="s">
+      <c r="I105" s="3" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:9">
-      <c r="A106" s="3">
+      <c r="A106" s="5">
         <v>46231</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C106" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D106" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E106" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="F106" s="1" t="s">
+      <c r="F106" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G106" s="1" t="s">
+      <c r="G106" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="H106" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I106" s="1" t="s">
+      <c r="I106" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="107" spans="1:9">
-      <c r="A107" s="3">
+      <c r="A107" s="5">
         <v>46231</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B107" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C107" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D107" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E107" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="F107" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="G107" s="2" t="s">
+      <c r="G107" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="H107" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I107" s="1" t="s">
+      <c r="I107" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:9">
-      <c r="A108" s="3">
+      <c r="A108" s="5">
         <v>46232</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B108" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D108" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E108" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="F108" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G108" s="1" t="s">
+      <c r="G108" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H108" s="2" t="s">
+      <c r="H108" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I108" s="1" t="s">
+      <c r="I108" s="3" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="109" spans="1:9">
-      <c r="A109" s="3">
+      <c r="A109" s="5">
         <v>46232</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B109" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D109" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E109" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F109" s="1" t="s">
+      <c r="F109" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G109" s="1" t="s">
+      <c r="G109" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H109" s="2" t="s">
+      <c r="H109" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I109" s="1" t="s">
+      <c r="I109" s="3" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="110" spans="1:9">
-      <c r="A110" s="3">
+      <c r="A110" s="5">
         <v>46232</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D110" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="E110" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="F110" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="G110" s="1" t="s">
+      <c r="G110" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H110" s="2" t="s">
+      <c r="H110" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="I110" s="1" t="s">
+      <c r="I110" s="3" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="111" spans="1:9">
-      <c r="A111" s="3">
+      <c r="A111" s="5">
         <v>46232</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="D111" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E111" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="F111" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="G111" s="1" t="s">
+      <c r="G111" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H111" s="2" t="s">
+      <c r="H111" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I111" s="1" t="s">
+      <c r="I111" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:9">
-      <c r="A112" s="3">
+      <c r="A112" s="5">
         <v>46232</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D112" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E112" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="F112" s="1" t="s">
+      <c r="F112" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="G112" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H112" s="2" t="s">
+      <c r="H112" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I112" s="1" t="s">
+      <c r="I112" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="113" spans="1:9">
-      <c r="A113" s="3">
+      <c r="A113" s="5">
         <v>46232</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C113" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D113" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E113" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F113" s="1" t="s">
+      <c r="F113" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="G113" s="1" t="s">
+      <c r="G113" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H113" s="2" t="s">
+      <c r="H113" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I113" s="1" t="s">
+      <c r="I113" s="3" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="114" spans="1:9">
-      <c r="A114" s="3">
+      <c r="A114" s="5">
         <v>46232</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D114" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E114" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="F114" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="G114" s="2" t="s">
+      <c r="G114" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H114" s="2" t="s">
+      <c r="H114" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="I114" s="1" t="s">
+      <c r="I114" s="3" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="115" spans="1:9">
-      <c r="A115" s="3">
+      <c r="A115" s="5">
         <v>46232</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D115" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E115" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F115" s="1" t="s">
+      <c r="F115" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G115" s="1" t="s">
+      <c r="G115" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H115" s="2" t="s">
+      <c r="H115" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I115" s="1" t="s">
+      <c r="I115" s="3" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="116" spans="1:9">
-      <c r="A116" s="3">
+      <c r="A116" s="5">
         <v>46232</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D116" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E116" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F116" s="1" t="s">
+      <c r="F116" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G116" s="1" t="s">
+      <c r="G116" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H116" s="2" t="s">
+      <c r="H116" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I116" s="1" t="s">
+      <c r="I116" s="3" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="117" spans="1:9">
-      <c r="A117" s="3">
+      <c r="A117" s="5">
         <v>46232</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D117" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E117" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F117" s="1" t="s">
+      <c r="F117" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="G117" s="1" t="s">
+      <c r="G117" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H117" s="2" t="s">
+      <c r="H117" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="I117" s="1" t="s">
+      <c r="I117" s="3" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="118" spans="1:9">
-      <c r="A118" s="3">
+      <c r="A118" s="5">
         <v>46233</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D118" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E118" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="F118" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="G118" s="2" t="s">
+      <c r="G118" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H118" s="2" t="s">
+      <c r="H118" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="I118" s="1" t="s">
+      <c r="I118" s="3" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="119" spans="1:9">
-      <c r="A119" s="3">
+      <c r="A119" s="5">
         <v>46233</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D119" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="E119" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="F119" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="G119" s="2" t="s">
+      <c r="G119" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H119" s="2" t="s">
+      <c r="H119" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="I119" s="1" t="s">
+      <c r="I119" s="3" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="120" spans="1:9">
-      <c r="A120" s="3">
+      <c r="A120" s="5">
         <v>46233</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B120" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="D120" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="E120" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="F120" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="G120" s="2" t="s">
+      <c r="G120" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H120" s="2" t="s">
+      <c r="H120" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="I120" s="1" t="s">
+      <c r="I120" s="3" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="121" spans="1:9">
-      <c r="A121" s="3">
+      <c r="A121" s="5">
         <v>46233</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="D121" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="E121" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F121" s="1" t="s">
+      <c r="F121" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="G121" s="1" t="s">
+      <c r="G121" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H121" s="2" t="s">
+      <c r="H121" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="I121" s="1" t="s">
+      <c r="I121" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="122" spans="1:9">
-      <c r="A122" s="3">
+      <c r="A122" s="5">
         <v>46233</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D122" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="E122" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="F122" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="G122" s="2" t="s">
+      <c r="G122" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H122" s="2" t="s">
+      <c r="H122" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="I122" s="1" t="s">
+      <c r="I122" s="3" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:9">
-      <c r="A123" s="3">
+      <c r="A123" s="5">
         <v>46233</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C123" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D123" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="E123" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="F123" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="G123" s="1" t="s">
+      <c r="G123" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H123" s="2" t="s">
+      <c r="H123" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I123" s="1" t="s">
+      <c r="I123" s="3" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:9">
-      <c r="A124" s="3">
+      <c r="A124" s="5">
         <v>46233</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="D124" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="E124" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="F124" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="G124" s="2" t="s">
+      <c r="G124" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H124" s="2" t="s">
+      <c r="H124" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="I124" s="1" t="s">
+      <c r="I124" s="3" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="125" spans="1:9">
-      <c r="A125" s="3">
+      <c r="A125" s="5">
         <v>46234</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D125" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="E125" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="F125" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="G125" s="2" t="s">
+      <c r="G125" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H125" s="2" t="s">
+      <c r="H125" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="I125" s="1" t="s">
+      <c r="I125" s="3" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="126" spans="1:9">
-      <c r="A126" s="3">
+      <c r="A126" s="5">
         <v>46234</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B126" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D126" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="E126" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="F126" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="G126" s="2" t="s">
+      <c r="G126" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H126" s="2" t="s">
+      <c r="H126" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="I126" s="1" t="s">
+      <c r="I126" s="3" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="127" spans="1:9">
-      <c r="A127" s="3">
+      <c r="A127" s="5">
         <v>46235</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B127" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D127" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E127" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F127" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G127" s="2" t="s">
+      <c r="G127" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H127" s="2" t="s">
+      <c r="H127" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="I127" s="1" t="s">
+      <c r="I127" s="3" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="128" spans="1:9">
-      <c r="A128" s="3">
+      <c r="A128" s="5">
         <v>46235</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B128" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D128" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="E128" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="F128" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G128" s="2" t="s">
+      <c r="G128" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H128" s="2" t="s">
+      <c r="H128" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I128" s="1" t="s">
+      <c r="I128" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="129" spans="1:9">
-      <c r="A129" s="3">
+      <c r="A129" s="5">
         <v>46235</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B129" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="E129" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="F129" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="G129" s="1" t="s">
+      <c r="G129" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H129" s="2" t="s">
+      <c r="H129" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="I129" s="1" t="s">
+      <c r="I129" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="130" spans="1:9">
-      <c r="A130" s="3">
+      <c r="A130" s="5">
         <v>46235</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B130" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="E130" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="F130" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="G130" s="2" t="s">
+      <c r="G130" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H130" s="2" t="s">
+      <c r="H130" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="I130" s="1" t="s">
+      <c r="I130" s="3" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="131" spans="1:9">
-      <c r="A131" s="3">
+      <c r="A131" s="5">
         <v>46235</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B131" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C131" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D131" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="E131" s="1" t="s">
+      <c r="E131" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="F131" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="G131" s="1" t="s">
+      <c r="G131" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H131" s="2" t="s">
+      <c r="H131" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="I131" s="1" t="s">
+      <c r="I131" s="3" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="132" spans="1:9">
-      <c r="A132" s="3">
+      <c r="A132" s="5">
         <v>46235</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B132" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C132" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D132" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="E132" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="F132" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="G132" s="1" t="s">
+      <c r="G132" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H132" s="2" t="s">
+      <c r="H132" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="I132" s="1" t="s">
+      <c r="I132" s="3" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="3">
+      <c r="A133" s="5">
         <v>46235</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B133" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C133" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D133" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="E133" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="F133" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="G133" s="1" t="s">
+      <c r="G133" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H133" s="2" t="s">
+      <c r="H133" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="I133" s="1" t="s">
+      <c r="I133" s="3" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="3">
+      <c r="A134" s="5">
         <v>46235</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B134" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C134" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D134" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="E134" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="F134" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G134" s="2" t="s">
+      <c r="G134" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H134" s="2" t="s">
+      <c r="H134" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="I134" s="1" t="s">
+      <c r="I134" s="3" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="135" spans="1:9">
-      <c r="A135" s="3">
+      <c r="A135" s="5">
         <v>46235</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B135" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="C135" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="D135" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="E135" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F135" s="1" t="s">
+      <c r="F135" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="G135" s="1" t="s">
+      <c r="G135" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H135" s="2" t="s">
+      <c r="H135" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="I135" s="1" t="s">
+      <c r="I135" s="3" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="136" spans="1:9">
-      <c r="A136" s="3">
+      <c r="A136" s="5">
         <v>46236</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B136" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C136" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E136" s="1" t="s">
+      <c r="E136" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="F136" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G136" s="2" t="s">
+      <c r="G136" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H136" s="2" t="s">
+      <c r="H136" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="I136" s="1" t="s">
+      <c r="I136" s="3" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="137" spans="1:9">
-      <c r="A137" s="3">
+      <c r="A137" s="5">
         <v>46236</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B137" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C137" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="D137" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="E137" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="F137" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="G137" s="1" t="s">
+      <c r="G137" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H137" s="2" t="s">
+      <c r="H137" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="I137" s="1" t="s">
+      <c r="I137" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="138" spans="1:9">
-      <c r="A138" s="3">
+      <c r="A138" s="5">
         <v>46236</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B138" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C138" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D138" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="E138" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="F138" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="G138" s="2" t="s">
+      <c r="G138" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H138" s="2" t="s">
+      <c r="H138" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="I138" s="1" t="s">
+      <c r="I138" s="3" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="139" spans="1:9">
-      <c r="A139" s="3">
+      <c r="A139" s="5">
         <v>46236</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B139" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C139" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D139" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E139" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="F139" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G139" s="1" t="s">
+      <c r="G139" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H139" s="2" t="s">
+      <c r="H139" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="I139" s="1" t="s">
+      <c r="I139" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="140" spans="1:9">
-      <c r="A140" s="3">
+      <c r="A140" s="5">
         <v>46236</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B140" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C140" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="D140" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="E140" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F140" s="1" t="s">
+      <c r="F140" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="G140" s="1" t="s">
+      <c r="G140" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H140" s="2" t="s">
+      <c r="H140" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="I140" s="1" t="s">
+      <c r="I140" s="3" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="141" spans="1:9">
-      <c r="A141" s="3">
+      <c r="A141" s="5">
         <v>46236</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B141" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="C141" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D141" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="E141" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="F141" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G141" s="2" t="s">
+      <c r="G141" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H141" s="2" t="s">
+      <c r="H141" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I141" s="1" t="s">
+      <c r="I141" s="3" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="142" spans="1:9">
-      <c r="A142" s="3">
+      <c r="A142" s="5">
         <v>46236</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B142" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C142" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D142" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="E142" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="F142" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="G142" s="2" t="s">
+      <c r="G142" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H142" s="2" t="s">
+      <c r="H142" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="I142" s="1" t="s">
+      <c r="I142" s="3" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="143" spans="1:9">
-      <c r="A143" s="3">
+      <c r="A143" s="5">
         <v>46236</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B143" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="C143" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D143" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="E143" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="F143" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G143" s="2" t="s">
+      <c r="G143" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H143" s="2" t="s">
+      <c r="H143" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="I143" s="1" t="s">
+      <c r="I143" s="3" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="144" spans="1:9">
-      <c r="A144" s="3">
+      <c r="A144" s="5">
         <v>46236</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="C144" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="D144" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="E144" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F144" s="1" t="s">
+      <c r="F144" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="G144" s="1" t="s">
+      <c r="G144" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H144" s="2" t="s">
+      <c r="H144" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="I144" s="1" t="s">
+      <c r="I144" s="3" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="145" spans="1:9">
-      <c r="A145" s="3">
+      <c r="A145" s="5">
         <v>46236</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B145" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="C145" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="D145" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E145" s="1" t="s">
+      <c r="E145" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F145" s="1" t="s">
+      <c r="F145" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G145" s="2" t="s">
+      <c r="G145" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H145" s="2" t="s">
+      <c r="H145" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I145" s="1" t="s">
+      <c r="I145" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="146" spans="1:9">
-      <c r="A146" s="3">
+      <c r="A146" s="5">
         <v>46236</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B146" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="C146" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="D146" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E146" s="1" t="s">
+      <c r="E146" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F146" s="1" t="s">
+      <c r="F146" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="G146" s="1" t="s">
+      <c r="G146" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H146" s="2" t="s">
+      <c r="H146" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I146" s="1" t="s">
+      <c r="I146" s="3" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="147" spans="1:9">
-      <c r="A147" s="3">
+      <c r="A147" s="5">
         <v>46237</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B147" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="C147" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="D147" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="E147" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F147" s="1" t="s">
+      <c r="F147" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="G147" s="1" t="s">
+      <c r="G147" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H147" s="2" t="s">
+      <c r="H147" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="I147" s="1" t="s">
+      <c r="I147" s="3" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="148" spans="1:9">
-      <c r="A148" s="3">
+      <c r="A148" s="5">
         <v>46237</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B148" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="C148" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="D148" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E148" s="1" t="s">
+      <c r="E148" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F148" s="1" t="s">
+      <c r="F148" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="G148" s="2" t="s">
+      <c r="G148" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H148" s="2" t="s">
+      <c r="H148" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="I148" s="1" t="s">
+      <c r="I148" s="3" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="149" spans="1:9">
-      <c r="A149" s="3">
+      <c r="A149" s="5">
         <v>46237</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B149" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="C149" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="D149" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E149" s="1" t="s">
+      <c r="E149" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F149" s="1" t="s">
+      <c r="F149" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="G149" s="1" t="s">
+      <c r="G149" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H149" s="2" t="s">
+      <c r="H149" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="I149" s="1" t="s">
+      <c r="I149" s="3" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="150" spans="1:9">
-      <c r="A150" s="3">
+      <c r="A150" s="5">
         <v>46237</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B150" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="C150" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D150" s="1" t="s">
+      <c r="D150" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E150" s="1" t="s">
+      <c r="E150" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F150" s="1" t="s">
+      <c r="F150" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="G150" s="1" t="s">
+      <c r="G150" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H150" s="2" t="s">
+      <c r="H150" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="I150" s="1" t="s">
+      <c r="I150" s="3" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="151" spans="1:9">
-      <c r="A151" s="3">
+      <c r="A151" s="5">
         <v>46237</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B151" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="C151" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="D151" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E151" s="1" t="s">
+      <c r="E151" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F151" s="1" t="s">
+      <c r="F151" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="G151" s="1" t="s">
+      <c r="G151" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H151" s="2" t="s">
+      <c r="H151" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="I151" s="1" t="s">
+      <c r="I151" s="3" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="152" spans="1:9">
-      <c r="A152" s="3">
+      <c r="A152" s="5">
         <v>46237</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="B152" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="C152" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="D152" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E152" s="1" t="s">
+      <c r="E152" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F152" s="1" t="s">
+      <c r="F152" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="G152" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H152" s="2" t="s">
+      <c r="H152" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I152" s="1" t="s">
+      <c r="I152" s="3" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="153" spans="1:9">
-      <c r="A153" s="3">
+      <c r="A153" s="5">
         <v>46237</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="B153" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="C153" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D153" s="1" t="s">
+      <c r="D153" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E153" s="1" t="s">
+      <c r="E153" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="F153" s="1" t="s">
+      <c r="F153" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G153" s="2" t="s">
+      <c r="G153" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H153" s="2" t="s">
+      <c r="H153" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I153" s="1" t="s">
+      <c r="I153" s="3" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="154" spans="1:9">
-      <c r="A154" s="3">
+      <c r="A154" s="5">
         <v>46237</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B154" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C154" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="D154" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="E154" s="1" t="s">
+      <c r="E154" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="F154" s="1" t="s">
+      <c r="F154" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G154" s="2" t="s">
+      <c r="G154" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H154" s="2" t="s">
+      <c r="H154" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="I154" s="1" t="s">
+      <c r="I154" s="3" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="155" spans="1:9">
-      <c r="A155" s="3">
+      <c r="A155" s="5">
         <v>46237</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="B155" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="C155" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="D155" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E155" s="1" t="s">
+      <c r="E155" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="F155" s="1" t="s">
+      <c r="F155" s="3" t="s">
         <v>128</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="H155" s="2" t="s">
+      <c r="H155" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I155" s="1" t="s">
+      <c r="I155" s="3" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="156" ht="30" spans="1:9">
-      <c r="A156" s="3">
+      <c r="A156" s="5">
         <v>46238</v>
       </c>
-      <c r="B156" s="5" t="s">
+      <c r="B156" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C156" s="5" t="s">
+      <c r="C156" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D156" s="5" t="s">
+      <c r="D156" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="E156" s="5" t="s">
+      <c r="E156" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F156" s="5" t="s">
+      <c r="F156" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="G156" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H156" s="6" t="s">
+      <c r="H156" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I156" s="7" t="s">
+      <c r="I156" s="8" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="157" ht="30" spans="1:9">
-      <c r="A157" s="3">
+      <c r="A157" s="5">
         <v>46238</v>
       </c>
-      <c r="B157" s="5" t="s">
+      <c r="B157" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C157" s="5" t="s">
+      <c r="C157" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="D157" s="5" t="s">
+      <c r="D157" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E157" s="5" t="s">
+      <c r="E157" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="F157" s="5" t="s">
+      <c r="F157" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="G157" s="2" t="s">
+      <c r="G157" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H157" s="6" t="s">
+      <c r="H157" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I157" s="5" t="s">
+      <c r="I157" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="158" ht="30" spans="1:9">
-      <c r="A158" s="3">
+      <c r="A158" s="5">
         <v>46238</v>
       </c>
-      <c r="B158" s="5" t="s">
+      <c r="B158" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C158" s="5" t="s">
+      <c r="C158" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="D158" s="5" t="s">
+      <c r="D158" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="E158" s="5" t="s">
+      <c r="E158" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="F158" s="5" t="s">
+      <c r="F158" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="G158" s="2" t="s">
+      <c r="G158" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H158" s="2" t="s">
+      <c r="H158" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="I158" s="7" t="s">
+      <c r="I158" s="8" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="159" ht="30" spans="1:9">
-      <c r="A159" s="3">
+      <c r="A159" s="5">
         <v>46238</v>
       </c>
-      <c r="B159" s="5" t="s">
+      <c r="B159" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="C159" s="5" t="s">
+      <c r="C159" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="D159" s="5" t="s">
+      <c r="D159" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="E159" s="5" t="s">
+      <c r="E159" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="F159" s="5" t="s">
+      <c r="F159" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="G159" s="2" t="s">
+      <c r="G159" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H159" s="6" t="s">
+      <c r="H159" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I159" s="5" t="s">
+      <c r="I159" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="160" ht="27" spans="1:9">
-      <c r="A160" s="3">
+      <c r="A160" s="5">
         <v>46238</v>
       </c>
-      <c r="B160" s="5" t="s">
+      <c r="B160" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="C160" s="5" t="s">
+      <c r="C160" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="D160" s="5" t="s">
+      <c r="D160" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="E160" s="5" t="s">
+      <c r="E160" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="F160" s="5" t="s">
+      <c r="F160" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="G160" s="2" t="s">
+      <c r="G160" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H160" s="6" t="s">
+      <c r="H160" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I160" s="5" t="s">
+      <c r="I160" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="161" ht="27" spans="1:9">
-      <c r="A161" s="3">
+      <c r="A161" s="5">
         <v>46238</v>
       </c>
-      <c r="B161" s="5" t="s">
+      <c r="B161" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C161" s="5" t="s">
+      <c r="C161" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="D161" s="5" t="s">
+      <c r="D161" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="E161" s="5" t="s">
+      <c r="E161" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F161" s="5" t="s">
+      <c r="F161" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="G161" s="2" t="s">
+      <c r="G161" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H161" s="6" t="s">
+      <c r="H161" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I161" s="5" t="s">
+      <c r="I161" s="6" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="1:9">
-      <c r="A162" s="3">
+      <c r="A162" s="5">
         <v>46238</v>
       </c>
-      <c r="B162" s="5" t="s">
+      <c r="B162" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="C162" s="5" t="s">
+      <c r="C162" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D162" s="5" t="s">
+      <c r="D162" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="E162" s="5" t="s">
+      <c r="E162" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F162" s="5" t="s">
+      <c r="F162" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G162" s="2" t="s">
+      <c r="G162" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="H162" s="6" t="s">
+      <c r="H162" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I162" s="5" t="s">
+      <c r="I162" s="6" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="163" ht="30" spans="1:9">
-      <c r="A163" s="3">
+      <c r="A163" s="5">
         <v>46238</v>
       </c>
-      <c r="B163" s="5" t="s">
+      <c r="B163" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="C163" s="5" t="s">
+      <c r="C163" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="D163" s="5" t="s">
+      <c r="D163" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="E163" s="5" t="s">
+      <c r="E163" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="F163" s="5" t="s">
+      <c r="F163" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="G163" s="2" t="s">
+      <c r="G163" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H163" s="6" t="s">
+      <c r="H163" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I163" s="7" t="s">
+      <c r="I163" s="8" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="164" ht="27" spans="1:9">
-      <c r="A164" s="3">
+      <c r="A164" s="5">
         <v>46238</v>
       </c>
-      <c r="B164" s="5" t="s">
+      <c r="B164" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C164" s="5" t="s">
+      <c r="C164" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="D164" s="5" t="s">
+      <c r="D164" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="E164" s="5" t="s">
+      <c r="E164" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F164" s="5" t="s">
+      <c r="F164" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="G164" s="2" t="s">
+      <c r="G164" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H164" s="6" t="s">
+      <c r="H164" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I164" s="5" t="s">
+      <c r="I164" s="6" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="165" ht="27" spans="1:9">
-      <c r="A165" s="3">
+      <c r="A165" s="5">
         <v>46238</v>
       </c>
-      <c r="B165" s="5" t="s">
+      <c r="B165" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="C165" s="5" t="s">
+      <c r="C165" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="D165" s="5" t="s">
+      <c r="D165" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="E165" s="5" t="s">
+      <c r="E165" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="F165" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G165" s="2" t="s">
+      <c r="G165" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H165" s="6" t="s">
+      <c r="H165" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I165" s="5" t="s">
+      <c r="I165" s="6" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="166" ht="27" spans="1:9">
-      <c r="A166" s="3">
+      <c r="A166" s="5">
         <v>46238</v>
       </c>
-      <c r="B166" s="5" t="s">
+      <c r="B166" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C166" s="5" t="s">
+      <c r="C166" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="D166" s="5" t="s">
+      <c r="D166" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="E166" s="5" t="s">
+      <c r="E166" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F166" s="5" t="s">
+      <c r="F166" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="G166" s="2" t="s">
+      <c r="G166" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H166" s="6" t="s">
+      <c r="H166" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I166" s="5" t="s">
+      <c r="I166" s="6" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="167" ht="27" spans="1:9">
-      <c r="A167" s="3">
+      <c r="A167" s="5">
         <v>46238</v>
       </c>
-      <c r="B167" s="5" t="s">
+      <c r="B167" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C167" s="5" t="s">
+      <c r="C167" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="D167" s="5" t="s">
+      <c r="D167" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="E167" s="5" t="s">
+      <c r="E167" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="F167" s="5" t="s">
+      <c r="F167" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="G167" s="2" t="s">
+      <c r="G167" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H167" s="6" t="s">
+      <c r="H167" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I167" s="5" t="s">
+      <c r="I167" s="6" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="168" ht="30" spans="1:9">
-      <c r="A168" s="3">
+      <c r="A168" s="5">
         <v>46238</v>
       </c>
-      <c r="B168" s="5" t="s">
+      <c r="B168" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C168" s="5" t="s">
+      <c r="C168" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="D168" s="5" t="s">
+      <c r="D168" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="E168" s="5" t="s">
+      <c r="E168" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="F168" s="5" t="s">
+      <c r="F168" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="G168" s="2" t="s">
+      <c r="G168" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H168" s="6" t="s">
+      <c r="H168" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I168" s="7" t="s">
+      <c r="I168" s="8" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="169" ht="27" spans="1:9">
-      <c r="A169" s="3">
+      <c r="A169" s="5">
         <v>46238</v>
       </c>
-      <c r="B169" s="5" t="s">
+      <c r="B169" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C169" s="5" t="s">
+      <c r="C169" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D169" s="5" t="s">
+      <c r="D169" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="E169" s="5" t="s">
+      <c r="E169" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F169" s="5" t="s">
+      <c r="F169" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G169" s="2" t="s">
+      <c r="G169" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H169" s="6" t="s">
+      <c r="H169" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I169" s="7" t="s">
+      <c r="I169" s="8" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="170" ht="30" spans="1:9">
-      <c r="A170" s="3">
+      <c r="A170" s="5">
         <v>46238</v>
       </c>
-      <c r="B170" s="5" t="s">
+      <c r="B170" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="C170" s="5" t="s">
+      <c r="C170" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="D170" s="5" t="s">
+      <c r="D170" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="E170" s="5" t="s">
+      <c r="E170" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="F170" s="5" t="s">
+      <c r="F170" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G170" s="2" t="s">
+      <c r="G170" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H170" s="6" t="s">
+      <c r="H170" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I170" s="5" t="s">
+      <c r="I170" s="6" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="171" ht="27" spans="1:9">
-      <c r="A171" s="3">
+      <c r="A171" s="5">
         <v>46238</v>
       </c>
-      <c r="B171" s="5" t="s">
+      <c r="B171" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="C171" s="5" t="s">
+      <c r="C171" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="D171" s="5" t="s">
+      <c r="D171" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="E171" s="5" t="s">
+      <c r="E171" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="F171" s="5" t="s">
+      <c r="F171" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G171" s="2" t="s">
+      <c r="G171" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H171" s="6" t="s">
+      <c r="H171" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I171" s="5" t="s">
+      <c r="I171" s="6" t="s">
         <v>184</v>
       </c>
     </row>
+    <row r="172" spans="1:9">
+      <c r="A172" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G172" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I172" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
+      <c r="A173" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H173" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H174" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I174" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
+      <c r="A175" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H175" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I175" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
+      <c r="A176" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H176" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I176" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="A177" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H177" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I177" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="A178" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G178" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H178" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I178" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
+      <c r="A179" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
+      <c r="A180" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G180" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I180" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="A181" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H181" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="A182" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G182" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H182" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I182" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="A183" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I183" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
+      <c r="A184" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="A185" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I185" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="A186" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H186" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I186" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="A187" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="G187" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H187" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I187" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="A188" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="G188" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H188" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I188" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
+      <c r="A189" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G189" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H189" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
+      <c r="A190" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G190" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="H190" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="A191" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G191" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H191" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I191" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="A192" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="G192" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H192" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="G193" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H193" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="G194" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H194" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I194" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I195" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H196" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G197" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H197" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G198" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H198" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="A199" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G199" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H199" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I199" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="A200" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G200" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H200" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I200" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
+      <c r="A201" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G201" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="H201" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="A202" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G202" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H202" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I202" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="A203" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G203" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H203" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I203" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G204" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H204" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I204" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G205" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H205" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G206" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H206" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I206" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G207" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H207" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I207" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G208" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H208" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="A209" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G209" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H209" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I209" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="A210" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G210" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H210" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
+      <c r="A211" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="G211" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="H211" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
+      <c r="A212" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
+      <c r="A213" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G213" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H213" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
+      <c r="A214" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G214" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H214" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I171" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:I171">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I214" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:I214">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -7448,4 +8954,364 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46024</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F4" t="s">
+        <v>358</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46082</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+      <c r="E6" t="s">
+        <v>357</v>
+      </c>
+      <c r="F6" t="s">
+        <v>362</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" t="s">
+        <v>447</v>
+      </c>
+      <c r="D7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E7" t="s">
+        <v>357</v>
+      </c>
+      <c r="F7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C8" t="s">
+        <v>422</v>
+      </c>
+      <c r="D8" t="s">
+        <v>423</v>
+      </c>
+      <c r="E8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" t="s">
+        <v>424</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E9" t="s">
+        <v>353</v>
+      </c>
+      <c r="F9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46054</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>440</v>
+      </c>
+      <c r="D10" t="s">
+        <v>441</v>
+      </c>
+      <c r="E10" t="s">
+        <v>349</v>
+      </c>
+      <c r="F10" t="s">
+        <v>410</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="s">
+        <v>378</v>
+      </c>
+      <c r="C11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D11" t="s">
+        <v>442</v>
+      </c>
+      <c r="E11" t="s">
+        <v>353</v>
+      </c>
+      <c r="F11" t="s">
+        <v>402</v>
+      </c>
+      <c r="G11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="s">
+        <v>359</v>
+      </c>
+      <c r="C12" t="s">
+        <v>479</v>
+      </c>
+      <c r="D12" t="s">
+        <v>480</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>362</v>
+      </c>
+      <c r="G12" s="2">
+        <v>46054</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/数据库.xlsx
+++ b/数据库.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2697" uniqueCount="693">
   <si>
     <t>日期</t>
   </si>
@@ -1536,6 +1536,642 @@
   </si>
   <si>
     <t>巴西国际</t>
+  </si>
+  <si>
+    <t>客队+0.5+大球</t>
+  </si>
+  <si>
+    <t>+100元</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>桑德菲杰</t>
+  </si>
+  <si>
+    <t>主场权重高估</t>
+  </si>
+  <si>
+    <t>丹麦超</t>
+  </si>
+  <si>
+    <t>桑德捷斯基</t>
+  </si>
+  <si>
+    <t>维堡</t>
+  </si>
+  <si>
+    <t>球会友谊</t>
+  </si>
+  <si>
+    <t>富勒姆</t>
+  </si>
+  <si>
+    <t>水晶宫</t>
+  </si>
+  <si>
+    <t>奥甲</t>
+  </si>
+  <si>
+    <t>阿尔塔奇</t>
+  </si>
+  <si>
+    <t>WSG蒂罗尔</t>
+  </si>
+  <si>
+    <t>瑞士甲</t>
+  </si>
+  <si>
+    <t>克里恩斯</t>
+  </si>
+  <si>
+    <t>伊韦尔东</t>
+  </si>
+  <si>
+    <t>乌契</t>
+  </si>
+  <si>
+    <t>瑞普斯威尔</t>
+  </si>
+  <si>
+    <t>温特图尔</t>
+  </si>
+  <si>
+    <t>韦尔</t>
+  </si>
+  <si>
+    <t>荷甲</t>
+  </si>
+  <si>
+    <t>坎布尔</t>
+  </si>
+  <si>
+    <t>SBV精英</t>
+  </si>
+  <si>
+    <t>SBV精英平手</t>
+  </si>
+  <si>
+    <t>荷乙</t>
+  </si>
+  <si>
+    <t>多德勒支</t>
+  </si>
+  <si>
+    <t>阿贾克斯青</t>
+  </si>
+  <si>
+    <t>埃门</t>
+  </si>
+  <si>
+    <t>罗达JC</t>
+  </si>
+  <si>
+    <t>奥斯</t>
+  </si>
+  <si>
+    <t>布雷达</t>
+  </si>
+  <si>
+    <t>芬洛</t>
+  </si>
+  <si>
+    <t>赫拉克勒斯</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>维特斯</t>
+  </si>
+  <si>
+    <t>瓦尔韦克</t>
+  </si>
+  <si>
+    <t>阿劳</t>
+  </si>
+  <si>
+    <t>尼奈斯</t>
+  </si>
+  <si>
+    <t>卡鲁日星</t>
+  </si>
+  <si>
+    <t>纳沙泰尔</t>
+  </si>
+  <si>
+    <t>德乙</t>
+  </si>
+  <si>
+    <t>波鸿</t>
+  </si>
+  <si>
+    <t>柏林赫塔</t>
+  </si>
+  <si>
+    <t>柏林赫塔不败</t>
+  </si>
+  <si>
+    <t>波兰超</t>
+  </si>
+  <si>
+    <t>克拉科夫</t>
+  </si>
+  <si>
+    <t>华沙普洛克</t>
+  </si>
+  <si>
+    <t>比甲</t>
+  </si>
+  <si>
+    <t>布鲁日</t>
+  </si>
+  <si>
+    <t>科特赖克</t>
+  </si>
+  <si>
+    <t>狼队</t>
+  </si>
+  <si>
+    <t>维尔港</t>
+  </si>
+  <si>
+    <t>米德尔斯堡</t>
+  </si>
+  <si>
+    <t>雷克瑟姆</t>
+  </si>
+  <si>
+    <t>韦康比流浪者</t>
+  </si>
+  <si>
+    <t>斯蒂文尼奇</t>
+  </si>
+  <si>
+    <t>爱超</t>
+  </si>
+  <si>
+    <t>邓多克</t>
+  </si>
+  <si>
+    <t>德利城</t>
+  </si>
+  <si>
+    <t>斯莱戈流浪者</t>
+  </si>
+  <si>
+    <t>戈尔韦联</t>
+  </si>
+  <si>
+    <t>德罗赫达联</t>
+  </si>
+  <si>
+    <t>威超</t>
+  </si>
+  <si>
+    <t>新圣徒</t>
+  </si>
+  <si>
+    <t>西哈弗福德</t>
+  </si>
+  <si>
+    <t>特芬琳</t>
+  </si>
+  <si>
+    <t>兰迪德诺</t>
+  </si>
+  <si>
+    <t>弗林特镇</t>
+  </si>
+  <si>
+    <t>巴里镇联</t>
+  </si>
+  <si>
+    <t>霍利韦尔</t>
+  </si>
+  <si>
+    <t>康纳斯码头</t>
+  </si>
+  <si>
+    <t>阿曼福德</t>
+  </si>
+  <si>
+    <t>科尔温湾</t>
+  </si>
+  <si>
+    <t>卡那封</t>
+  </si>
+  <si>
+    <t>佩尼邦</t>
+  </si>
+  <si>
+    <t>卡姆比利安</t>
+  </si>
+  <si>
+    <t>布里顿费里</t>
+  </si>
+  <si>
+    <t>葡超</t>
+  </si>
+  <si>
+    <t>埃斯托里尔</t>
+  </si>
+  <si>
+    <t>法马利康</t>
+  </si>
+  <si>
+    <t>法马利康不败</t>
+  </si>
+  <si>
+    <t>罗萨里奥中央</t>
+  </si>
+  <si>
+    <t>阿尔多斯维</t>
+  </si>
+  <si>
+    <t>巴西乙</t>
+  </si>
+  <si>
+    <t>欧帕尔利奥</t>
+  </si>
+  <si>
+    <t>圣贝纳多</t>
+  </si>
+  <si>
+    <t>塞阿拉</t>
+  </si>
+  <si>
+    <t>庞特普雷塔</t>
+  </si>
+  <si>
+    <t>门多萨独立</t>
+  </si>
+  <si>
+    <t>里奥夸尔托</t>
+  </si>
+  <si>
+    <t>日职联</t>
+  </si>
+  <si>
+    <t>横滨水手</t>
+  </si>
+  <si>
+    <t>鹿岛鹿角</t>
+  </si>
+  <si>
+    <t>鹿岛鹿角胜</t>
+  </si>
+  <si>
+    <t>大阪钢巴</t>
+  </si>
+  <si>
+    <t>浦和红钻</t>
+  </si>
+  <si>
+    <t>浦和红钻不败</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>冷门（钢巴主场爆发）</t>
+  </si>
+  <si>
+    <t>新加坡</t>
+  </si>
+  <si>
+    <t>印度尼西亚</t>
+  </si>
+  <si>
+    <t>印尼不败</t>
+  </si>
+  <si>
+    <t>越南</t>
+  </si>
+  <si>
+    <t>柬埔寨</t>
+  </si>
+  <si>
+    <t>主让3</t>
+  </si>
+  <si>
+    <t>柬埔寨+3+大球</t>
+  </si>
+  <si>
+    <t>圣图尔登</t>
+  </si>
+  <si>
+    <t>洛默尔</t>
+  </si>
+  <si>
+    <t>穿盘失败</t>
+  </si>
+  <si>
+    <t>韦斯特洛</t>
+  </si>
+  <si>
+    <t>圣吉罗斯</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>福冈黄蜂</t>
+  </si>
+  <si>
+    <t>神户胜利船</t>
+  </si>
+  <si>
+    <t>大阪樱花</t>
+  </si>
+  <si>
+    <t>冈山绿雉</t>
+  </si>
+  <si>
+    <t>FC东京</t>
+  </si>
+  <si>
+    <t>町田泽维亚</t>
+  </si>
+  <si>
+    <t>名古屋鲸八</t>
+  </si>
+  <si>
+    <t>清水鼓动</t>
+  </si>
+  <si>
+    <t>广岛三箭</t>
+  </si>
+  <si>
+    <t>千叶市原</t>
+  </si>
+  <si>
+    <t>达姆施塔特</t>
+  </si>
+  <si>
+    <t>荷尔斯泰因</t>
+  </si>
+  <si>
+    <t>海登海姆</t>
+  </si>
+  <si>
+    <t>奥斯纳布鲁克</t>
+  </si>
+  <si>
+    <t>卡尔斯鲁厄</t>
+  </si>
+  <si>
+    <t>比勒菲尔德</t>
+  </si>
+  <si>
+    <t>瓦勒伦加</t>
+  </si>
+  <si>
+    <t>俄超</t>
+  </si>
+  <si>
+    <t>苏维埃之翼</t>
+  </si>
+  <si>
+    <t>巴蒂卡</t>
+  </si>
+  <si>
+    <t>马里迪莫</t>
+  </si>
+  <si>
+    <t>卡萨皮亚</t>
+  </si>
+  <si>
+    <t>特尔斯达</t>
+  </si>
+  <si>
+    <t>莫斯科火车头</t>
+  </si>
+  <si>
+    <t>阿克伦托</t>
+  </si>
+  <si>
+    <t>瑞士超</t>
+  </si>
+  <si>
+    <t>洛桑</t>
+  </si>
+  <si>
+    <t>年轻人</t>
+  </si>
+  <si>
+    <t>标准列日</t>
+  </si>
+  <si>
+    <t>色格拉布鲁日</t>
+  </si>
+  <si>
+    <t>前进之鹰</t>
+  </si>
+  <si>
+    <t>威廉二世</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>吉马良斯</t>
+  </si>
+  <si>
+    <t>阿罗卡</t>
+  </si>
+  <si>
+    <t>莫斯科中央陆军</t>
+  </si>
+  <si>
+    <t>罗斯托夫</t>
+  </si>
+  <si>
+    <t>埃因霍温</t>
+  </si>
+  <si>
+    <t>福图纳锡塔德</t>
+  </si>
+  <si>
+    <t>主让2/2.5</t>
+  </si>
+  <si>
+    <t>沃尔夫斯堡</t>
+  </si>
+  <si>
+    <t>凯泽斯劳滕</t>
+  </si>
+  <si>
+    <t>塞尔维特</t>
+  </si>
+  <si>
+    <t>草蜢</t>
+  </si>
+  <si>
+    <t>阿尔克马尔</t>
+  </si>
+  <si>
+    <t>海牙</t>
+  </si>
+  <si>
+    <t>阿马多拉</t>
+  </si>
+  <si>
+    <t>葡萄牙体育</t>
+  </si>
+  <si>
+    <t>博卡青年</t>
+  </si>
+  <si>
+    <t>萨斯菲尔德</t>
+  </si>
+  <si>
+    <t>主胜+小球</t>
+  </si>
+  <si>
+    <t>阿根廷独立</t>
+  </si>
+  <si>
+    <t>普拉腾斯</t>
+  </si>
+  <si>
+    <t>浅盘陷阱</t>
+  </si>
+  <si>
+    <t>东京绿茵</t>
+  </si>
+  <si>
+    <t>川崎前锋</t>
+  </si>
+  <si>
+    <t>东京绿茵+0/0.5</t>
+  </si>
+  <si>
+    <t>TPS土尔库</t>
+  </si>
+  <si>
+    <t>古比斯-1/1.5 + 大球</t>
+  </si>
+  <si>
+    <t>方向+大小球双错</t>
+  </si>
+  <si>
+    <t>哈马比-1/1.5</t>
+  </si>
+  <si>
+    <t>马尔默-1</t>
+  </si>
+  <si>
+    <t>兹沃勒</t>
+  </si>
+  <si>
+    <t>兹沃勒+1胜</t>
+  </si>
+  <si>
+    <t>客胜穿盘</t>
+  </si>
+  <si>
+    <t>鹿斯巴达</t>
+  </si>
+  <si>
+    <t>费耶诺德</t>
+  </si>
+  <si>
+    <t>鹿斯巴达+1胜</t>
+  </si>
+  <si>
+    <t>巴西甲</t>
+  </si>
+  <si>
+    <t>克鲁塞罗</t>
+  </si>
+  <si>
+    <t>米拉索</t>
+  </si>
+  <si>
+    <t>克鲁塞罗-0.5/1</t>
+  </si>
+  <si>
+    <t>主场失准</t>
+  </si>
+  <si>
+    <t>圣彼得堡泽尼特</t>
+  </si>
+  <si>
+    <t>罗迪纳莫斯科</t>
+  </si>
+  <si>
+    <t>拉路维尔</t>
+  </si>
+  <si>
+    <t>安德莱赫特-0.5/1</t>
+  </si>
+  <si>
+    <t>安特卫普</t>
+  </si>
+  <si>
+    <t>华斯兰德</t>
+  </si>
+  <si>
+    <t>安特卫普-0.5</t>
+  </si>
+  <si>
+    <t>帕尔梅拉斯</t>
+  </si>
+  <si>
+    <t>帕尔梅拉斯-0.5/1</t>
+  </si>
+  <si>
+    <t>弗拉门戈</t>
+  </si>
+  <si>
+    <t>东京绿茵 +0/0.5</t>
+  </si>
+  <si>
+    <t>B级</t>
+  </si>
+  <si>
+    <t>古比斯 -1/1.5 + 大球</t>
+  </si>
+  <si>
+    <t>错</t>
+  </si>
+  <si>
+    <t>A级</t>
+  </si>
+  <si>
+    <t>数据面碾压但未能赢球</t>
+  </si>
+  <si>
+    <t>哈马比 -1/1.5</t>
+  </si>
+  <si>
+    <t>对</t>
+  </si>
+  <si>
+    <t>马尔默 -1</t>
+  </si>
+  <si>
+    <t>冷门，降盘信号被误读</t>
+  </si>
+  <si>
+    <t>兹沃勒 +1胜</t>
+  </si>
+  <si>
+    <t>客队穿盘，首轮大球未现</t>
+  </si>
+  <si>
+    <t>鹿斯巴达 +1胜</t>
+  </si>
+  <si>
+    <t>安德莱赫特 -0.5/1</t>
+  </si>
+  <si>
+    <t>安特卫普 -0.5</t>
+  </si>
+  <si>
+    <t>帕尔梅拉斯 -0.5/1</t>
   </si>
 </sst>
 </file>
@@ -2175,7 +2811,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2202,6 +2838,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2728,10 +3367,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I214"/>
+  <dimension ref="A1:I311"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.875" style="3"/>
+    <col min="1" max="1" width="16" style="3"/>
     <col min="2" max="6" width="9" style="3"/>
     <col min="7" max="7" width="10.375" style="4"/>
     <col min="8" max="8" width="9" style="4"/>
@@ -8942,6 +9581,2819 @@
       </c>
       <c r="I214" s="3" t="s">
         <v>326</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
+      <c r="A215" s="5">
+        <v>46241</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="G215" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H215" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
+      <c r="A216" s="5">
+        <v>46241.0416666667</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G216" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H216" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
+      <c r="A217" s="5">
+        <v>46241.0416666667</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G217" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H217" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
+      <c r="A218" s="5">
+        <v>46241.0416666667</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G218" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H218" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I218" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
+      <c r="A219" s="5">
+        <v>46241.0625</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G219" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H219" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
+      <c r="A220" s="5">
+        <v>46241.0625</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G220" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H220" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I220" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
+      <c r="A221" s="5">
+        <v>46241.0625</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G221" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H221" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
+      <c r="A222" s="5">
+        <v>46241.0625</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G222" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H222" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223" s="5">
+        <v>46241.0833333333</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="G223" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H223" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
+      <c r="A224" s="5">
+        <v>46241.0833333333</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G224" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H224" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
+      <c r="A225" s="5">
+        <v>46241.0833333333</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G225" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H225" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
+      <c r="A226" s="5">
+        <v>46241.0833333333</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H226" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I226" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
+      <c r="A227" s="5">
+        <v>46241.0833333333</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G227" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="H227" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
+      <c r="A228" s="5">
+        <v>46241.0833333333</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G228" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H228" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
+      <c r="A229" s="5">
+        <v>46241.09375</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G229" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H229" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
+      <c r="A230" s="5">
+        <v>46241.09375</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G230" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H230" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
+      <c r="A231" s="5">
+        <v>46241.1041666667</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="G231" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H231" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
+      <c r="A232" s="5">
+        <v>46241.1041666667</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G232" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H232" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
+      <c r="A233" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G233" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H233" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
+      <c r="A234" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G234" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H234" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
+      <c r="A235" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G235" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H235" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
+      <c r="A236" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G236" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H236" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
+      <c r="A237" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G237" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H237" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
+      <c r="A238" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G238" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H238" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
+      <c r="A239" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G239" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H239" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I239" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
+      <c r="A240" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G240" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H240" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
+      <c r="A241" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G241" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H241" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
+      <c r="A242" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G242" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H242" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I242" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9">
+      <c r="A243" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G243" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H243" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
+      <c r="A244" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G244" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H244" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I244" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9">
+      <c r="A245" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G245" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H245" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9">
+      <c r="A246" s="5">
+        <v>46241.1145833333</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G246" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H246" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I246" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9">
+      <c r="A247" s="5">
+        <v>46241.125</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G247" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H247" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
+      <c r="A248" s="5">
+        <v>46241.1354166667</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="G248" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H248" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I248" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
+      <c r="A249" s="5">
+        <v>46241.2708333333</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G249" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H249" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I249" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
+      <c r="A250" s="5">
+        <v>46241.2708333333</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G250" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H250" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I250" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
+      <c r="A251" s="5">
+        <v>46241.3125</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G251" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H251" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I251" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
+      <c r="A252" s="5">
+        <v>46241.3645833333</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G252" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="H252" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I252" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9">
+      <c r="A253" s="5">
+        <v>46241.7673611111</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="G253" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="H253" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I253" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
+      <c r="A254" s="5">
+        <v>46241.7708333333</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="G254" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="H254" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I254" s="3" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
+      <c r="A255" s="5">
+        <v>46241.875</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="G255" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H255" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I255" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9">
+      <c r="A256" s="5">
+        <v>46241.875</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="G256" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H256" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I256" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
+      <c r="A257" s="5">
+        <v>46242</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G257" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H257" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I257" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
+      <c r="A258" s="5">
+        <v>46242</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G258" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H258" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I258" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
+      <c r="A259" s="5">
+        <v>46242</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G259" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H259" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I259" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
+      <c r="A260" s="5">
+        <v>46242</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G260" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H260" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I260" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
+      <c r="A261" s="5">
+        <v>46242.1145833333</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G261" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H261" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I261" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
+      <c r="A262" s="5">
+        <v>46242.1145833333</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G262" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H262" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I262" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
+      <c r="A263" s="5">
+        <v>46242.1145833333</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="G263" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H263" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I263" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
+      <c r="A264" s="5">
+        <v>46242.1354166667</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G264" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H264" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I264" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
+      <c r="A265" s="5">
+        <v>46242.75</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G265" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H265" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I265" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
+      <c r="A266" s="5">
+        <v>46242.75</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G266" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H266" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I266" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
+      <c r="A267" s="5">
+        <v>46242.75</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G267" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H267" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I267" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
+      <c r="A268" s="5">
+        <v>46242.75</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G268" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H268" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I268" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9">
+      <c r="A269" s="5">
+        <v>46242.7604166667</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G269" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H269" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I269" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9">
+      <c r="A270" s="5">
+        <v>46242.7916666667</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G270" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H270" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I270" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9">
+      <c r="A271" s="5">
+        <v>46242.7916666667</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G271" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="H271" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I271" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9">
+      <c r="A272" s="5">
+        <v>46242.7916666667</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G272" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H272" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I272" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9">
+      <c r="A273" s="5">
+        <v>46242.7916666667</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G273" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H273" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I273" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9">
+      <c r="A274" s="5">
+        <v>46242.7916666667</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G274" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H274" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I274" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9">
+      <c r="A275" s="5">
+        <v>46242.7916666667</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G275" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H275" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I275" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9">
+      <c r="A276" s="5">
+        <v>46242.8333333333</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G276" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H276" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I276" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9">
+      <c r="A277" s="5">
+        <v>46242.8541666667</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G277" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H277" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I277" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9">
+      <c r="A278" s="5">
+        <v>46242.875</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G278" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="H278" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I278" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9">
+      <c r="A279" s="5">
+        <v>46242.9166666667</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G279" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H279" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I279" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9">
+      <c r="A280" s="5">
+        <v>46242.9375</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G280" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H280" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I280" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9">
+      <c r="A281" s="5">
+        <v>46242.9375</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G281" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H281" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I281" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9">
+      <c r="A282" s="5">
+        <v>46242.9583333333</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G282" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H282" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I282" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9">
+      <c r="A283" s="5">
+        <v>46242.9791666667</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G283" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H283" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I283" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9">
+      <c r="A284" s="5">
+        <v>46243</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="E284" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G284" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H284" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I284" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9">
+      <c r="A285" s="5">
+        <v>46243</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E285" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F285" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G285" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H285" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I285" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9">
+      <c r="A286" s="5">
+        <v>46243</v>
+      </c>
+      <c r="B286" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E286" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F286" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G286" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H286" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I286" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9">
+      <c r="A287" s="5">
+        <v>46243.0104166667</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="E287" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F287" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G287" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H287" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I287" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9">
+      <c r="A288" s="5">
+        <v>46243.03125</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C288" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G288" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="H288" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I288" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9">
+      <c r="A289" s="5">
+        <v>46243.0416666667</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C289" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G289" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H289" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I289" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9">
+      <c r="A290" s="5">
+        <v>46243.0625</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C290" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="E290" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="G290" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H290" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I290" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9">
+      <c r="A291" s="5">
+        <v>46243.0833333333</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="F291" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G291" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H291" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I291" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9">
+      <c r="A292" s="5">
+        <v>46243.1041666667</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="E292" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G292" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H292" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I292" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9">
+      <c r="A293" s="5">
+        <v>46243.1041666667</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G293" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H293" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I293" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9">
+      <c r="A294" s="5">
+        <v>46243.1145833333</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E294" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G294" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H294" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I294" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9">
+      <c r="A295" s="5">
+        <v>46243.1145833333</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="E295" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F295" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="G295" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H295" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I295" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9">
+      <c r="A296" s="5">
+        <v>46243.125</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="E296" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G296" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H296" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I296" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9">
+      <c r="A297" s="5">
+        <v>46243.1458333333</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G297" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H297" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I297" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9">
+      <c r="A298" s="5">
+        <v>46243.2604166667</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C298" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="G298" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="H298" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I298" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9">
+      <c r="A299" s="5">
+        <v>46243.3541666667</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G299" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H299" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I299" s="3" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9">
+      <c r="A300" s="9">
+        <v>46243.7083333333</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="E300" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="G300" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H300" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I300" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9">
+      <c r="A301" s="9">
+        <v>46243.8333333333</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="E301" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="G301" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H301" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I301" s="3" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9">
+      <c r="A302" s="9">
+        <v>46243.8333333333</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C302" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E302" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="G302" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H302" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I302" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9">
+      <c r="A303" s="9">
+        <v>46243.8333333333</v>
+      </c>
+      <c r="B303" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C303" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="G303" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H303" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I303" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9">
+      <c r="A304" s="9">
+        <v>46243.8541666667</v>
+      </c>
+      <c r="B304" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C304" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="E304" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="G304" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H304" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I304" s="3" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9">
+      <c r="A305" s="9">
+        <v>46243.8541666667</v>
+      </c>
+      <c r="B305" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C305" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="D305" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="E305" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="G305" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H305" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I305" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9">
+      <c r="A306" s="9">
+        <v>46243.9166666667</v>
+      </c>
+      <c r="B306" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F306" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="G306" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H306" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I306" s="3" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9">
+      <c r="A307" s="9">
+        <v>46243.9166666667</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="D307" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G307" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H307" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I307" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9">
+      <c r="A308" s="9">
+        <v>46243.0208333333</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C308" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="E308" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F308" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="G308" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H308" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I308" s="3" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9">
+      <c r="A309" s="9">
+        <v>46243.0520833333</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="E309" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F309" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="G309" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H309" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I309" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9">
+      <c r="A310" s="9">
+        <v>46243.125</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="E310" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F310" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="G310" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H310" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I310" s="3" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9">
+      <c r="A311" s="9">
+        <v>46243.2708333333</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E311" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F311" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G311" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H311" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I311" s="3" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -8959,8 +12411,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="14.875"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
@@ -9308,6 +12763,439 @@
       </c>
       <c r="I12" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>481</v>
+      </c>
+      <c r="G13" s="2">
+        <v>46055</v>
+      </c>
+      <c r="H13" t="s">
+        <v>482</v>
+      </c>
+      <c r="I13" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1">
+        <v>46241.0416666667</v>
+      </c>
+      <c r="B14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" t="s">
+        <v>484</v>
+      </c>
+      <c r="D14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" t="s">
+        <v>362</v>
+      </c>
+      <c r="G14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1">
+        <v>46241.0833333333</v>
+      </c>
+      <c r="B15" t="s">
+        <v>502</v>
+      </c>
+      <c r="C15" t="s">
+        <v>503</v>
+      </c>
+      <c r="D15" t="s">
+        <v>504</v>
+      </c>
+      <c r="E15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" t="s">
+        <v>505</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="1">
+        <v>46241.1041666667</v>
+      </c>
+      <c r="B16" t="s">
+        <v>522</v>
+      </c>
+      <c r="C16" t="s">
+        <v>523</v>
+      </c>
+      <c r="D16" t="s">
+        <v>524</v>
+      </c>
+      <c r="E16" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" t="s">
+        <v>525</v>
+      </c>
+      <c r="G16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="1">
+        <v>46241.1354166667</v>
+      </c>
+      <c r="B17" t="s">
+        <v>559</v>
+      </c>
+      <c r="C17" t="s">
+        <v>560</v>
+      </c>
+      <c r="D17" t="s">
+        <v>561</v>
+      </c>
+      <c r="E17" t="s">
+        <v>353</v>
+      </c>
+      <c r="F17" t="s">
+        <v>562</v>
+      </c>
+      <c r="G17" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B18" t="s">
+        <v>572</v>
+      </c>
+      <c r="C18" t="s">
+        <v>648</v>
+      </c>
+      <c r="D18" t="s">
+        <v>649</v>
+      </c>
+      <c r="E18" t="s">
+        <v>677</v>
+      </c>
+      <c r="F18" s="2">
+        <v>46023</v>
+      </c>
+      <c r="G18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" t="s">
+        <v>678</v>
+      </c>
+      <c r="J18" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" t="s">
+        <v>651</v>
+      </c>
+      <c r="E19" t="s">
+        <v>679</v>
+      </c>
+      <c r="F19" s="2">
+        <v>46023</v>
+      </c>
+      <c r="G19" t="s">
+        <v>680</v>
+      </c>
+      <c r="H19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" t="s">
+        <v>681</v>
+      </c>
+      <c r="J19" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" t="s">
+        <v>301</v>
+      </c>
+      <c r="E20" t="s">
+        <v>683</v>
+      </c>
+      <c r="F20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" t="s">
+        <v>684</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" t="s">
+        <v>681</v>
+      </c>
+      <c r="J20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" t="s">
+        <v>150</v>
+      </c>
+      <c r="E21" t="s">
+        <v>685</v>
+      </c>
+      <c r="F21" s="2">
+        <v>46024</v>
+      </c>
+      <c r="G21" t="s">
+        <v>680</v>
+      </c>
+      <c r="H21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" t="s">
+        <v>681</v>
+      </c>
+      <c r="J21" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B22" t="s">
+        <v>502</v>
+      </c>
+      <c r="C22" t="s">
+        <v>656</v>
+      </c>
+      <c r="D22" t="s">
+        <v>450</v>
+      </c>
+      <c r="E22" t="s">
+        <v>687</v>
+      </c>
+      <c r="F22" t="s">
+        <v>156</v>
+      </c>
+      <c r="G22" t="s">
+        <v>680</v>
+      </c>
+      <c r="H22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" t="s">
+        <v>681</v>
+      </c>
+      <c r="J22" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B23" t="s">
+        <v>502</v>
+      </c>
+      <c r="C23" t="s">
+        <v>659</v>
+      </c>
+      <c r="D23" t="s">
+        <v>660</v>
+      </c>
+      <c r="E23" t="s">
+        <v>689</v>
+      </c>
+      <c r="F23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" t="s">
+        <v>684</v>
+      </c>
+      <c r="H23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" t="s">
+        <v>678</v>
+      </c>
+      <c r="J23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B24" t="s">
+        <v>529</v>
+      </c>
+      <c r="C24" t="s">
+        <v>280</v>
+      </c>
+      <c r="D24" t="s">
+        <v>669</v>
+      </c>
+      <c r="E24" t="s">
+        <v>690</v>
+      </c>
+      <c r="F24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" t="s">
+        <v>680</v>
+      </c>
+      <c r="H24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" t="s">
+        <v>681</v>
+      </c>
+      <c r="J24" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B25" t="s">
+        <v>529</v>
+      </c>
+      <c r="C25" t="s">
+        <v>671</v>
+      </c>
+      <c r="D25" t="s">
+        <v>672</v>
+      </c>
+      <c r="E25" t="s">
+        <v>691</v>
+      </c>
+      <c r="F25" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G25" t="s">
+        <v>684</v>
+      </c>
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" t="s">
+        <v>681</v>
+      </c>
+      <c r="J25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B26" t="s">
+        <v>662</v>
+      </c>
+      <c r="C26" t="s">
+        <v>674</v>
+      </c>
+      <c r="D26" t="s">
+        <v>480</v>
+      </c>
+      <c r="E26" t="s">
+        <v>692</v>
+      </c>
+      <c r="F26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" t="s">
+        <v>680</v>
+      </c>
+      <c r="H26" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" t="s">
+        <v>681</v>
+      </c>
+      <c r="J26" t="s">
+        <v>666</v>
       </c>
     </row>
   </sheetData>

--- a/数据库.xlsx
+++ b/数据库.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3018" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3438" uniqueCount="791">
   <si>
     <t>日期</t>
   </si>
@@ -2246,12 +2246,153 @@
     <t>主队主场逆转</t>
   </si>
   <si>
+    <t>柏太阳神</t>
+  </si>
+  <si>
+    <t>1:3</t>
+  </si>
+  <si>
+    <t>客让半一低水命中</t>
+  </si>
+  <si>
+    <t>高水阻上失败</t>
+  </si>
+  <si>
+    <t>低水+盘口反常命中</t>
+  </si>
+  <si>
+    <t>3:0</t>
+  </si>
+  <si>
+    <t>主场低水穿盘</t>
+  </si>
+  <si>
+    <t>3:3</t>
+  </si>
+  <si>
+    <t>比甲中游对决平局</t>
+  </si>
+  <si>
+    <t>竞技俱乐部</t>
+  </si>
+  <si>
+    <t>0:1</t>
+  </si>
+  <si>
+    <t>南美主场权重仍被低估</t>
+  </si>
+  <si>
+    <t>主场让球合理</t>
+  </si>
+  <si>
+    <t>长崎成功丸</t>
+  </si>
+  <si>
+    <t>1:0</t>
+  </si>
+  <si>
+    <t>低排名让高排名</t>
+  </si>
+  <si>
+    <t>0:4</t>
+  </si>
+  <si>
+    <t>客让半一穿盘</t>
+  </si>
+  <si>
+    <t>1:4</t>
+  </si>
+  <si>
+    <t>客让0.5低水</t>
+  </si>
+  <si>
+    <t>4:2</t>
+  </si>
+  <si>
+    <t>榜首主场命中</t>
+  </si>
+  <si>
+    <t>0:0</t>
+  </si>
+  <si>
+    <t>客让低水未穿</t>
+  </si>
+  <si>
+    <t>亨克</t>
+  </si>
+  <si>
+    <t>3:2</t>
+  </si>
+  <si>
+    <t>赢1球输一半</t>
+  </si>
+  <si>
+    <t>旧海弗莱鲁汶</t>
+  </si>
+  <si>
+    <t>0:3</t>
+  </si>
+  <si>
+    <t>客让深盘穿盘</t>
+  </si>
+  <si>
+    <t>弗鲁米嫩塞</t>
+  </si>
+  <si>
+    <t>客队超低水诱盘</t>
+  </si>
+  <si>
+    <t>客让深盘高水输球</t>
+  </si>
+  <si>
+    <t>客队低水平手穿盘</t>
+  </si>
+  <si>
+    <t>榜首客场超低水命中</t>
+  </si>
+  <si>
+    <t>1:5</t>
+  </si>
+  <si>
+    <t>格雷米奥</t>
+  </si>
+  <si>
+    <t>主场低水命中</t>
+  </si>
+  <si>
+    <t>挪超主场低水</t>
+  </si>
+  <si>
+    <t>客场低水受让翻车</t>
+  </si>
+  <si>
+    <t>沙勒罗瓦</t>
+  </si>
+  <si>
+    <t>客场浅盘低水命中</t>
+  </si>
+  <si>
+    <t>客场受让低水</t>
+  </si>
+  <si>
+    <t>2:3</t>
+  </si>
+  <si>
+    <t>客场浅盘命中</t>
+  </si>
+  <si>
+    <t>萨尔米安杜</t>
+  </si>
+  <si>
+    <t>主场爆冷，客队超低水诱盘</t>
+  </si>
+  <si>
+    <t>欧战干扰降仓仍输盘</t>
+  </si>
+  <si>
     <t>推荐方向</t>
   </si>
   <si>
-    <t>0:0</t>
-  </si>
-  <si>
     <t>错</t>
   </si>
   <si>
@@ -2261,18 +2402,9 @@
     <t>对</t>
   </si>
   <si>
-    <t>1:0</t>
-  </si>
-  <si>
-    <t>0:1</t>
-  </si>
-  <si>
     <t>2:2</t>
   </si>
   <si>
-    <t>0:4</t>
-  </si>
-  <si>
     <t>1:1</t>
   </si>
   <si>
@@ -2282,9 +2414,6 @@
     <t>古比斯-1/1.5+大球</t>
   </si>
   <si>
-    <t>3:0</t>
-  </si>
-  <si>
     <t>0:2</t>
   </si>
   <si>
@@ -2307,6 +2436,36 @@
   </si>
   <si>
     <t>南美主场权重低估</t>
+  </si>
+  <si>
+    <t>客队-0.5/1</t>
+  </si>
+  <si>
+    <t>主队-0.5/1</t>
+  </si>
+  <si>
+    <t>低水+盘口反常</t>
+  </si>
+  <si>
+    <t>比甲中游平局</t>
+  </si>
+  <si>
+    <t>南美主场低估</t>
+  </si>
+  <si>
+    <t>榜首主场翻车</t>
+  </si>
+  <si>
+    <t>榜首客场超低水</t>
+  </si>
+  <si>
+    <t>主场低水</t>
+  </si>
+  <si>
+    <t>客场浅盘低水</t>
+  </si>
+  <si>
+    <t>客场浅盘</t>
   </si>
 </sst>
 </file>
@@ -3505,7 +3664,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I339"/>
+  <dimension ref="A1:I367"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" style="5"/>
@@ -13344,6 +13503,818 @@
       </c>
       <c r="I339" s="5" t="s">
         <v>716</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9">
+      <c r="A340" s="7">
+        <v>46248</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="D340" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="E340" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F340" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G340" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="H340" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I340" s="5" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9">
+      <c r="A341" s="7">
+        <v>46248</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D341" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="E341" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F341" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G341" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="H341" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I341" s="5" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9">
+      <c r="A342" s="7">
+        <v>46248</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C342" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D342" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E342" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F342" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G342" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="H342" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I342" s="5" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9">
+      <c r="A343" s="7">
+        <v>46248</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C343" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D343" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E343" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F343" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G343" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="H343" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I343" s="5" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9">
+      <c r="A344" s="7">
+        <v>46248</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C344" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D344" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="E344" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F344" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G344" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="H344" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I344" s="5" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9">
+      <c r="A345" s="7">
+        <v>46248</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C345" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="D345" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="E345" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F345" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G345" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H345" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I345" s="5" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9">
+      <c r="A346" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C346" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="D346" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="E346" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F346" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G346" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="H346" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I346" s="5" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9">
+      <c r="A347" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B347" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="D347" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="E347" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F347" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G347" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="H347" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I347" s="5" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9">
+      <c r="A348" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C348" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="D348" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="E348" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F348" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G348" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="H348" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I348" s="5" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9">
+      <c r="A349" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C349" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="D349" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="E349" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F349" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G349" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="H349" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I349" s="5" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9">
+      <c r="A350" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C350" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D350" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E350" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F350" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G350" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="H350" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I350" s="5" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9">
+      <c r="A351" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D351" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E351" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F351" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G351" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="H351" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I351" s="5" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9">
+      <c r="A352" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="D352" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="E352" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F352" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G352" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="H352" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I352" s="5" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9">
+      <c r="A353" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C353" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="D353" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="E353" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F353" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G353" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="H353" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I353" s="5" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9">
+      <c r="A354" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="C354" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D354" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="E354" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F354" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G354" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="H354" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I354" s="5" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9">
+      <c r="A355" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C355" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D355" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E355" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F355" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G355" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="H355" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I355" s="5" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9">
+      <c r="A356" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C356" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="D356" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="E356" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F356" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G356" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="H356" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I356" s="5" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9">
+      <c r="A357" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B357" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D357" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E357" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F357" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G357" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="H357" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I357" s="5" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9">
+      <c r="A358" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="C358" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="D358" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="E358" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F358" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G358" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="H358" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I358" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9">
+      <c r="A359" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B359" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D359" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="E359" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F359" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G359" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="H359" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I359" s="5" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9">
+      <c r="A360" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C360" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D360" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E360" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F360" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G360" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="H360" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I360" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9">
+      <c r="A361" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C361" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D361" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E361" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F361" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G361" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="H361" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I361" s="5" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9">
+      <c r="A362" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B362" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="C362" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D362" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="E362" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F362" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G362" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="H362" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I362" s="5" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9">
+      <c r="A363" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B363" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C363" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="D363" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="E363" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F363" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G363" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H363" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I363" s="5" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9">
+      <c r="A364" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B364" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C364" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D364" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E364" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F364" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G364" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H364" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I364" s="5" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9">
+      <c r="A365" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C365" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D365" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E365" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F365" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G365" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="H365" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I365" s="5" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9">
+      <c r="A366" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B366" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C366" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="D366" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="E366" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F366" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G366" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="H366" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I366" s="5" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9">
+      <c r="A367" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C367" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D367" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E367" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F367" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G367" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="H367" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I367" s="5" t="s">
+        <v>764</v>
       </c>
     </row>
   </sheetData>
@@ -13361,7 +14332,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.875"/>
@@ -13382,7 +14353,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>717</v>
+        <v>765</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
@@ -13411,10 +14382,10 @@
         <v>354</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H2" t="s">
         <v>30</v>
@@ -13440,7 +14411,7 @@
         <v>715</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H3" t="s">
         <v>30</v>
@@ -13463,10 +14434,10 @@
         <v>358</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>720</v>
+        <v>767</v>
       </c>
       <c r="G4" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -13489,10 +14460,10 @@
         <v>362</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="G5" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H5" t="s">
         <v>30</v>
@@ -13515,10 +14486,10 @@
         <v>362</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="G6" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -13541,10 +14512,10 @@
         <v>362</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G7" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H7" t="s">
         <v>448</v>
@@ -13567,10 +14538,10 @@
         <v>424</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -13596,7 +14567,7 @@
         <v>715</v>
       </c>
       <c r="G9" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H9" t="s">
         <v>241</v>
@@ -13619,10 +14590,10 @@
         <v>410</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="G10" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H10" t="s">
         <v>23</v>
@@ -13645,10 +14616,10 @@
         <v>402</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -13674,7 +14645,7 @@
         <v>715</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -13697,10 +14668,10 @@
         <v>481</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>724</v>
+        <v>769</v>
       </c>
       <c r="G13" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H13" t="s">
         <v>483</v>
@@ -13723,10 +14694,10 @@
         <v>362</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G14" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H14" t="s">
         <v>485</v>
@@ -13749,10 +14720,10 @@
         <v>505</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="G15" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H15" t="s">
         <v>483</v>
@@ -13775,10 +14746,10 @@
         <v>525</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H16" t="s">
         <v>483</v>
@@ -13801,10 +14772,10 @@
         <v>562</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>726</v>
+        <v>770</v>
       </c>
       <c r="G17" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H17" t="s">
         <v>483</v>
@@ -13827,10 +14798,10 @@
         <v>650</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>726</v>
+        <v>770</v>
       </c>
       <c r="G18" t="s">
-        <v>727</v>
+        <v>771</v>
       </c>
       <c r="H18" t="s">
         <v>324</v>
@@ -13850,13 +14821,13 @@
         <v>651</v>
       </c>
       <c r="E19" t="s">
-        <v>728</v>
+        <v>772</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>726</v>
+        <v>770</v>
       </c>
       <c r="G19" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H19" t="s">
         <v>653</v>
@@ -13879,10 +14850,10 @@
         <v>654</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="G20" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -13908,7 +14879,7 @@
         <v>709</v>
       </c>
       <c r="G21" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H21" t="s">
         <v>30</v>
@@ -13931,13 +14902,13 @@
         <v>657</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>730</v>
+        <v>773</v>
       </c>
       <c r="G22" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H22" t="s">
-        <v>731</v>
+        <v>774</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -13957,10 +14928,10 @@
         <v>661</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="G23" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H23" t="s">
         <v>124</v>
@@ -13983,10 +14954,10 @@
         <v>670</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="G24" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H24" t="s">
         <v>666</v>
@@ -14012,7 +14983,7 @@
         <v>715</v>
       </c>
       <c r="G25" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -14035,10 +15006,10 @@
         <v>675</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="G26" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H26" t="s">
         <v>666</v>
@@ -14061,13 +15032,13 @@
         <v>677</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>724</v>
+        <v>769</v>
       </c>
       <c r="G27" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H27" t="s">
-        <v>732</v>
+        <v>775</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -14087,10 +15058,10 @@
         <v>658</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="G28" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H28" t="s">
         <v>679</v>
@@ -14113,10 +15084,10 @@
         <v>346</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>730</v>
+        <v>773</v>
       </c>
       <c r="G29" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H29" t="s">
         <v>682</v>
@@ -14142,7 +15113,7 @@
         <v>709</v>
       </c>
       <c r="G30" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H30" t="s">
         <v>684</v>
@@ -14165,13 +15136,13 @@
         <v>362</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>730</v>
+        <v>773</v>
       </c>
       <c r="G31" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H31" t="s">
-        <v>733</v>
+        <v>776</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -14191,10 +15162,10 @@
         <v>402</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G32" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H32" t="s">
         <v>692</v>
@@ -14217,10 +15188,10 @@
         <v>362</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>724</v>
+        <v>769</v>
       </c>
       <c r="G33" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H33" t="s">
         <v>693</v>
@@ -14243,13 +15214,13 @@
         <v>362</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>726</v>
+        <v>770</v>
       </c>
       <c r="G34" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H34" t="s">
-        <v>734</v>
+        <v>777</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -14269,13 +15240,13 @@
         <v>402</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>726</v>
+        <v>770</v>
       </c>
       <c r="G35" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H35" t="s">
-        <v>735</v>
+        <v>778</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -14295,10 +15266,10 @@
         <v>424</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>726</v>
+        <v>770</v>
       </c>
       <c r="G36" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H36" t="s">
         <v>696</v>
@@ -14321,13 +15292,13 @@
         <v>402</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G37" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H37" t="s">
-        <v>735</v>
+        <v>778</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -14347,10 +15318,10 @@
         <v>402</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="G38" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H38" t="s">
         <v>703</v>
@@ -14376,10 +15347,10 @@
         <v>712</v>
       </c>
       <c r="G39" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H39" t="s">
-        <v>736</v>
+        <v>779</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -14402,10 +15373,10 @@
         <v>714</v>
       </c>
       <c r="G40" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H40" t="s">
-        <v>736</v>
+        <v>779</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -14428,10 +15399,10 @@
         <v>707</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H41" t="s">
-        <v>737</v>
+        <v>780</v>
       </c>
       <c r="I41" t="s">
         <v>713</v>
@@ -14457,7 +15428,7 @@
         <v>709</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H42" t="s">
         <v>702</v>
@@ -14486,13 +15457,741 @@
         <v>709</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="H43" t="s">
         <v>711</v>
       </c>
       <c r="I43" t="s">
         <v>716</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B44" t="s">
+        <v>572</v>
+      </c>
+      <c r="C44" t="s">
+        <v>648</v>
+      </c>
+      <c r="D44" t="s">
+        <v>717</v>
+      </c>
+      <c r="E44" t="s">
+        <v>781</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="H44" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B45" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" t="s">
+        <v>651</v>
+      </c>
+      <c r="E45" t="s">
+        <v>782</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="H45" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B46" t="s">
+        <v>152</v>
+      </c>
+      <c r="C46" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" t="s">
+        <v>710</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="H46" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B47" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" t="s">
+        <v>239</v>
+      </c>
+      <c r="D47" t="s">
+        <v>149</v>
+      </c>
+      <c r="E47" t="s">
+        <v>710</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="G47" t="s">
+        <v>768</v>
+      </c>
+      <c r="H47" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B48" t="s">
+        <v>529</v>
+      </c>
+      <c r="C48" t="s">
+        <v>623</v>
+      </c>
+      <c r="D48" t="s">
+        <v>588</v>
+      </c>
+      <c r="E48" t="s">
+        <v>710</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="G48" t="s">
+        <v>766</v>
+      </c>
+      <c r="H48" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B49" t="s">
+        <v>363</v>
+      </c>
+      <c r="C49" t="s">
+        <v>726</v>
+      </c>
+      <c r="D49" t="s">
+        <v>680</v>
+      </c>
+      <c r="E49" t="s">
+        <v>362</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="G49" t="s">
+        <v>766</v>
+      </c>
+      <c r="H49" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B50" t="s">
+        <v>572</v>
+      </c>
+      <c r="C50" t="s">
+        <v>574</v>
+      </c>
+      <c r="D50" t="s">
+        <v>600</v>
+      </c>
+      <c r="E50" t="s">
+        <v>362</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="G50" t="s">
+        <v>768</v>
+      </c>
+      <c r="H50" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B51" t="s">
+        <v>572</v>
+      </c>
+      <c r="C51" t="s">
+        <v>597</v>
+      </c>
+      <c r="D51" t="s">
+        <v>730</v>
+      </c>
+      <c r="E51" t="s">
+        <v>710</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="G51" t="s">
+        <v>768</v>
+      </c>
+      <c r="H51" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B52" t="s">
+        <v>572</v>
+      </c>
+      <c r="C52" t="s">
+        <v>603</v>
+      </c>
+      <c r="D52" t="s">
+        <v>599</v>
+      </c>
+      <c r="E52" t="s">
+        <v>424</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="G52" t="s">
+        <v>768</v>
+      </c>
+      <c r="H52" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B53" t="s">
+        <v>572</v>
+      </c>
+      <c r="C53" t="s">
+        <v>577</v>
+      </c>
+      <c r="D53" t="s">
+        <v>602</v>
+      </c>
+      <c r="E53" t="s">
+        <v>424</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="G53" t="s">
+        <v>768</v>
+      </c>
+      <c r="H53" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B54" t="s">
+        <v>91</v>
+      </c>
+      <c r="C54" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" t="s">
+        <v>125</v>
+      </c>
+      <c r="E54" t="s">
+        <v>362</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="G54" t="s">
+        <v>766</v>
+      </c>
+      <c r="H54" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B55" t="s">
+        <v>152</v>
+      </c>
+      <c r="C55" t="s">
+        <v>153</v>
+      </c>
+      <c r="D55" t="s">
+        <v>194</v>
+      </c>
+      <c r="E55" t="s">
+        <v>424</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="G55" t="s">
+        <v>766</v>
+      </c>
+      <c r="H55" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B56" t="s">
+        <v>529</v>
+      </c>
+      <c r="C56" t="s">
+        <v>741</v>
+      </c>
+      <c r="D56" t="s">
+        <v>591</v>
+      </c>
+      <c r="E56" t="s">
+        <v>362</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="G56" t="s">
+        <v>768</v>
+      </c>
+      <c r="H56" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B57" t="s">
+        <v>529</v>
+      </c>
+      <c r="C57" t="s">
+        <v>744</v>
+      </c>
+      <c r="D57" t="s">
+        <v>530</v>
+      </c>
+      <c r="E57" t="s">
+        <v>424</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="G57" t="s">
+        <v>768</v>
+      </c>
+      <c r="H57" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B58" t="s">
+        <v>662</v>
+      </c>
+      <c r="C58" t="s">
+        <v>747</v>
+      </c>
+      <c r="D58" t="s">
+        <v>674</v>
+      </c>
+      <c r="E58" t="s">
+        <v>402</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="G58" t="s">
+        <v>766</v>
+      </c>
+      <c r="H58" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B59" t="s">
+        <v>130</v>
+      </c>
+      <c r="C59" t="s">
+        <v>138</v>
+      </c>
+      <c r="D59" t="s">
+        <v>211</v>
+      </c>
+      <c r="E59" t="s">
+        <v>424</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="G59" t="s">
+        <v>766</v>
+      </c>
+      <c r="H59" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B60" t="s">
+        <v>529</v>
+      </c>
+      <c r="C60" t="s">
+        <v>531</v>
+      </c>
+      <c r="D60" t="s">
+        <v>671</v>
+      </c>
+      <c r="E60" t="s">
+        <v>402</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="G60" t="s">
+        <v>768</v>
+      </c>
+      <c r="H60" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" t="s">
+        <v>131</v>
+      </c>
+      <c r="D61" t="s">
+        <v>199</v>
+      </c>
+      <c r="E61" t="s">
+        <v>402</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="G61" t="s">
+        <v>768</v>
+      </c>
+      <c r="H61" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B62" t="s">
+        <v>662</v>
+      </c>
+      <c r="C62" t="s">
+        <v>664</v>
+      </c>
+      <c r="D62" t="s">
+        <v>676</v>
+      </c>
+      <c r="E62" t="s">
+        <v>424</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="G62" t="s">
+        <v>768</v>
+      </c>
+      <c r="H62" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B63" t="s">
+        <v>662</v>
+      </c>
+      <c r="C63" t="s">
+        <v>395</v>
+      </c>
+      <c r="D63" t="s">
+        <v>753</v>
+      </c>
+      <c r="E63" t="s">
+        <v>362</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="G63" t="s">
+        <v>768</v>
+      </c>
+      <c r="H63" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B64" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" t="s">
+        <v>147</v>
+      </c>
+      <c r="D64" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64" t="s">
+        <v>424</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="G64" t="s">
+        <v>768</v>
+      </c>
+      <c r="H64" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B65" t="s">
+        <v>152</v>
+      </c>
+      <c r="C65" t="s">
+        <v>181</v>
+      </c>
+      <c r="D65" t="s">
+        <v>161</v>
+      </c>
+      <c r="E65" t="s">
+        <v>362</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="G65" t="s">
+        <v>768</v>
+      </c>
+      <c r="H65" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B66" t="s">
+        <v>662</v>
+      </c>
+      <c r="C66" t="s">
+        <v>361</v>
+      </c>
+      <c r="D66" t="s">
+        <v>706</v>
+      </c>
+      <c r="E66" t="s">
+        <v>402</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="G66" t="s">
+        <v>766</v>
+      </c>
+      <c r="H66" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B67" t="s">
+        <v>529</v>
+      </c>
+      <c r="C67" t="s">
+        <v>589</v>
+      </c>
+      <c r="D67" t="s">
+        <v>757</v>
+      </c>
+      <c r="E67" t="s">
+        <v>424</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="G67" t="s">
+        <v>768</v>
+      </c>
+      <c r="H67" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B68" t="s">
+        <v>141</v>
+      </c>
+      <c r="C68" t="s">
+        <v>192</v>
+      </c>
+      <c r="D68" t="s">
+        <v>142</v>
+      </c>
+      <c r="E68" t="s">
+        <v>402</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="G68" t="s">
+        <v>768</v>
+      </c>
+      <c r="H68" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B69" t="s">
+        <v>130</v>
+      </c>
+      <c r="C69" t="s">
+        <v>197</v>
+      </c>
+      <c r="D69" t="s">
+        <v>307</v>
+      </c>
+      <c r="E69" t="s">
+        <v>424</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="G69" t="s">
+        <v>768</v>
+      </c>
+      <c r="H69" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B70" t="s">
+        <v>363</v>
+      </c>
+      <c r="C70" t="s">
+        <v>762</v>
+      </c>
+      <c r="D70" t="s">
+        <v>364</v>
+      </c>
+      <c r="E70" t="s">
+        <v>402</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="G70" t="s">
+        <v>766</v>
+      </c>
+      <c r="H70" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B71" t="s">
+        <v>152</v>
+      </c>
+      <c r="C71" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" t="s">
+        <v>165</v>
+      </c>
+      <c r="E71" t="s">
+        <v>362</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="G71" t="s">
+        <v>766</v>
+      </c>
+      <c r="H71" t="s">
+        <v>764</v>
       </c>
     </row>
   </sheetData>

--- a/数据库.xlsx
+++ b/数据库.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7695" activeTab="1"/>
+    <workbookView windowWidth="19635" windowHeight="7695"/>
   </bookViews>
   <sheets>
     <sheet name="智胜库" sheetId="1" r:id="rId1"/>
     <sheet name="精选场次" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">智胜库!$A$1:$I$339</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">智胜库!$A$1:$I$367</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3438" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3558" uniqueCount="808">
   <si>
     <t>日期</t>
   </si>
@@ -2390,6 +2390,51 @@
     <t>欧战干扰降仓仍输盘</t>
   </si>
   <si>
+    <t>主场爆冷，客队低水诱盘</t>
+  </si>
+  <si>
+    <t>里奥夸尔托学院</t>
+  </si>
+  <si>
+    <t>主场受让翻车</t>
+  </si>
+  <si>
+    <t>客场低水受让命中</t>
+  </si>
+  <si>
+    <t>防卫者</t>
+  </si>
+  <si>
+    <t>1:1</t>
+  </si>
+  <si>
+    <t>主场低水翻车</t>
+  </si>
+  <si>
+    <t>瑞模贝雷</t>
+  </si>
+  <si>
+    <t>主场深盘翻车</t>
+  </si>
+  <si>
+    <t>甘拿斯亚门多萨</t>
+  </si>
+  <si>
+    <t>塔勒瑞斯</t>
+  </si>
+  <si>
+    <t>客队超低水0.75诱盘</t>
+  </si>
+  <si>
+    <t>西甲</t>
+  </si>
+  <si>
+    <t>拉科鲁尼亚</t>
+  </si>
+  <si>
+    <t>埃尔切</t>
+  </si>
+  <si>
     <t>推荐方向</t>
   </si>
   <si>
@@ -2405,9 +2450,6 @@
     <t>2:2</t>
   </si>
   <si>
-    <t>1:1</t>
-  </si>
-  <si>
     <t>走</t>
   </si>
   <si>
@@ -2466,6 +2508,15 @@
   </si>
   <si>
     <t>客场浅盘</t>
+  </si>
+  <si>
+    <t>主场爆冷</t>
+  </si>
+  <si>
+    <t>低水受让命中</t>
+  </si>
+  <si>
+    <t>输半</t>
   </si>
 </sst>
 </file>
@@ -3664,7 +3715,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I367"/>
+  <dimension ref="A1:I375"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" style="5"/>
@@ -14317,9 +14368,241 @@
         <v>764</v>
       </c>
     </row>
+    <row r="368" spans="1:9">
+      <c r="A368" s="7">
+        <v>46251</v>
+      </c>
+      <c r="B368" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C368" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D368" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="E368" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F368" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G368" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="H368" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I368" s="5" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9">
+      <c r="A369" s="7">
+        <v>46251</v>
+      </c>
+      <c r="B369" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C369" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D369" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E369" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F369" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G369" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="H369" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I369" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9">
+      <c r="A370" s="7">
+        <v>46251</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C370" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="D370" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="E370" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F370" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G370" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H370" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I370" s="5" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9">
+      <c r="A371" s="7">
+        <v>46251</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C371" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="D371" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="E371" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F371" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G371" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="H371" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I371" s="5" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9">
+      <c r="A372" s="7">
+        <v>46251</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C372" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="D372" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="E372" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F372" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G372" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H372" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I372" s="5" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9">
+      <c r="A373" s="7">
+        <v>46251</v>
+      </c>
+      <c r="B373" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="D373" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="E373" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F373" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G373" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H373" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I373" s="5" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9">
+      <c r="A374" s="7">
+        <v>46251</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C374" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="D374" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="E374" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F374" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G374" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="H374" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I374" s="5" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9">
+      <c r="A375" s="7">
+        <v>46251</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="C375" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="D375" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="E375" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F375" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G375" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H375" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I375" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I339" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:I339">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I367" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:I367">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -14332,7 +14615,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.875"/>
@@ -14353,7 +14636,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>765</v>
+        <v>780</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
@@ -14385,7 +14668,7 @@
         <v>739</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H2" t="s">
         <v>30</v>
@@ -14411,7 +14694,7 @@
         <v>715</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H3" t="s">
         <v>30</v>
@@ -14434,10 +14717,10 @@
         <v>358</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>767</v>
+        <v>782</v>
       </c>
       <c r="G4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -14463,7 +14746,7 @@
         <v>739</v>
       </c>
       <c r="G5" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H5" t="s">
         <v>30</v>
@@ -14489,7 +14772,7 @@
         <v>731</v>
       </c>
       <c r="G6" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -14515,7 +14798,7 @@
         <v>727</v>
       </c>
       <c r="G7" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H7" t="s">
         <v>448</v>
@@ -14541,7 +14824,7 @@
         <v>727</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -14567,7 +14850,7 @@
         <v>715</v>
       </c>
       <c r="G9" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H9" t="s">
         <v>241</v>
@@ -14593,7 +14876,7 @@
         <v>731</v>
       </c>
       <c r="G10" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H10" t="s">
         <v>23</v>
@@ -14619,7 +14902,7 @@
         <v>727</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -14645,7 +14928,7 @@
         <v>715</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -14668,10 +14951,10 @@
         <v>481</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="G13" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H13" t="s">
         <v>483</v>
@@ -14697,7 +14980,7 @@
         <v>727</v>
       </c>
       <c r="G14" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H14" t="s">
         <v>485</v>
@@ -14723,7 +15006,7 @@
         <v>733</v>
       </c>
       <c r="G15" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H15" t="s">
         <v>483</v>
@@ -14749,7 +15032,7 @@
         <v>727</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H16" t="s">
         <v>483</v>
@@ -14775,7 +15058,7 @@
         <v>770</v>
       </c>
       <c r="G17" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H17" t="s">
         <v>483</v>
@@ -14801,7 +15084,7 @@
         <v>770</v>
       </c>
       <c r="G18" t="s">
-        <v>771</v>
+        <v>785</v>
       </c>
       <c r="H18" t="s">
         <v>324</v>
@@ -14821,13 +15104,13 @@
         <v>651</v>
       </c>
       <c r="E19" t="s">
-        <v>772</v>
+        <v>786</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>770</v>
       </c>
       <c r="G19" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H19" t="s">
         <v>653</v>
@@ -14853,7 +15136,7 @@
         <v>722</v>
       </c>
       <c r="G20" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -14879,7 +15162,7 @@
         <v>709</v>
       </c>
       <c r="G21" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H21" t="s">
         <v>30</v>
@@ -14902,13 +15185,13 @@
         <v>657</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>773</v>
+        <v>787</v>
       </c>
       <c r="G22" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H22" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -14931,7 +15214,7 @@
         <v>739</v>
       </c>
       <c r="G23" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H23" t="s">
         <v>124</v>
@@ -14957,7 +15240,7 @@
         <v>739</v>
       </c>
       <c r="G24" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H24" t="s">
         <v>666</v>
@@ -14983,7 +15266,7 @@
         <v>715</v>
       </c>
       <c r="G25" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -15009,7 +15292,7 @@
         <v>739</v>
       </c>
       <c r="G26" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H26" t="s">
         <v>666</v>
@@ -15032,13 +15315,13 @@
         <v>677</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="G27" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H27" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -15061,7 +15344,7 @@
         <v>731</v>
       </c>
       <c r="G28" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H28" t="s">
         <v>679</v>
@@ -15084,10 +15367,10 @@
         <v>346</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>773</v>
+        <v>787</v>
       </c>
       <c r="G29" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H29" t="s">
         <v>682</v>
@@ -15113,7 +15396,7 @@
         <v>709</v>
       </c>
       <c r="G30" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H30" t="s">
         <v>684</v>
@@ -15136,13 +15419,13 @@
         <v>362</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>773</v>
+        <v>787</v>
       </c>
       <c r="G31" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H31" t="s">
-        <v>776</v>
+        <v>790</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -15165,7 +15448,7 @@
         <v>727</v>
       </c>
       <c r="G32" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H32" t="s">
         <v>692</v>
@@ -15188,10 +15471,10 @@
         <v>362</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="G33" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H33" t="s">
         <v>693</v>
@@ -15217,10 +15500,10 @@
         <v>770</v>
       </c>
       <c r="G34" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H34" t="s">
-        <v>777</v>
+        <v>791</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -15243,10 +15526,10 @@
         <v>770</v>
       </c>
       <c r="G35" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H35" t="s">
-        <v>778</v>
+        <v>792</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -15269,7 +15552,7 @@
         <v>770</v>
       </c>
       <c r="G36" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H36" t="s">
         <v>696</v>
@@ -15295,10 +15578,10 @@
         <v>727</v>
       </c>
       <c r="G37" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H37" t="s">
-        <v>778</v>
+        <v>792</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -15321,7 +15604,7 @@
         <v>731</v>
       </c>
       <c r="G38" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H38" t="s">
         <v>703</v>
@@ -15347,10 +15630,10 @@
         <v>712</v>
       </c>
       <c r="G39" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H39" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -15373,10 +15656,10 @@
         <v>714</v>
       </c>
       <c r="G40" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H40" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -15399,10 +15682,10 @@
         <v>707</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H41" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
       <c r="I41" t="s">
         <v>713</v>
@@ -15428,7 +15711,7 @@
         <v>709</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H42" t="s">
         <v>702</v>
@@ -15457,7 +15740,7 @@
         <v>709</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H43" t="s">
         <v>711</v>
@@ -15480,13 +15763,13 @@
         <v>717</v>
       </c>
       <c r="E44" t="s">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>718</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H44" t="s">
         <v>719</v>
@@ -15506,13 +15789,13 @@
         <v>651</v>
       </c>
       <c r="E45" t="s">
-        <v>782</v>
+        <v>796</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>718</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H45" t="s">
         <v>720</v>
@@ -15538,10 +15821,10 @@
         <v>715</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H46" t="s">
-        <v>783</v>
+        <v>797</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -15564,7 +15847,7 @@
         <v>722</v>
       </c>
       <c r="G47" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H47" t="s">
         <v>723</v>
@@ -15590,10 +15873,10 @@
         <v>724</v>
       </c>
       <c r="G48" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H48" t="s">
-        <v>784</v>
+        <v>798</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -15616,10 +15899,10 @@
         <v>727</v>
       </c>
       <c r="G49" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H49" t="s">
-        <v>785</v>
+        <v>799</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -15642,7 +15925,7 @@
         <v>715</v>
       </c>
       <c r="G50" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H50" t="s">
         <v>729</v>
@@ -15668,7 +15951,7 @@
         <v>731</v>
       </c>
       <c r="G51" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H51" t="s">
         <v>732</v>
@@ -15694,7 +15977,7 @@
         <v>733</v>
       </c>
       <c r="G52" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H52" t="s">
         <v>734</v>
@@ -15720,7 +16003,7 @@
         <v>735</v>
       </c>
       <c r="G53" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H53" t="s">
         <v>736</v>
@@ -15746,10 +16029,10 @@
         <v>727</v>
       </c>
       <c r="G54" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H54" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -15772,7 +16055,7 @@
         <v>739</v>
       </c>
       <c r="G55" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H55" t="s">
         <v>740</v>
@@ -15798,7 +16081,7 @@
         <v>742</v>
       </c>
       <c r="G56" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H56" t="s">
         <v>23</v>
@@ -15824,7 +16107,7 @@
         <v>745</v>
       </c>
       <c r="G57" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H57" t="s">
         <v>746</v>
@@ -15850,7 +16133,7 @@
         <v>742</v>
       </c>
       <c r="G58" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H58" t="s">
         <v>748</v>
@@ -15876,7 +16159,7 @@
         <v>714</v>
       </c>
       <c r="G59" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H59" t="s">
         <v>749</v>
@@ -15902,7 +16185,7 @@
         <v>745</v>
       </c>
       <c r="G60" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H60" t="s">
         <v>750</v>
@@ -15928,10 +16211,10 @@
         <v>709</v>
       </c>
       <c r="G61" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H61" t="s">
-        <v>787</v>
+        <v>801</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -15954,7 +16237,7 @@
         <v>752</v>
       </c>
       <c r="G62" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -15980,10 +16263,10 @@
         <v>722</v>
       </c>
       <c r="G63" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H63" t="s">
-        <v>788</v>
+        <v>802</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -16006,7 +16289,7 @@
         <v>733</v>
       </c>
       <c r="G64" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H64" t="s">
         <v>16</v>
@@ -16032,7 +16315,7 @@
         <v>731</v>
       </c>
       <c r="G65" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H65" t="s">
         <v>755</v>
@@ -16058,7 +16341,7 @@
         <v>731</v>
       </c>
       <c r="G66" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H66" t="s">
         <v>756</v>
@@ -16084,10 +16367,10 @@
         <v>727</v>
       </c>
       <c r="G67" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H67" t="s">
-        <v>789</v>
+        <v>803</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -16110,7 +16393,7 @@
         <v>727</v>
       </c>
       <c r="G68" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H68" t="s">
         <v>759</v>
@@ -16136,10 +16419,10 @@
         <v>760</v>
       </c>
       <c r="G69" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H69" t="s">
-        <v>790</v>
+        <v>804</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -16162,7 +16445,7 @@
         <v>714</v>
       </c>
       <c r="G70" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H70" t="s">
         <v>763</v>
@@ -16188,10 +16471,218 @@
         <v>745</v>
       </c>
       <c r="G71" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="H71" t="s">
         <v>764</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B72" t="s">
+        <v>130</v>
+      </c>
+      <c r="C72" t="s">
+        <v>137</v>
+      </c>
+      <c r="D72" t="s">
+        <v>310</v>
+      </c>
+      <c r="E72" t="s">
+        <v>402</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="G72" t="s">
+        <v>781</v>
+      </c>
+      <c r="H72" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B73" t="s">
+        <v>141</v>
+      </c>
+      <c r="C73" t="s">
+        <v>301</v>
+      </c>
+      <c r="D73" t="s">
+        <v>174</v>
+      </c>
+      <c r="E73" t="s">
+        <v>362</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="G73" t="s">
+        <v>781</v>
+      </c>
+      <c r="H73" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B74" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" t="s">
+        <v>766</v>
+      </c>
+      <c r="D74" t="s">
+        <v>365</v>
+      </c>
+      <c r="E74" t="s">
+        <v>710</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="G74" t="s">
+        <v>781</v>
+      </c>
+      <c r="H74" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B75" t="s">
+        <v>363</v>
+      </c>
+      <c r="C75" t="s">
+        <v>478</v>
+      </c>
+      <c r="D75" t="s">
+        <v>645</v>
+      </c>
+      <c r="E75" t="s">
+        <v>402</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="G75" t="s">
+        <v>783</v>
+      </c>
+      <c r="H75" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B76" t="s">
+        <v>363</v>
+      </c>
+      <c r="C76" t="s">
+        <v>643</v>
+      </c>
+      <c r="D76" t="s">
+        <v>769</v>
+      </c>
+      <c r="E76" t="s">
+        <v>362</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="G76" t="s">
+        <v>781</v>
+      </c>
+      <c r="H76" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B77" t="s">
+        <v>662</v>
+      </c>
+      <c r="C77" t="s">
+        <v>480</v>
+      </c>
+      <c r="D77" t="s">
+        <v>772</v>
+      </c>
+      <c r="E77" t="s">
+        <v>362</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="G77" t="s">
+        <v>781</v>
+      </c>
+      <c r="H77" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B78" t="s">
+        <v>363</v>
+      </c>
+      <c r="C78" t="s">
+        <v>774</v>
+      </c>
+      <c r="D78" t="s">
+        <v>775</v>
+      </c>
+      <c r="E78" t="s">
+        <v>402</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="G78" t="s">
+        <v>781</v>
+      </c>
+      <c r="H78" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B79" t="s">
+        <v>777</v>
+      </c>
+      <c r="C79" t="s">
+        <v>778</v>
+      </c>
+      <c r="D79" t="s">
+        <v>779</v>
+      </c>
+      <c r="E79" t="s">
+        <v>710</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="G79" t="s">
+        <v>781</v>
+      </c>
+      <c r="H79" t="s">
+        <v>807</v>
       </c>
     </row>
   </sheetData>

--- a/数据库.xlsx
+++ b/数据库.xlsx
@@ -11,7 +11,7 @@
     <sheet name="精选场次" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">智胜库!$A$1:$I$367</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">智胜库!$A$1:$I$375</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3558" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3824" uniqueCount="844">
   <si>
     <t>日期</t>
   </si>
@@ -2435,21 +2435,105 @@
     <t>埃尔切</t>
   </si>
   <si>
+    <t>主胜穿盘</t>
+  </si>
+  <si>
+    <t>2:2</t>
+  </si>
+  <si>
+    <t>高水诱盘+门将失误</t>
+  </si>
+  <si>
+    <t>伤病满营，主场高估</t>
+  </si>
+  <si>
+    <t>AEK雅典</t>
+  </si>
+  <si>
+    <t>解放者杯</t>
+  </si>
+  <si>
+    <t>托利马体育</t>
+  </si>
+  <si>
+    <t>山谷独立</t>
+  </si>
+  <si>
+    <t>主场零封被破</t>
+  </si>
+  <si>
+    <t>智利天主大学</t>
+  </si>
+  <si>
+    <t>拉普拉塔大学生</t>
+  </si>
+  <si>
+    <t>南美主场陷阱</t>
+  </si>
+  <si>
+    <t>圣保罗</t>
+  </si>
+  <si>
+    <t>玻利瓦尔</t>
+  </si>
+  <si>
+    <t>客队受让</t>
+  </si>
+  <si>
+    <t>3:1</t>
+  </si>
+  <si>
+    <t>深盘实力盘误判</t>
+  </si>
+  <si>
+    <t>凯尔特人</t>
+  </si>
+  <si>
+    <t>LASK林茨</t>
+  </si>
+  <si>
+    <t>方向误判</t>
+  </si>
+  <si>
+    <t>唐津市民</t>
+  </si>
+  <si>
+    <t>轮换超预期</t>
+  </si>
+  <si>
+    <t>晋州市民</t>
+  </si>
+  <si>
+    <t>诱盘判断失败</t>
+  </si>
+  <si>
+    <t>主队受让</t>
+  </si>
+  <si>
+    <t>黑马神话终结</t>
+  </si>
+  <si>
+    <t>客让0</t>
+  </si>
+  <si>
+    <t>济州客场疲软</t>
+  </si>
+  <si>
+    <t>主让0</t>
+  </si>
+  <si>
+    <t>城南FC</t>
+  </si>
+  <si>
     <t>推荐方向</t>
   </si>
   <si>
     <t>错</t>
   </si>
   <si>
-    <t>3:1</t>
-  </si>
-  <si>
     <t>对</t>
   </si>
   <si>
-    <t>2:2</t>
-  </si>
-  <si>
     <t>走</t>
   </si>
   <si>
@@ -2517,6 +2601,30 @@
   </si>
   <si>
     <t>输半</t>
+  </si>
+  <si>
+    <t>高水诱盘</t>
+  </si>
+  <si>
+    <t>伤病高估</t>
+  </si>
+  <si>
+    <t>平局走水</t>
+  </si>
+  <si>
+    <t>历史数据陷阱</t>
+  </si>
+  <si>
+    <t>深盘误判</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>中立场低估</t>
+  </si>
+  <si>
+    <t>黑马终结</t>
   </si>
 </sst>
 </file>
@@ -3715,7 +3823,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I375"/>
+  <dimension ref="A1:I392"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" style="5"/>
@@ -14600,9 +14708,502 @@
         <v>59</v>
       </c>
     </row>
+    <row r="376" spans="1:9">
+      <c r="A376" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C376" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="D376" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E376" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F376" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="G376" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="H376" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I376" s="5" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9">
+      <c r="A377" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B377" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C377" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D377" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E377" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F377" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G377" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H377" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I377" s="5" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9">
+      <c r="A378" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B378" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C378" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="D378" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E378" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F378" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G378" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="H378" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I378" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9">
+      <c r="A379" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="C379" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="D379" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="E379" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F379" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G379" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H379" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I379" s="5" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9">
+      <c r="A380" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B380" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="C380" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="D380" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="E380" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F380" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G380" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="H380" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I380" s="5" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9">
+      <c r="A381" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B381" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="C381" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="D381" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="E381" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F381" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="G381" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="H381" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I381" s="5" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9">
+      <c r="A382" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C382" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="D382" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="E382" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F382" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="G382" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="H382" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I382" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9">
+      <c r="A383" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B383" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C383" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D383" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E383" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F383" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G383" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="H383" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I383" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9">
+      <c r="A384" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B384" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="D384" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="E384" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F384" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G384" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H384" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I384" s="5" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9">
+      <c r="A385" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B385" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C385" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="D385" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E385" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F385" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G385" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="H385" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I385" s="5" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9">
+      <c r="A386" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B386" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C386" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D386" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="E386" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F386" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="G386" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="H386" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I386" s="5" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9">
+      <c r="A387" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B387" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C387" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D387" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E387" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F387" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G387" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="H387" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I387" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9">
+      <c r="A388" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B388" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C388" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D388" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="E388" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="F388" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="G388" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="H388" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I388" s="5" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9">
+      <c r="A389" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B389" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C389" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D389" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E389" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F389" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="G389" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H389" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I389" s="5" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9">
+      <c r="A390" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B390" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C390" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D390" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E390" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="F390" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G390" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="H390" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I390" s="5" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9">
+      <c r="A391" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B391" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C391" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D391" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E391" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="F391" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G391" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="H391" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I391" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9">
+      <c r="A392" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B392" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C392" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D392" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="E392" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F392" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="G392" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="H392" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I392" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I367" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:I367">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I375" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:I375">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -14615,7 +15216,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.875"/>
@@ -14636,7 +15237,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
@@ -14668,7 +15269,7 @@
         <v>739</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H2" t="s">
         <v>30</v>
@@ -14694,7 +15295,7 @@
         <v>715</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H3" t="s">
         <v>30</v>
@@ -14717,10 +15318,10 @@
         <v>358</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>782</v>
+        <v>795</v>
       </c>
       <c r="G4" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -14746,7 +15347,7 @@
         <v>739</v>
       </c>
       <c r="G5" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H5" t="s">
         <v>30</v>
@@ -14772,7 +15373,7 @@
         <v>731</v>
       </c>
       <c r="G6" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -14798,7 +15399,7 @@
         <v>727</v>
       </c>
       <c r="G7" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H7" t="s">
         <v>448</v>
@@ -14824,7 +15425,7 @@
         <v>727</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -14850,7 +15451,7 @@
         <v>715</v>
       </c>
       <c r="G9" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H9" t="s">
         <v>241</v>
@@ -14876,7 +15477,7 @@
         <v>731</v>
       </c>
       <c r="G10" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H10" t="s">
         <v>23</v>
@@ -14902,7 +15503,7 @@
         <v>727</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -14928,7 +15529,7 @@
         <v>715</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -14951,10 +15552,10 @@
         <v>481</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="G13" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H13" t="s">
         <v>483</v>
@@ -14980,7 +15581,7 @@
         <v>727</v>
       </c>
       <c r="G14" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H14" t="s">
         <v>485</v>
@@ -15006,7 +15607,7 @@
         <v>733</v>
       </c>
       <c r="G15" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H15" t="s">
         <v>483</v>
@@ -15032,7 +15633,7 @@
         <v>727</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H16" t="s">
         <v>483</v>
@@ -15058,7 +15659,7 @@
         <v>770</v>
       </c>
       <c r="G17" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H17" t="s">
         <v>483</v>
@@ -15084,7 +15685,7 @@
         <v>770</v>
       </c>
       <c r="G18" t="s">
-        <v>785</v>
+        <v>813</v>
       </c>
       <c r="H18" t="s">
         <v>324</v>
@@ -15104,13 +15705,13 @@
         <v>651</v>
       </c>
       <c r="E19" t="s">
-        <v>786</v>
+        <v>814</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>770</v>
       </c>
       <c r="G19" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H19" t="s">
         <v>653</v>
@@ -15136,7 +15737,7 @@
         <v>722</v>
       </c>
       <c r="G20" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -15162,7 +15763,7 @@
         <v>709</v>
       </c>
       <c r="G21" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H21" t="s">
         <v>30</v>
@@ -15185,13 +15786,13 @@
         <v>657</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>787</v>
+        <v>815</v>
       </c>
       <c r="G22" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H22" t="s">
-        <v>788</v>
+        <v>816</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -15214,7 +15815,7 @@
         <v>739</v>
       </c>
       <c r="G23" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H23" t="s">
         <v>124</v>
@@ -15240,7 +15841,7 @@
         <v>739</v>
       </c>
       <c r="G24" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H24" t="s">
         <v>666</v>
@@ -15266,7 +15867,7 @@
         <v>715</v>
       </c>
       <c r="G25" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -15292,7 +15893,7 @@
         <v>739</v>
       </c>
       <c r="G26" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H26" t="s">
         <v>666</v>
@@ -15315,13 +15916,13 @@
         <v>677</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="G27" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H27" t="s">
-        <v>789</v>
+        <v>817</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -15344,7 +15945,7 @@
         <v>731</v>
       </c>
       <c r="G28" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H28" t="s">
         <v>679</v>
@@ -15367,10 +15968,10 @@
         <v>346</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>787</v>
+        <v>815</v>
       </c>
       <c r="G29" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H29" t="s">
         <v>682</v>
@@ -15396,7 +15997,7 @@
         <v>709</v>
       </c>
       <c r="G30" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H30" t="s">
         <v>684</v>
@@ -15419,13 +16020,13 @@
         <v>362</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>787</v>
+        <v>815</v>
       </c>
       <c r="G31" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H31" t="s">
-        <v>790</v>
+        <v>818</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -15448,7 +16049,7 @@
         <v>727</v>
       </c>
       <c r="G32" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H32" t="s">
         <v>692</v>
@@ -15471,10 +16072,10 @@
         <v>362</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="G33" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H33" t="s">
         <v>693</v>
@@ -15500,10 +16101,10 @@
         <v>770</v>
       </c>
       <c r="G34" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H34" t="s">
-        <v>791</v>
+        <v>819</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -15526,10 +16127,10 @@
         <v>770</v>
       </c>
       <c r="G35" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H35" t="s">
-        <v>792</v>
+        <v>820</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -15552,7 +16153,7 @@
         <v>770</v>
       </c>
       <c r="G36" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H36" t="s">
         <v>696</v>
@@ -15578,10 +16179,10 @@
         <v>727</v>
       </c>
       <c r="G37" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H37" t="s">
-        <v>792</v>
+        <v>820</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -15604,7 +16205,7 @@
         <v>731</v>
       </c>
       <c r="G38" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H38" t="s">
         <v>703</v>
@@ -15630,10 +16231,10 @@
         <v>712</v>
       </c>
       <c r="G39" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H39" t="s">
-        <v>793</v>
+        <v>821</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -15656,10 +16257,10 @@
         <v>714</v>
       </c>
       <c r="G40" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H40" t="s">
-        <v>793</v>
+        <v>821</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -15682,10 +16283,10 @@
         <v>707</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H41" t="s">
-        <v>794</v>
+        <v>822</v>
       </c>
       <c r="I41" t="s">
         <v>713</v>
@@ -15711,7 +16312,7 @@
         <v>709</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H42" t="s">
         <v>702</v>
@@ -15740,7 +16341,7 @@
         <v>709</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H43" t="s">
         <v>711</v>
@@ -15763,13 +16364,13 @@
         <v>717</v>
       </c>
       <c r="E44" t="s">
-        <v>795</v>
+        <v>823</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>718</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H44" t="s">
         <v>719</v>
@@ -15789,13 +16390,13 @@
         <v>651</v>
       </c>
       <c r="E45" t="s">
-        <v>796</v>
+        <v>824</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>718</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H45" t="s">
         <v>720</v>
@@ -15821,10 +16422,10 @@
         <v>715</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H46" t="s">
-        <v>797</v>
+        <v>825</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -15847,7 +16448,7 @@
         <v>722</v>
       </c>
       <c r="G47" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H47" t="s">
         <v>723</v>
@@ -15873,10 +16474,10 @@
         <v>724</v>
       </c>
       <c r="G48" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H48" t="s">
-        <v>798</v>
+        <v>826</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -15899,10 +16500,10 @@
         <v>727</v>
       </c>
       <c r="G49" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H49" t="s">
-        <v>799</v>
+        <v>827</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -15925,7 +16526,7 @@
         <v>715</v>
       </c>
       <c r="G50" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H50" t="s">
         <v>729</v>
@@ -15951,7 +16552,7 @@
         <v>731</v>
       </c>
       <c r="G51" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H51" t="s">
         <v>732</v>
@@ -15977,7 +16578,7 @@
         <v>733</v>
       </c>
       <c r="G52" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H52" t="s">
         <v>734</v>
@@ -16003,7 +16604,7 @@
         <v>735</v>
       </c>
       <c r="G53" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H53" t="s">
         <v>736</v>
@@ -16029,10 +16630,10 @@
         <v>727</v>
       </c>
       <c r="G54" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H54" t="s">
-        <v>800</v>
+        <v>828</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -16055,7 +16656,7 @@
         <v>739</v>
       </c>
       <c r="G55" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H55" t="s">
         <v>740</v>
@@ -16081,7 +16682,7 @@
         <v>742</v>
       </c>
       <c r="G56" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H56" t="s">
         <v>23</v>
@@ -16107,7 +16708,7 @@
         <v>745</v>
       </c>
       <c r="G57" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H57" t="s">
         <v>746</v>
@@ -16133,7 +16734,7 @@
         <v>742</v>
       </c>
       <c r="G58" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H58" t="s">
         <v>748</v>
@@ -16159,7 +16760,7 @@
         <v>714</v>
       </c>
       <c r="G59" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H59" t="s">
         <v>749</v>
@@ -16185,7 +16786,7 @@
         <v>745</v>
       </c>
       <c r="G60" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H60" t="s">
         <v>750</v>
@@ -16211,10 +16812,10 @@
         <v>709</v>
       </c>
       <c r="G61" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H61" t="s">
-        <v>801</v>
+        <v>829</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -16237,7 +16838,7 @@
         <v>752</v>
       </c>
       <c r="G62" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -16263,10 +16864,10 @@
         <v>722</v>
       </c>
       <c r="G63" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H63" t="s">
-        <v>802</v>
+        <v>830</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -16289,7 +16890,7 @@
         <v>733</v>
       </c>
       <c r="G64" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H64" t="s">
         <v>16</v>
@@ -16315,7 +16916,7 @@
         <v>731</v>
       </c>
       <c r="G65" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H65" t="s">
         <v>755</v>
@@ -16341,7 +16942,7 @@
         <v>731</v>
       </c>
       <c r="G66" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H66" t="s">
         <v>756</v>
@@ -16367,10 +16968,10 @@
         <v>727</v>
       </c>
       <c r="G67" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H67" t="s">
-        <v>803</v>
+        <v>831</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -16393,7 +16994,7 @@
         <v>727</v>
       </c>
       <c r="G68" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H68" t="s">
         <v>759</v>
@@ -16419,10 +17020,10 @@
         <v>760</v>
       </c>
       <c r="G69" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H69" t="s">
-        <v>804</v>
+        <v>832</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -16445,7 +17046,7 @@
         <v>714</v>
       </c>
       <c r="G70" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H70" t="s">
         <v>763</v>
@@ -16471,7 +17072,7 @@
         <v>745</v>
       </c>
       <c r="G71" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H71" t="s">
         <v>764</v>
@@ -16497,10 +17098,10 @@
         <v>742</v>
       </c>
       <c r="G72" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H72" t="s">
-        <v>805</v>
+        <v>833</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -16523,7 +17124,7 @@
         <v>731</v>
       </c>
       <c r="G73" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H73" t="s">
         <v>112</v>
@@ -16549,7 +17150,7 @@
         <v>727</v>
       </c>
       <c r="G74" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H74" t="s">
         <v>767</v>
@@ -16575,10 +17176,10 @@
         <v>718</v>
       </c>
       <c r="G75" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="H75" t="s">
-        <v>806</v>
+        <v>834</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -16601,7 +17202,7 @@
         <v>770</v>
       </c>
       <c r="G76" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H76" t="s">
         <v>771</v>
@@ -16627,7 +17228,7 @@
         <v>770</v>
       </c>
       <c r="G77" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H77" t="s">
         <v>773</v>
@@ -16653,7 +17254,7 @@
         <v>722</v>
       </c>
       <c r="G78" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="H78" t="s">
         <v>748</v>
@@ -16679,10 +17280,485 @@
         <v>770</v>
       </c>
       <c r="G79" t="s">
+        <v>811</v>
+      </c>
+      <c r="H79" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C80" t="s">
+        <v>229</v>
+      </c>
+      <c r="D80" t="s">
+        <v>168</v>
+      </c>
+      <c r="E80" t="s">
+        <v>780</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="H79" t="s">
+      <c r="G80" t="s">
+        <v>811</v>
+      </c>
+      <c r="H80" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B81" t="s">
+        <v>344</v>
+      </c>
+      <c r="C81" t="s">
+        <v>270</v>
+      </c>
+      <c r="D81" t="s">
+        <v>352</v>
+      </c>
+      <c r="E81" t="s">
+        <v>362</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="G81" t="s">
+        <v>811</v>
+      </c>
+      <c r="H81" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B82" t="s">
+        <v>344</v>
+      </c>
+      <c r="C82" t="s">
+        <v>383</v>
+      </c>
+      <c r="D82" t="s">
+        <v>784</v>
+      </c>
+      <c r="E82" t="s">
+        <v>710</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="G82" t="s">
+        <v>813</v>
+      </c>
+      <c r="H82" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B83" t="s">
+        <v>785</v>
+      </c>
+      <c r="C83" t="s">
+        <v>786</v>
+      </c>
+      <c r="D83" t="s">
+        <v>787</v>
+      </c>
+      <c r="E83" t="s">
+        <v>710</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="G83" t="s">
+        <v>811</v>
+      </c>
+      <c r="H83" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B84" t="s">
+        <v>785</v>
+      </c>
+      <c r="C84" t="s">
+        <v>789</v>
+      </c>
+      <c r="D84" t="s">
+        <v>790</v>
+      </c>
+      <c r="E84" t="s">
+        <v>710</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="G84" t="s">
+        <v>811</v>
+      </c>
+      <c r="H84" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B85" t="s">
+        <v>700</v>
+      </c>
+      <c r="C85" t="s">
+        <v>792</v>
+      </c>
+      <c r="D85" t="s">
+        <v>793</v>
+      </c>
+      <c r="E85" t="s">
+        <v>794</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="G85" t="s">
+        <v>811</v>
+      </c>
+      <c r="H85" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B86" t="s">
+        <v>344</v>
+      </c>
+      <c r="C86" t="s">
+        <v>797</v>
+      </c>
+      <c r="D86" t="s">
+        <v>798</v>
+      </c>
+      <c r="E86" t="s">
+        <v>780</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="G86" t="s">
+        <v>812</v>
+      </c>
+      <c r="H86" t="s">
+        <v>812</v>
+      </c>
+      <c r="I86" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B87" t="s">
+        <v>344</v>
+      </c>
+      <c r="C87" t="s">
+        <v>386</v>
+      </c>
+      <c r="D87" t="s">
+        <v>154</v>
+      </c>
+      <c r="E87" t="s">
+        <v>424</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="G87" t="s">
+        <v>812</v>
+      </c>
+      <c r="H87" t="s">
+        <v>812</v>
+      </c>
+      <c r="I87" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B88" t="s">
+        <v>344</v>
+      </c>
+      <c r="C88" t="s">
+        <v>345</v>
+      </c>
+      <c r="D88" t="s">
+        <v>226</v>
+      </c>
+      <c r="E88" t="s">
+        <v>362</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="G88" t="s">
+        <v>811</v>
+      </c>
+      <c r="H88" t="s">
+        <v>812</v>
+      </c>
+      <c r="I88" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B89" t="s">
+        <v>344</v>
+      </c>
+      <c r="C89" t="s">
+        <v>381</v>
+      </c>
+      <c r="D89" t="s">
+        <v>249</v>
+      </c>
+      <c r="E89" t="s">
+        <v>402</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="G89" t="s">
+        <v>811</v>
+      </c>
+      <c r="H89" t="s">
+        <v>812</v>
+      </c>
+      <c r="I89" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B90" t="s">
+        <v>253</v>
+      </c>
+      <c r="C90" t="s">
+        <v>190</v>
+      </c>
+      <c r="D90" t="s">
+        <v>800</v>
+      </c>
+      <c r="E90" t="s">
+        <v>780</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="G90" t="s">
+        <v>811</v>
+      </c>
+      <c r="H90" t="s">
+        <v>812</v>
+      </c>
+      <c r="I90" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B91" t="s">
+        <v>253</v>
+      </c>
+      <c r="C91" t="s">
+        <v>254</v>
+      </c>
+      <c r="D91" t="s">
+        <v>95</v>
+      </c>
+      <c r="E91" t="s">
+        <v>710</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="G91" t="s">
+        <v>812</v>
+      </c>
+      <c r="H91" t="s">
+        <v>812</v>
+      </c>
+      <c r="I91" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B92" t="s">
+        <v>253</v>
+      </c>
+      <c r="C92" t="s">
+        <v>188</v>
+      </c>
+      <c r="D92" t="s">
+        <v>802</v>
+      </c>
+      <c r="E92" t="s">
+        <v>794</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="G92" t="s">
+        <v>811</v>
+      </c>
+      <c r="H92" t="s">
+        <v>812</v>
+      </c>
+      <c r="I92" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B93" t="s">
+        <v>253</v>
+      </c>
+      <c r="C93" t="s">
+        <v>256</v>
+      </c>
+      <c r="D93" t="s">
+        <v>98</v>
+      </c>
+      <c r="E93" t="s">
+        <v>804</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="G93" t="s">
+        <v>811</v>
+      </c>
+      <c r="H93" t="s">
+        <v>812</v>
+      </c>
+      <c r="I93" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B94" t="s">
+        <v>253</v>
+      </c>
+      <c r="C94" t="s">
+        <v>122</v>
+      </c>
+      <c r="D94" t="s">
+        <v>96</v>
+      </c>
+      <c r="E94" t="s">
+        <v>402</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="G94" t="s">
+        <v>811</v>
+      </c>
+      <c r="H94" t="s">
+        <v>812</v>
+      </c>
+      <c r="I94" t="s">
         <v>807</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B95" t="s">
+        <v>253</v>
+      </c>
+      <c r="C95" t="s">
+        <v>257</v>
+      </c>
+      <c r="D95" t="s">
+        <v>206</v>
+      </c>
+      <c r="E95" t="s">
+        <v>710</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="G95" t="s">
+        <v>813</v>
+      </c>
+      <c r="H95" t="s">
+        <v>812</v>
+      </c>
+      <c r="I95" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B96" t="s">
+        <v>253</v>
+      </c>
+      <c r="C96" t="s">
+        <v>127</v>
+      </c>
+      <c r="D96" t="s">
+        <v>809</v>
+      </c>
+      <c r="E96" t="s">
+        <v>794</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="G96" t="s">
+        <v>812</v>
+      </c>
+      <c r="H96" t="s">
+        <v>812</v>
+      </c>
+      <c r="I96" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/数据库.xlsx
+++ b/数据库.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7695"/>
+    <workbookView windowWidth="19635" windowHeight="7695" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="智胜库" sheetId="1" r:id="rId1"/>
     <sheet name="精选场次" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">智胜库!$A$1:$I$375</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">智胜库!$A$1:$I$392</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3824" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4296" uniqueCount="906">
   <si>
     <t>日期</t>
   </si>
@@ -2525,6 +2525,186 @@
     <t>城南FC</t>
   </si>
   <si>
+    <t>4:0</t>
+  </si>
+  <si>
+    <t>林肯红魔(中)</t>
+  </si>
+  <si>
+    <t>0:2</t>
+  </si>
+  <si>
+    <t>芬甲</t>
+  </si>
+  <si>
+    <t>卡亚尼卡帕</t>
+  </si>
+  <si>
+    <t>吉普</t>
+  </si>
+  <si>
+    <t>特拉布宗体育</t>
+  </si>
+  <si>
+    <t>布莱顿</t>
+  </si>
+  <si>
+    <t>克拉斯维克</t>
+  </si>
+  <si>
+    <t>比尔森胜利</t>
+  </si>
+  <si>
+    <t>OFI克里特</t>
+  </si>
+  <si>
+    <t>德利塔(中)</t>
+  </si>
+  <si>
+    <t>摩纳哥</t>
+  </si>
+  <si>
+    <t>2:4</t>
+  </si>
+  <si>
+    <t>亚特兰大</t>
+  </si>
+  <si>
+    <t>弗赖堡</t>
+  </si>
+  <si>
+    <t>赫拉德茨</t>
+  </si>
+  <si>
+    <t>布拉加</t>
+  </si>
+  <si>
+    <t>赫塔菲</t>
+  </si>
+  <si>
+    <t>巴列卡诺</t>
+  </si>
+  <si>
+    <t>阿拉维斯</t>
+  </si>
+  <si>
+    <t>英甲</t>
+  </si>
+  <si>
+    <t>谢周三</t>
+  </si>
+  <si>
+    <t>布拉德福德</t>
+  </si>
+  <si>
+    <t>瑞典杯</t>
+  </si>
+  <si>
+    <t>派提亚</t>
+  </si>
+  <si>
+    <t>客让3</t>
+  </si>
+  <si>
+    <t>FC阿尔兰达</t>
+  </si>
+  <si>
+    <t>奥斯特桑斯</t>
+  </si>
+  <si>
+    <t>俄杯</t>
+  </si>
+  <si>
+    <t>加里宁格勒</t>
+  </si>
+  <si>
+    <t>马哈奇卡拉</t>
+  </si>
+  <si>
+    <t>图尔克</t>
+  </si>
+  <si>
+    <t>泰格雷</t>
+  </si>
+  <si>
+    <t>圣塔菲</t>
+  </si>
+  <si>
+    <t>河床</t>
+  </si>
+  <si>
+    <t>保地花高SP</t>
+  </si>
+  <si>
+    <t>克里丘马</t>
+  </si>
+  <si>
+    <t>巴西竞技</t>
+  </si>
+  <si>
+    <t>雷加塔斯巴西</t>
+  </si>
+  <si>
+    <t>诺瓦里桑蒂诺</t>
+  </si>
+  <si>
+    <t>米内罗美洲</t>
+  </si>
+  <si>
+    <t>美职业</t>
+  </si>
+  <si>
+    <t>堪萨斯城竞技</t>
+  </si>
+  <si>
+    <t>圣路易斯城</t>
+  </si>
+  <si>
+    <t>明尼苏达联</t>
+  </si>
+  <si>
+    <t>亚特兰大联</t>
+  </si>
+  <si>
+    <t>科罗拉多急流</t>
+  </si>
+  <si>
+    <t>洛杉矶FC</t>
+  </si>
+  <si>
+    <t>皇家盐湖城</t>
+  </si>
+  <si>
+    <t>达拉斯FC</t>
+  </si>
+  <si>
+    <t>3:4</t>
+  </si>
+  <si>
+    <t>西雅图海湾人</t>
+  </si>
+  <si>
+    <t>奥斯汀FC</t>
+  </si>
+  <si>
+    <t>洛杉矶银河</t>
+  </si>
+  <si>
+    <t>圣何塞地震</t>
+  </si>
+  <si>
+    <t>波特兰伐木者</t>
+  </si>
+  <si>
+    <t>圣地亚哥</t>
+  </si>
+  <si>
+    <t>温哥华白浪</t>
+  </si>
+  <si>
+    <t>休斯敦迪纳摩</t>
+  </si>
+  <si>
     <t>推荐方向</t>
   </si>
   <si>
@@ -2540,9 +2720,6 @@
     <t>古比斯-1/1.5+大球</t>
   </si>
   <si>
-    <t>0:2</t>
-  </si>
-  <si>
     <t>客队穿盘</t>
   </si>
   <si>
@@ -2625,6 +2802,15 @@
   </si>
   <si>
     <t>黑马终结</t>
+  </si>
+  <si>
+    <t>客场劣势被高估</t>
+  </si>
+  <si>
+    <t>伤病被高估</t>
+  </si>
+  <si>
+    <t>进攻哑火</t>
   </si>
 </sst>
 </file>
@@ -3823,7 +4009,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I392"/>
+  <dimension ref="A1:I446"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" style="5"/>
@@ -15201,9 +15387,1575 @@
         <v>483</v>
       </c>
     </row>
+    <row r="393" spans="1:9">
+      <c r="A393" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B393" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C393" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="D393" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="E393" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F393" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G393" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="H393" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I393" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9">
+      <c r="A394" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B394" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C394" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="D394" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E394" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F394" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G394" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="H394" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I394" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9">
+      <c r="A395" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B395" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D395" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="E395" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F395" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G395" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H395" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I395" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9">
+      <c r="A396" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B396" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C396" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D396" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E396" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F396" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G396" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="H396" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I396" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9">
+      <c r="A397" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B397" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="D397" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="E397" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F397" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G397" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="H397" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I397" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9">
+      <c r="A398" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B398" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="C398" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="D398" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="E398" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F398" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G398" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="H398" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I398" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9">
+      <c r="A399" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B399" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C399" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="D399" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="E399" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="F399" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="G399" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="H399" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I399" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9">
+      <c r="A400" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B400" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C400" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D400" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E400" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F400" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G400" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="H400" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I400" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9">
+      <c r="A401" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C401" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="D401" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="E401" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F401" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G401" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H401" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I401" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9">
+      <c r="A402" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B402" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C402" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D402" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E402" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F402" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G402" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H402" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I402" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9">
+      <c r="A403" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B403" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C403" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="D403" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="E403" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F403" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G403" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="H403" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I403" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9">
+      <c r="A404" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B404" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C404" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D404" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E404" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F404" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G404" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="H404" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I404" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9">
+      <c r="A405" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B405" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C405" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D405" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="E405" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F405" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G405" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="H405" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I405" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9">
+      <c r="A406" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B406" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="D406" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="E406" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F406" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G406" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="H406" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I406" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9">
+      <c r="A407" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B407" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C407" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="D407" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E407" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F407" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G407" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H407" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I407" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9">
+      <c r="A408" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B408" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C408" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="D408" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="E408" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F408" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G408" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="H408" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I408" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9">
+      <c r="A409" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B409" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C409" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="D409" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="E409" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F409" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G409" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="H409" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I409" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9">
+      <c r="A410" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B410" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C410" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D410" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E410" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F410" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G410" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="H410" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I410" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9">
+      <c r="A411" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B411" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C411" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="D411" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E411" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F411" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G411" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="H411" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I411" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9">
+      <c r="A412" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B412" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C412" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D412" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="E412" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F412" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G412" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="H412" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I412" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9">
+      <c r="A413" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B413" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C413" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D413" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="E413" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F413" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G413" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H413" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I413" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9">
+      <c r="A414" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B414" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C414" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D414" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="E414" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F414" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G414" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="H414" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I414" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9">
+      <c r="A415" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B415" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C415" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D415" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="E415" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F415" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G415" s="6" t="s">
+        <v>823</v>
+      </c>
+      <c r="H415" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I415" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9">
+      <c r="A416" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B416" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C416" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="D416" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="E416" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="F416" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G416" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="H416" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I416" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9">
+      <c r="A417" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B417" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="D417" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="E417" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F417" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G417" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="H417" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I417" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9">
+      <c r="A418" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B418" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C418" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="D418" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="E418" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F418" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G418" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="H418" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I418" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9">
+      <c r="A419" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B419" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C419" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="D419" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="E419" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F419" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G419" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="H419" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I419" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9">
+      <c r="A420" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B420" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C420" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D420" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="E420" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F420" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G420" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="H420" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I420" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9">
+      <c r="A421" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B421" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C421" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="D421" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="E421" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F421" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G421" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="H421" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I421" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9">
+      <c r="A422" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B422" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C422" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="D422" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E422" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F422" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G422" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="H422" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I422" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9">
+      <c r="A423" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B423" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C423" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="D423" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E423" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F423" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G423" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="H423" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I423" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9">
+      <c r="A424" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B424" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C424" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="D424" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="E424" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F424" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G424" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="H424" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I424" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9">
+      <c r="A425" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B425" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C425" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="D425" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="E425" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F425" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G425" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="H425" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I425" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9">
+      <c r="A426" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B426" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C426" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D426" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E426" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F426" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G426" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H426" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I426" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9">
+      <c r="A427" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B427" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C427" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="D427" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E427" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="F427" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="G427" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="H427" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I427" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9">
+      <c r="A428" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B428" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="D428" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="E428" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F428" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G428" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H428" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I428" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9">
+      <c r="A429" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B429" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="C429" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="D429" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="E429" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="F429" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G429" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H429" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I429" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9">
+      <c r="A430" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B430" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="C430" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="D430" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E430" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="F430" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G430" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="H430" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I430" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9">
+      <c r="A431" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B431" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="C431" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="D431" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="E431" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F431" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G431" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="H431" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I431" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9">
+      <c r="A432" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B432" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="C432" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="D432" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="E432" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F432" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G432" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H432" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I432" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9">
+      <c r="A433" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B433" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="C433" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="D433" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="E433" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F433" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G433" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="H433" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I433" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9">
+      <c r="A434" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B434" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="C434" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="D434" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="E434" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F434" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G434" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="H434" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I434" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9">
+      <c r="A435" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B435" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="C435" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="D435" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="E435" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="F435" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G435" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H435" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I435" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9">
+      <c r="A436" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B436" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C436" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="D436" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="E436" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F436" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G436" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H436" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I436" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9">
+      <c r="A437" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B437" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C437" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="D437" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="E437" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F437" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G437" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H437" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I437" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9">
+      <c r="A438" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B438" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C438" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="D438" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="E438" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F438" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G438" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H438" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I438" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9">
+      <c r="A439" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B439" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="D439" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="E439" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F439" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G439" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="H439" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I439" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9">
+      <c r="A440" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B440" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="C440" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="D440" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="E440" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F440" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G440" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="H440" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I440" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9">
+      <c r="A441" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B441" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="C441" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="D441" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="E441" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F441" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G441" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="H441" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I441" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9">
+      <c r="A442" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B442" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="C442" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="D442" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="E442" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F442" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G442" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="H442" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I442" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9">
+      <c r="A443" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B443" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="C443" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="D443" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="E443" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F443" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G443" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="H443" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I443" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9">
+      <c r="A444" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B444" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="C444" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="D444" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="E444" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F444" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G444" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="H444" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I444" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9">
+      <c r="A445" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B445" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="C445" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="D445" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="E445" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F445" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G445" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="H445" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I445" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9">
+      <c r="A446" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B446" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="C446" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="D446" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="E446" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F446" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G446" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H446" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I446" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I375" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:I375">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I392" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:I392">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -15216,7 +16968,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.875"/>
@@ -15237,7 +16989,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>810</v>
+        <v>870</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
@@ -15269,7 +17021,7 @@
         <v>739</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H2" t="s">
         <v>30</v>
@@ -15295,7 +17047,7 @@
         <v>715</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H3" t="s">
         <v>30</v>
@@ -15321,7 +17073,7 @@
         <v>795</v>
       </c>
       <c r="G4" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -15347,7 +17099,7 @@
         <v>739</v>
       </c>
       <c r="G5" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H5" t="s">
         <v>30</v>
@@ -15373,7 +17125,7 @@
         <v>731</v>
       </c>
       <c r="G6" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -15399,7 +17151,7 @@
         <v>727</v>
       </c>
       <c r="G7" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H7" t="s">
         <v>448</v>
@@ -15425,7 +17177,7 @@
         <v>727</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -15451,7 +17203,7 @@
         <v>715</v>
       </c>
       <c r="G9" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H9" t="s">
         <v>241</v>
@@ -15477,7 +17229,7 @@
         <v>731</v>
       </c>
       <c r="G10" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H10" t="s">
         <v>23</v>
@@ -15503,7 +17255,7 @@
         <v>727</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -15529,7 +17281,7 @@
         <v>715</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -15555,7 +17307,7 @@
         <v>781</v>
       </c>
       <c r="G13" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H13" t="s">
         <v>483</v>
@@ -15581,7 +17333,7 @@
         <v>727</v>
       </c>
       <c r="G14" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H14" t="s">
         <v>485</v>
@@ -15607,7 +17359,7 @@
         <v>733</v>
       </c>
       <c r="G15" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H15" t="s">
         <v>483</v>
@@ -15633,7 +17385,7 @@
         <v>727</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H16" t="s">
         <v>483</v>
@@ -15659,7 +17411,7 @@
         <v>770</v>
       </c>
       <c r="G17" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H17" t="s">
         <v>483</v>
@@ -15685,7 +17437,7 @@
         <v>770</v>
       </c>
       <c r="G18" t="s">
-        <v>813</v>
+        <v>873</v>
       </c>
       <c r="H18" t="s">
         <v>324</v>
@@ -15705,13 +17457,13 @@
         <v>651</v>
       </c>
       <c r="E19" t="s">
-        <v>814</v>
+        <v>874</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>770</v>
       </c>
       <c r="G19" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H19" t="s">
         <v>653</v>
@@ -15737,7 +17489,7 @@
         <v>722</v>
       </c>
       <c r="G20" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -15763,7 +17515,7 @@
         <v>709</v>
       </c>
       <c r="G21" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H21" t="s">
         <v>30</v>
@@ -15786,13 +17538,13 @@
         <v>657</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="G22" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H22" t="s">
-        <v>816</v>
+        <v>875</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -15815,7 +17567,7 @@
         <v>739</v>
       </c>
       <c r="G23" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H23" t="s">
         <v>124</v>
@@ -15841,7 +17593,7 @@
         <v>739</v>
       </c>
       <c r="G24" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H24" t="s">
         <v>666</v>
@@ -15867,7 +17619,7 @@
         <v>715</v>
       </c>
       <c r="G25" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -15893,7 +17645,7 @@
         <v>739</v>
       </c>
       <c r="G26" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H26" t="s">
         <v>666</v>
@@ -15919,10 +17671,10 @@
         <v>781</v>
       </c>
       <c r="G27" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H27" t="s">
-        <v>817</v>
+        <v>876</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -15945,7 +17697,7 @@
         <v>731</v>
       </c>
       <c r="G28" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H28" t="s">
         <v>679</v>
@@ -15968,10 +17720,10 @@
         <v>346</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="G29" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H29" t="s">
         <v>682</v>
@@ -15997,7 +17749,7 @@
         <v>709</v>
       </c>
       <c r="G30" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H30" t="s">
         <v>684</v>
@@ -16020,13 +17772,13 @@
         <v>362</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="G31" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H31" t="s">
-        <v>818</v>
+        <v>877</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -16049,7 +17801,7 @@
         <v>727</v>
       </c>
       <c r="G32" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H32" t="s">
         <v>692</v>
@@ -16075,7 +17827,7 @@
         <v>781</v>
       </c>
       <c r="G33" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H33" t="s">
         <v>693</v>
@@ -16101,10 +17853,10 @@
         <v>770</v>
       </c>
       <c r="G34" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H34" t="s">
-        <v>819</v>
+        <v>878</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -16127,10 +17879,10 @@
         <v>770</v>
       </c>
       <c r="G35" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H35" t="s">
-        <v>820</v>
+        <v>879</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -16153,7 +17905,7 @@
         <v>770</v>
       </c>
       <c r="G36" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H36" t="s">
         <v>696</v>
@@ -16179,10 +17931,10 @@
         <v>727</v>
       </c>
       <c r="G37" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H37" t="s">
-        <v>820</v>
+        <v>879</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -16205,7 +17957,7 @@
         <v>731</v>
       </c>
       <c r="G38" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H38" t="s">
         <v>703</v>
@@ -16231,10 +17983,10 @@
         <v>712</v>
       </c>
       <c r="G39" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H39" t="s">
-        <v>821</v>
+        <v>880</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -16257,10 +18009,10 @@
         <v>714</v>
       </c>
       <c r="G40" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H40" t="s">
-        <v>821</v>
+        <v>880</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -16283,10 +18035,10 @@
         <v>707</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H41" t="s">
-        <v>822</v>
+        <v>881</v>
       </c>
       <c r="I41" t="s">
         <v>713</v>
@@ -16312,7 +18064,7 @@
         <v>709</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H42" t="s">
         <v>702</v>
@@ -16341,7 +18093,7 @@
         <v>709</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H43" t="s">
         <v>711</v>
@@ -16364,13 +18116,13 @@
         <v>717</v>
       </c>
       <c r="E44" t="s">
-        <v>823</v>
+        <v>882</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>718</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H44" t="s">
         <v>719</v>
@@ -16390,13 +18142,13 @@
         <v>651</v>
       </c>
       <c r="E45" t="s">
-        <v>824</v>
+        <v>883</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>718</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H45" t="s">
         <v>720</v>
@@ -16422,10 +18174,10 @@
         <v>715</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H46" t="s">
-        <v>825</v>
+        <v>884</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -16448,7 +18200,7 @@
         <v>722</v>
       </c>
       <c r="G47" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H47" t="s">
         <v>723</v>
@@ -16474,10 +18226,10 @@
         <v>724</v>
       </c>
       <c r="G48" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H48" t="s">
-        <v>826</v>
+        <v>885</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -16500,10 +18252,10 @@
         <v>727</v>
       </c>
       <c r="G49" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H49" t="s">
-        <v>827</v>
+        <v>886</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -16526,7 +18278,7 @@
         <v>715</v>
       </c>
       <c r="G50" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H50" t="s">
         <v>729</v>
@@ -16552,7 +18304,7 @@
         <v>731</v>
       </c>
       <c r="G51" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H51" t="s">
         <v>732</v>
@@ -16578,7 +18330,7 @@
         <v>733</v>
       </c>
       <c r="G52" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H52" t="s">
         <v>734</v>
@@ -16604,7 +18356,7 @@
         <v>735</v>
       </c>
       <c r="G53" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H53" t="s">
         <v>736</v>
@@ -16630,10 +18382,10 @@
         <v>727</v>
       </c>
       <c r="G54" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H54" t="s">
-        <v>828</v>
+        <v>887</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -16656,7 +18408,7 @@
         <v>739</v>
       </c>
       <c r="G55" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H55" t="s">
         <v>740</v>
@@ -16682,7 +18434,7 @@
         <v>742</v>
       </c>
       <c r="G56" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H56" t="s">
         <v>23</v>
@@ -16708,7 +18460,7 @@
         <v>745</v>
       </c>
       <c r="G57" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H57" t="s">
         <v>746</v>
@@ -16734,7 +18486,7 @@
         <v>742</v>
       </c>
       <c r="G58" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H58" t="s">
         <v>748</v>
@@ -16760,7 +18512,7 @@
         <v>714</v>
       </c>
       <c r="G59" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H59" t="s">
         <v>749</v>
@@ -16786,7 +18538,7 @@
         <v>745</v>
       </c>
       <c r="G60" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H60" t="s">
         <v>750</v>
@@ -16812,10 +18564,10 @@
         <v>709</v>
       </c>
       <c r="G61" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H61" t="s">
-        <v>829</v>
+        <v>888</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -16838,7 +18590,7 @@
         <v>752</v>
       </c>
       <c r="G62" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -16864,10 +18616,10 @@
         <v>722</v>
       </c>
       <c r="G63" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H63" t="s">
-        <v>830</v>
+        <v>889</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -16890,7 +18642,7 @@
         <v>733</v>
       </c>
       <c r="G64" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H64" t="s">
         <v>16</v>
@@ -16916,7 +18668,7 @@
         <v>731</v>
       </c>
       <c r="G65" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H65" t="s">
         <v>755</v>
@@ -16942,7 +18694,7 @@
         <v>731</v>
       </c>
       <c r="G66" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H66" t="s">
         <v>756</v>
@@ -16968,10 +18720,10 @@
         <v>727</v>
       </c>
       <c r="G67" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H67" t="s">
-        <v>831</v>
+        <v>890</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -16994,7 +18746,7 @@
         <v>727</v>
       </c>
       <c r="G68" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H68" t="s">
         <v>759</v>
@@ -17020,10 +18772,10 @@
         <v>760</v>
       </c>
       <c r="G69" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H69" t="s">
-        <v>832</v>
+        <v>891</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -17046,7 +18798,7 @@
         <v>714</v>
       </c>
       <c r="G70" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H70" t="s">
         <v>763</v>
@@ -17072,7 +18824,7 @@
         <v>745</v>
       </c>
       <c r="G71" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H71" t="s">
         <v>764</v>
@@ -17098,10 +18850,10 @@
         <v>742</v>
       </c>
       <c r="G72" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H72" t="s">
-        <v>833</v>
+        <v>892</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -17124,7 +18876,7 @@
         <v>731</v>
       </c>
       <c r="G73" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H73" t="s">
         <v>112</v>
@@ -17150,7 +18902,7 @@
         <v>727</v>
       </c>
       <c r="G74" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H74" t="s">
         <v>767</v>
@@ -17176,10 +18928,10 @@
         <v>718</v>
       </c>
       <c r="G75" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H75" t="s">
-        <v>834</v>
+        <v>893</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -17202,7 +18954,7 @@
         <v>770</v>
       </c>
       <c r="G76" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H76" t="s">
         <v>771</v>
@@ -17228,7 +18980,7 @@
         <v>770</v>
       </c>
       <c r="G77" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H77" t="s">
         <v>773</v>
@@ -17254,7 +19006,7 @@
         <v>722</v>
       </c>
       <c r="G78" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H78" t="s">
         <v>748</v>
@@ -17280,10 +19032,10 @@
         <v>770</v>
       </c>
       <c r="G79" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H79" t="s">
-        <v>835</v>
+        <v>894</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -17306,10 +19058,10 @@
         <v>781</v>
       </c>
       <c r="G80" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H80" t="s">
-        <v>836</v>
+        <v>895</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -17332,10 +19084,10 @@
         <v>770</v>
       </c>
       <c r="G81" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H81" t="s">
-        <v>837</v>
+        <v>896</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -17358,10 +19110,10 @@
         <v>739</v>
       </c>
       <c r="G82" t="s">
-        <v>813</v>
+        <v>873</v>
       </c>
       <c r="H82" t="s">
-        <v>838</v>
+        <v>897</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -17384,10 +19136,10 @@
         <v>727</v>
       </c>
       <c r="G83" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H83" t="s">
-        <v>839</v>
+        <v>898</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -17410,7 +19162,7 @@
         <v>745</v>
       </c>
       <c r="G84" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H84" t="s">
         <v>791</v>
@@ -17436,10 +19188,10 @@
         <v>795</v>
       </c>
       <c r="G85" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H85" t="s">
-        <v>840</v>
+        <v>899</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -17462,13 +19214,13 @@
         <v>722</v>
       </c>
       <c r="G86" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H86" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="I86" t="s">
-        <v>841</v>
+        <v>900</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -17491,13 +19243,13 @@
         <v>718</v>
       </c>
       <c r="G87" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H87" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="I87" t="s">
-        <v>841</v>
+        <v>900</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -17520,10 +19272,10 @@
         <v>770</v>
       </c>
       <c r="G88" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H88" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="I88" t="s">
         <v>799</v>
@@ -17549,13 +19301,13 @@
         <v>715</v>
       </c>
       <c r="G89" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H89" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="I89" t="s">
-        <v>842</v>
+        <v>901</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -17578,10 +19330,10 @@
         <v>781</v>
       </c>
       <c r="G90" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H90" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="I90" t="s">
         <v>801</v>
@@ -17607,10 +19359,10 @@
         <v>715</v>
       </c>
       <c r="G91" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H91" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="I91" t="s">
         <v>439</v>
@@ -17636,10 +19388,10 @@
         <v>795</v>
       </c>
       <c r="G92" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H92" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="I92" t="s">
         <v>803</v>
@@ -17665,13 +19417,13 @@
         <v>727</v>
       </c>
       <c r="G93" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H93" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="I93" t="s">
-        <v>843</v>
+        <v>902</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -17694,10 +19446,10 @@
         <v>715</v>
       </c>
       <c r="G94" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="H94" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="I94" t="s">
         <v>807</v>
@@ -17723,10 +19475,10 @@
         <v>739</v>
       </c>
       <c r="G95" t="s">
-        <v>813</v>
+        <v>873</v>
       </c>
       <c r="H95" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="I95" t="s">
         <v>59</v>
@@ -17752,13 +19504,158 @@
         <v>739</v>
       </c>
       <c r="G96" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H96" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="I96" t="s">
         <v>483</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B97" t="s">
+        <v>276</v>
+      </c>
+      <c r="C97" t="s">
+        <v>384</v>
+      </c>
+      <c r="D97" t="s">
+        <v>280</v>
+      </c>
+      <c r="E97" t="s">
+        <v>804</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="G97" t="s">
+        <v>871</v>
+      </c>
+      <c r="H97" t="s">
+        <v>871</v>
+      </c>
+      <c r="I97" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B98" t="s">
+        <v>276</v>
+      </c>
+      <c r="C98" t="s">
+        <v>178</v>
+      </c>
+      <c r="D98" t="s">
+        <v>425</v>
+      </c>
+      <c r="E98" t="s">
+        <v>804</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="G98" t="s">
+        <v>871</v>
+      </c>
+      <c r="H98" t="s">
+        <v>872</v>
+      </c>
+      <c r="I98" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B99" t="s">
+        <v>276</v>
+      </c>
+      <c r="C99" t="s">
+        <v>423</v>
+      </c>
+      <c r="D99" t="s">
+        <v>390</v>
+      </c>
+      <c r="E99" t="s">
+        <v>780</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="G99" t="s">
+        <v>872</v>
+      </c>
+      <c r="H99" t="s">
+        <v>872</v>
+      </c>
+      <c r="I99" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B100" t="s">
+        <v>378</v>
+      </c>
+      <c r="C100" t="s">
+        <v>307</v>
+      </c>
+      <c r="D100" t="s">
+        <v>429</v>
+      </c>
+      <c r="E100" t="s">
+        <v>424</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="G100" t="s">
+        <v>871</v>
+      </c>
+      <c r="H100" t="s">
+        <v>871</v>
+      </c>
+      <c r="I100" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B101" t="s">
+        <v>276</v>
+      </c>
+      <c r="C101" t="s">
+        <v>473</v>
+      </c>
+      <c r="D101" t="s">
+        <v>267</v>
+      </c>
+      <c r="E101" t="s">
+        <v>780</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="G101" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" t="s">
+        <v>872</v>
+      </c>
+      <c r="I101" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
